--- a/EKİM SD KARNE.xlsx
+++ b/EKİM SD KARNE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B263361-1C5A-43FC-A111-9C52BBE1A43F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15A92C8-BA31-4935-8C3F-8721E6971174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2690,11 +2690,11 @@
       </c>
       <c r="B9" s="75">
         <f>I32</f>
-        <v>1538171</v>
+        <v>1683906</v>
       </c>
       <c r="C9" s="76">
         <f>IFERROR(B9/A9,)</f>
-        <v>0.51272366666666669</v>
+        <v>0.56130199999999997</v>
       </c>
       <c r="D9" s="168">
         <f>IFERROR(IF(B9&lt;=A9,A4,IF(AND(B9&gt;A9,B9&lt;B1),A4,IF(AND(B9&gt;=B1,B9&lt;C1),B4,IF(AND(B9&gt;=C1,B9&lt;D1),C4,IF(AND(B9&gt;=D1,B9&lt;E1),D4,IF(AND(B9&gt;=E1,B9&lt;F1),E4,IF(AND(B9&gt;=F1,B9&lt;G1),F4,IF(AND(B9&gt;=G1,B9&lt;H1),G4,IF(AND(B9&gt;=H1,B9&lt;I1),H4,IF(AND(B9&gt;=I1,B9&lt;J1),I4,IF(AND(B9&gt;=J1,B9&lt;K1),J4,IF(B9&gt;=K4,K4,K4)))))))))))),)</f>
@@ -2761,27 +2761,27 @@
       </c>
       <c r="H10" s="83">
         <f ca="1">B11-M10</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I10" s="84">
         <f>C11</f>
-        <v>3553</v>
+        <v>4053</v>
       </c>
       <c r="J10" s="85">
         <f ca="1">I10/H10</f>
-        <v>209</v>
+        <v>225.16666666666666</v>
       </c>
       <c r="K10" s="85">
         <f>IFERROR(I10/G10,)</f>
-        <v>710.6</v>
+        <v>810.6</v>
       </c>
       <c r="L10" s="86">
         <f ca="1">IFERROR(J10/G10,)</f>
-        <v>41.8</v>
+        <v>45.033333333333331</v>
       </c>
       <c r="M10" s="87">
         <f ca="1">(M11-A11)+B11</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N10" s="2">
         <f>LOOKUP(A9,'PRİM HAVUZU (SV SİSTEM)'!$A:$A,'PRİM HAVUZU (SV SİSTEM)'!$C:$C)*A9</f>
@@ -2804,14 +2804,14 @@
     <row r="11" spans="1:58" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="169">
         <f ca="1">TODAY()</f>
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B11" s="170">
         <f ca="1">(N11-M11)+1</f>
         <v>31</v>
       </c>
       <c r="C11" s="171">
-        <v>3553</v>
+        <v>4053</v>
       </c>
       <c r="F11" s="66"/>
       <c r="K11" s="89"/>
@@ -2977,35 +2977,35 @@
       </c>
       <c r="D13" s="107" cm="1">
         <f t="array" ref="D13:D31">DATA!C2:C20</f>
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E13" s="107" cm="1">
         <f t="array" ref="E13:E31">DATA!D2:D20</f>
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="F13" s="108">
         <f>DATA!E2</f>
-        <v>1.5161290322580645</v>
+        <v>1.5223880597014925</v>
       </c>
       <c r="G13" s="109">
         <f>DATA!F2</f>
-        <v>5985.6129032258068</v>
+        <v>5941.6567164179105</v>
       </c>
       <c r="H13" s="109">
         <f>DATA!G2</f>
-        <v>3947.9574468085107</v>
+        <v>3902.8529411764707</v>
       </c>
       <c r="I13" s="106" cm="1">
         <f t="array" ref="I13:I31">DATA!B2:B20</f>
-        <v>371108</v>
+        <v>398091</v>
       </c>
       <c r="J13" s="110">
         <f t="shared" ref="J13:J31" si="3">IFERROR(I13/C13,0)</f>
-        <v>0.7781296774193549</v>
+        <v>0.83470693548387109</v>
       </c>
       <c r="K13" s="111">
         <f>IFERROR(I13/$I$32,)</f>
-        <v>0.24126576303934999</v>
+        <v>0.236409277002398</v>
       </c>
       <c r="L13" s="112" t="str">
         <f t="shared" ref="L13:L31" si="4">IFERROR(IF(J13&lt;0.85,"",IF(AND(J13&gt;0.85,J13&lt;1),$M$2*AB13*AJ13,$M$2*AB13*AJ13)),"")</f>
@@ -3017,38 +3017,38 @@
       </c>
       <c r="N13" s="114">
         <f>IFERROR(IF(C13-I13&lt;0,"",C13-I13),"")</f>
-        <v>105815.07692307688</v>
+        <v>78832.076923076878</v>
       </c>
       <c r="O13" s="114">
         <f t="shared" ref="O13:O31" si="6">IFERROR(IF(N13/(W13-V13)&gt;0,N13/(W13-V13),""),"")</f>
-        <v>7558.219780219777</v>
+        <v>6064.0059171597595</v>
       </c>
       <c r="P13" s="110">
         <f t="shared" ref="P13:P31" si="7">IFERROR(I13/C13,0)</f>
-        <v>0.7781296774193549</v>
+        <v>0.83470693548387109</v>
       </c>
       <c r="Q13" s="109">
         <f t="shared" ref="Q13:Q31" si="8">IF(V13="",0,IF(W13=V13,I13,(I13/V13)*(W13-V13)+I13))</f>
-        <v>676726.35294117639</v>
+        <v>685601.16666666674</v>
       </c>
       <c r="R13" s="115">
         <f>IFERROR(Q13/$Q$32,)</f>
-        <v>0.23805183025545271</v>
+        <v>0.23244897733154324</v>
       </c>
       <c r="S13" s="106">
         <f>IFERROR(IF(T13&lt;0.85,"",IF(AND(T13&gt;0.85,T13&lt;1),$M$2*AD13*AK13,$M$2*AD13*AK13)),"")</f>
-        <v>13111.894810470334</v>
+        <v>12803.289671421402</v>
       </c>
       <c r="T13" s="110">
         <f t="shared" ref="T13:T31" si="9">IFERROR(Q13/C13,0)</f>
-        <v>1.4189423529411764</v>
+        <v>1.4375508333333336</v>
       </c>
       <c r="U13" s="116">
         <f t="shared" ref="U13:U31" si="10">IFERROR(D13/Z13,0)</f>
-        <v>8.6223738017582485E-2</v>
+        <v>8.1736436658716452E-2</v>
       </c>
       <c r="V13" s="62">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W13" s="63">
         <v>31</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z13" s="118">
         <f t="shared" ref="Z13:Z31" si="12">(V13/$V$32)*$I$10</f>
-        <v>719.05952380952385</v>
+        <v>819.70786516853934</v>
       </c>
       <c r="AA13" s="119">
         <f t="shared" ref="AA13:AA31" si="13">IFERROR(((Y13/$Y$32)*$A$9),"")</f>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AB13" s="120">
         <f t="shared" ref="AB13:AB31" si="14">I13/$I$32</f>
-        <v>0.24126576303934999</v>
+        <v>0.236409277002398</v>
       </c>
       <c r="AC13" s="121">
         <f>AA13/$C$32</f>
@@ -3075,15 +3075,15 @@
       </c>
       <c r="AD13" s="120">
         <f>Q13/$Q$32</f>
-        <v>0.23805183025545271</v>
+        <v>0.23244897733154324</v>
       </c>
       <c r="AE13" s="120">
         <f t="shared" ref="AE13:AE31" si="15">I13/C13</f>
-        <v>0.7781296774193549</v>
+        <v>0.83470693548387109</v>
       </c>
       <c r="AF13" s="120">
         <f t="shared" ref="AF13:AF31" si="16">Q13/C13</f>
-        <v>1.4189423529411764</v>
+        <v>1.4375508333333336</v>
       </c>
       <c r="AG13" s="120">
         <f>IFERROR(VLOOKUP(A13,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3124,33 +3124,33 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D14" s="126">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E14" s="126">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="F14" s="127">
         <f>DATA!E3</f>
-        <v>1.5192307692307692</v>
+        <v>1.5862068965517242</v>
       </c>
       <c r="G14" s="128">
         <f>DATA!F3</f>
-        <v>6605.9807692307695</v>
+        <v>6679.6379310344828</v>
       </c>
       <c r="H14" s="128">
         <f>DATA!G3</f>
-        <v>4348.2405063291135</v>
+        <v>4211.076086956522</v>
       </c>
       <c r="I14" s="125">
-        <v>343511</v>
+        <v>387419</v>
       </c>
       <c r="J14" s="129">
         <f t="shared" si="3"/>
-        <v>0.54019875000000006</v>
+        <v>0.60924762096774199</v>
       </c>
       <c r="K14" s="111">
         <f t="shared" ref="K14:K31" si="21">IFERROR(I14/$I$32,)</f>
-        <v>0.22332432479873823</v>
+        <v>0.23007163107679407</v>
       </c>
       <c r="L14" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3162,38 +3162,38 @@
       </c>
       <c r="N14" s="130">
         <f t="shared" ref="N14:N31" si="22">IFERROR(IF(C14-I14&lt;0,"",C14-I14),"")</f>
-        <v>292386.43589743588</v>
+        <v>248478.43589743588</v>
       </c>
       <c r="O14" s="130">
         <f t="shared" si="6"/>
-        <v>20884.745421245421</v>
+        <v>19113.725838264298</v>
       </c>
       <c r="P14" s="129">
         <f t="shared" si="7"/>
-        <v>0.54019875000000006</v>
+        <v>0.60924762096774199</v>
       </c>
       <c r="Q14" s="109">
         <f t="shared" si="8"/>
-        <v>626402.4117647059</v>
+        <v>667221.61111111112</v>
       </c>
       <c r="R14" s="115">
         <f t="shared" ref="R14:R31" si="23">IFERROR(Q14/$Q$32,)</f>
-        <v>0.22034939226015293</v>
+        <v>0.22621749888545367</v>
       </c>
       <c r="S14" s="106">
         <f t="shared" ref="S14:S31" si="24">IFERROR(IF(T14&lt;0.85,"",IF(AND(T14&gt;0.85,T14&lt;1),$M$2*AD14*AK14,$M$2*AD14*AK14)),"")</f>
-        <v>9709.4756205513786</v>
+        <v>10798.718526796018</v>
       </c>
       <c r="T14" s="129">
         <f t="shared" si="9"/>
-        <v>0.98506830882352947</v>
+        <v>1.0492597916666668</v>
       </c>
       <c r="U14" s="131">
         <f t="shared" si="10"/>
-        <v>7.2316683498617571E-2</v>
+        <v>7.0756915316500801E-2</v>
       </c>
       <c r="V14" s="62">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W14" s="64">
         <v>31</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="Z14" s="133">
         <f t="shared" si="12"/>
-        <v>719.05952380952385</v>
+        <v>819.70786516853934</v>
       </c>
       <c r="AA14" s="17">
         <f t="shared" si="13"/>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="AB14" s="134">
         <f t="shared" si="14"/>
-        <v>0.22332432479873823</v>
+        <v>0.23007163107679407</v>
       </c>
       <c r="AC14" s="135">
         <f t="shared" ref="AC14:AC31" si="25">AA14/$C$32</f>
@@ -3220,15 +3220,15 @@
       </c>
       <c r="AD14" s="134">
         <f t="shared" ref="AD14:AD18" si="26">Q14/$Q$32</f>
-        <v>0.22034939226015293</v>
+        <v>0.22621749888545367</v>
       </c>
       <c r="AE14" s="134">
         <f t="shared" si="15"/>
-        <v>0.54019875000000006</v>
+        <v>0.60924762096774199</v>
       </c>
       <c r="AF14" s="134">
         <f t="shared" si="16"/>
-        <v>0.98506830882352947</v>
+        <v>1.0492597916666668</v>
       </c>
       <c r="AG14" s="134">
         <f>IFERROR(VLOOKUP(A14,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="AK14" s="137">
         <f t="shared" si="19"/>
-        <v>0.96</v>
+        <v>1.04</v>
       </c>
       <c r="AL14" s="93">
         <v>0.88</v>
@@ -3269,33 +3269,33 @@
         <v>615384.61538461538</v>
       </c>
       <c r="D15" s="126">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E15" s="126">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F15" s="127">
         <f>DATA!E4</f>
-        <v>1.2982456140350878</v>
+        <v>1.2666666666666666</v>
       </c>
       <c r="G15" s="128">
         <f>DATA!F4</f>
-        <v>5089.7894736842109</v>
+        <v>5057.3</v>
       </c>
       <c r="H15" s="128">
         <f>DATA!G4</f>
-        <v>3920.5135135135133</v>
+        <v>3992.6052631578946</v>
       </c>
       <c r="I15" s="125">
-        <v>290118</v>
+        <v>303438</v>
       </c>
       <c r="J15" s="129">
         <f t="shared" si="3"/>
-        <v>0.47144174999999999</v>
+        <v>0.49308675000000002</v>
       </c>
       <c r="K15" s="111">
         <f t="shared" si="21"/>
-        <v>0.18861231943652559</v>
+        <v>0.18019889471265024</v>
       </c>
       <c r="L15" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3307,38 +3307,38 @@
       </c>
       <c r="N15" s="130">
         <f t="shared" si="22"/>
-        <v>325266.61538461538</v>
+        <v>311946.61538461538</v>
       </c>
       <c r="O15" s="130">
         <f t="shared" si="6"/>
-        <v>23233.329670329669</v>
+        <v>23995.893491124261</v>
       </c>
       <c r="P15" s="129">
         <f t="shared" si="7"/>
-        <v>0.47144174999999999</v>
+        <v>0.49308675000000002</v>
       </c>
       <c r="Q15" s="109">
         <f t="shared" si="8"/>
-        <v>543971.25</v>
+        <v>535478.82352941181</v>
       </c>
       <c r="R15" s="115">
         <f t="shared" si="23"/>
-        <v>0.1913526067162076</v>
+        <v>0.1815508942571952</v>
       </c>
       <c r="S15" s="106">
         <f t="shared" si="24"/>
-        <v>6675.1443326881863</v>
+        <v>6166.5576743398915</v>
       </c>
       <c r="T15" s="129">
         <f t="shared" si="9"/>
-        <v>0.88395328125000006</v>
+        <v>0.87015308823529425</v>
       </c>
       <c r="U15" s="131">
         <f t="shared" si="10"/>
-        <v>8.4224598930481287E-2</v>
+        <v>7.750250359211043E-2</v>
       </c>
       <c r="V15" s="62">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W15" s="64">
         <v>30</v>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="Z15" s="133">
         <f t="shared" si="12"/>
-        <v>676.7619047619047</v>
+        <v>774.16853932584263</v>
       </c>
       <c r="AA15" s="17">
         <f t="shared" si="13"/>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="AB15" s="134">
         <f t="shared" si="14"/>
-        <v>0.18861231943652559</v>
+        <v>0.18019889471265024</v>
       </c>
       <c r="AC15" s="135">
         <f t="shared" si="25"/>
@@ -3365,15 +3365,15 @@
       </c>
       <c r="AD15" s="134">
         <f t="shared" si="26"/>
-        <v>0.1913526067162076</v>
+        <v>0.1815508942571952</v>
       </c>
       <c r="AE15" s="134">
         <f t="shared" si="15"/>
-        <v>0.47144174999999999</v>
+        <v>0.49308675000000002</v>
       </c>
       <c r="AF15" s="134">
         <f t="shared" si="16"/>
-        <v>0.88395328125000006</v>
+        <v>0.87015308823529425</v>
       </c>
       <c r="AG15" s="134">
         <f>IFERROR(VLOOKUP(A15,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="AK15" s="137">
         <f t="shared" si="19"/>
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="AL15" s="93">
         <v>0.89</v>
@@ -3414,33 +3414,33 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D16" s="126">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E16" s="126">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="F16" s="127">
         <f>DATA!E5</f>
-        <v>1.76</v>
+        <v>1.736842105263158</v>
       </c>
       <c r="G16" s="128">
         <f>DATA!F5</f>
-        <v>6473.56</v>
+        <v>6538.5087719298244</v>
       </c>
       <c r="H16" s="128">
         <f>DATA!G5</f>
-        <v>3678.159090909091</v>
+        <v>3764.5959595959598</v>
       </c>
       <c r="I16" s="125">
-        <v>323678</v>
+        <v>372695</v>
       </c>
       <c r="J16" s="129">
         <f t="shared" si="3"/>
-        <v>0.50900975806451609</v>
+        <v>0.58609294354838715</v>
       </c>
       <c r="K16" s="111">
         <f t="shared" si="21"/>
-        <v>0.21043043978855408</v>
+        <v>0.22132767506024684</v>
       </c>
       <c r="L16" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3452,38 +3452,38 @@
       </c>
       <c r="N16" s="130">
         <f t="shared" ref="N16:N25" si="28">IFERROR(IF(C16-I16&lt;0,"",C16-I16),"")</f>
-        <v>312219.43589743588</v>
+        <v>263202.43589743588</v>
       </c>
       <c r="O16" s="130">
         <f t="shared" si="6"/>
-        <v>22301.388278388276</v>
+        <v>20246.341222879684</v>
       </c>
       <c r="P16" s="129">
         <f t="shared" si="7"/>
-        <v>0.50900975806451609</v>
+        <v>0.58609294354838715</v>
       </c>
       <c r="Q16" s="109">
         <f t="shared" si="8"/>
-        <v>590236.35294117639</v>
+        <v>641863.61111111112</v>
       </c>
       <c r="R16" s="115">
         <f t="shared" si="23"/>
-        <v>0.20762726837854323</v>
+        <v>0.21762002056459326</v>
       </c>
       <c r="S16" s="106">
         <f t="shared" si="24"/>
-        <v>8005.2769596031121</v>
+        <v>9988.7589439148305</v>
       </c>
       <c r="T16" s="129">
         <f t="shared" si="9"/>
-        <v>0.92819426470588229</v>
+        <v>1.0093822916666668</v>
       </c>
       <c r="U16" s="131">
         <f t="shared" si="10"/>
-        <v>6.9535272594824588E-2</v>
+        <v>6.953696850069907E-2</v>
       </c>
       <c r="V16" s="62">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W16" s="64">
         <v>31</v>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="Z16" s="133">
         <f t="shared" si="12"/>
-        <v>719.05952380952385</v>
+        <v>819.70786516853934</v>
       </c>
       <c r="AA16" s="17">
         <f t="shared" si="13"/>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="AB16" s="134">
         <f t="shared" si="14"/>
-        <v>0.21043043978855408</v>
+        <v>0.22132767506024684</v>
       </c>
       <c r="AC16" s="135">
         <f t="shared" si="25"/>
@@ -3510,15 +3510,15 @@
       </c>
       <c r="AD16" s="134">
         <f t="shared" si="26"/>
-        <v>0.20762726837854323</v>
+        <v>0.21762002056459326</v>
       </c>
       <c r="AE16" s="134">
         <f t="shared" si="15"/>
-        <v>0.50900975806451609</v>
+        <v>0.58609294354838715</v>
       </c>
       <c r="AF16" s="134">
         <f t="shared" si="16"/>
-        <v>0.92819426470588229</v>
+        <v>1.0093822916666668</v>
       </c>
       <c r="AG16" s="134">
         <f>IFERROR(VLOOKUP(A16,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3538,7 +3538,7 @@
       </c>
       <c r="AK16" s="137">
         <f t="shared" si="19"/>
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="AL16" s="93">
         <v>0.9</v>
@@ -3559,33 +3559,33 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D17" s="126">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E17" s="126">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F17" s="127">
         <f>DATA!E6</f>
-        <v>1.325</v>
+        <v>1.2666666666666666</v>
       </c>
       <c r="G17" s="128">
         <f>DATA!F6</f>
-        <v>5558.35</v>
+        <v>5410.3777777777777</v>
       </c>
       <c r="H17" s="128">
         <f>DATA!G6</f>
-        <v>4194.9811320754716</v>
+        <v>4271.3508771929828</v>
       </c>
       <c r="I17" s="125">
-        <v>222334</v>
+        <v>243467</v>
       </c>
       <c r="J17" s="129">
         <f t="shared" si="3"/>
-        <v>0.34963814516129033</v>
+        <v>0.38287149193548387</v>
       </c>
       <c r="K17" s="111">
         <f t="shared" si="21"/>
-        <v>0.14454439720941301</v>
+        <v>0.14458467396636154</v>
       </c>
       <c r="L17" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3597,23 +3597,23 @@
       </c>
       <c r="N17" s="130">
         <f t="shared" si="28"/>
-        <v>413563.43589743588</v>
+        <v>392430.43589743588</v>
       </c>
       <c r="O17" s="130">
         <f t="shared" si="6"/>
-        <v>29540.245421245421</v>
+        <v>30186.956607495067</v>
       </c>
       <c r="P17" s="129">
         <f t="shared" si="7"/>
-        <v>0.34963814516129033</v>
+        <v>0.38287149193548387</v>
       </c>
       <c r="Q17" s="109">
         <f t="shared" si="8"/>
-        <v>405432.5882352941</v>
+        <v>419304.27777777775</v>
       </c>
       <c r="R17" s="115">
         <f t="shared" si="23"/>
-        <v>0.14261890238964353</v>
+        <v>0.14216260896121446</v>
       </c>
       <c r="S17" s="106" t="str">
         <f t="shared" si="24"/>
@@ -3621,14 +3621,14 @@
       </c>
       <c r="T17" s="129">
         <f t="shared" si="9"/>
-        <v>0.63757544117647058</v>
+        <v>0.65938979166666667</v>
       </c>
       <c r="U17" s="131">
         <f t="shared" si="10"/>
-        <v>5.5628218075859666E-2</v>
+        <v>5.4897606711078212E-2</v>
       </c>
       <c r="V17" s="62">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W17" s="64">
         <v>31</v>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="Z17" s="133">
         <f t="shared" si="12"/>
-        <v>719.05952380952385</v>
+        <v>819.70786516853934</v>
       </c>
       <c r="AA17" s="17">
         <f t="shared" si="13"/>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="AB17" s="134">
         <f t="shared" si="14"/>
-        <v>0.14454439720941301</v>
+        <v>0.14458467396636154</v>
       </c>
       <c r="AC17" s="135">
         <f t="shared" si="25"/>
@@ -3655,15 +3655,15 @@
       </c>
       <c r="AD17" s="134">
         <f t="shared" si="26"/>
-        <v>0.14261890238964353</v>
+        <v>0.14216260896121446</v>
       </c>
       <c r="AE17" s="134">
         <f t="shared" si="15"/>
-        <v>0.34963814516129033</v>
+        <v>0.38287149193548387</v>
       </c>
       <c r="AF17" s="134">
         <f t="shared" si="16"/>
-        <v>0.63757544117647058</v>
+        <v>0.65938979166666667</v>
       </c>
       <c r="AG17" s="134">
         <f>IFERROR(VLOOKUP(A17,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3704,10 +3704,10 @@
         <v>0</v>
       </c>
       <c r="D18" s="126">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="E18" s="126">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="F18" s="127">
         <f>DATA!E7</f>
@@ -3715,14 +3715,14 @@
       </c>
       <c r="G18" s="128">
         <f>DATA!F7</f>
-        <v>3144.5</v>
+        <v>3534</v>
       </c>
       <c r="H18" s="128">
         <f>DATA!G7</f>
-        <v>3144.5</v>
+        <v>3534</v>
       </c>
       <c r="I18" s="125">
-        <v>-12578</v>
+        <v>-21204</v>
       </c>
       <c r="J18" s="129">
         <f t="shared" si="3"/>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="K18" s="111">
         <f t="shared" si="21"/>
-        <v>-8.1772442725808765E-3</v>
+        <v>-1.2592151818450673E-2</v>
       </c>
       <c r="L18" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="N18" s="130">
         <f t="shared" si="28"/>
-        <v>12578</v>
+        <v>21204</v>
       </c>
       <c r="O18" s="130" t="str">
         <f t="shared" si="6"/>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="AB18" s="138">
         <f t="shared" si="14"/>
-        <v>-8.1772442725808765E-3</v>
+        <v>-1.2592151818450673E-2</v>
       </c>
       <c r="AC18" s="135">
         <f t="shared" si="25"/>
@@ -5699,35 +5699,35 @@
       </c>
       <c r="D32" s="153">
         <f>SUM(D13:D31)</f>
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="E32" s="153">
         <f>SUM(E13:E31)</f>
-        <v>384</v>
+        <v>420</v>
       </c>
       <c r="F32" s="154">
         <f>IFERROR(SUM(F13:F31)/G10,)</f>
-        <v>1.6837210831047842</v>
+        <v>1.6757540789699412</v>
       </c>
       <c r="G32" s="155">
         <f>IFERROR(SUM(G13:G31)/G10,)</f>
-        <v>6571.5586292281569</v>
+        <v>6632.2962394319984</v>
       </c>
       <c r="H32" s="155">
         <f>IFERROR(SUM(H13:H31)/G10,)</f>
-        <v>4646.8703379271401</v>
+        <v>4735.2962256159663</v>
       </c>
       <c r="I32" s="155">
         <f>SUM(I13:I31)</f>
-        <v>1538171</v>
+        <v>1683906</v>
       </c>
       <c r="J32" s="156">
         <f>IFERROR(I32/C32,)</f>
-        <v>0.51272366666666669</v>
+        <v>0.56130199999999997</v>
       </c>
       <c r="K32" s="156">
         <f>SUM(K13:K31)</f>
-        <v>0.99999999999999978</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="L32" s="155">
         <f>SUM(L13:L31)</f>
@@ -5739,33 +5739,33 @@
       </c>
       <c r="N32" s="155">
         <f>SUM(N13:N31)</f>
-        <v>1461829</v>
+        <v>1316094</v>
       </c>
       <c r="O32" s="155">
         <f>SUM(O13:O31)</f>
-        <v>103517.92857142857</v>
+        <v>99606.923076923078</v>
       </c>
       <c r="P32" s="157"/>
       <c r="Q32" s="152">
         <f>SUM(Q13:Q31)</f>
-        <v>2842768.9558823528</v>
+        <v>2949469.490196079</v>
       </c>
       <c r="R32" s="156">
         <f>SUM(R13:R31)</f>
-        <v>1</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="S32" s="155">
         <f>SUM(S13:S31)</f>
-        <v>37501.791723313014</v>
+        <v>39757.324816472144</v>
       </c>
       <c r="T32" s="158">
         <f>IFERROR(Q32/C32,)</f>
-        <v>0.94758965196078426</v>
+        <v>0.98315649673202632</v>
       </c>
       <c r="U32" s="165"/>
       <c r="V32" s="166">
         <f>SUM(V13:V31)</f>
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="W32" s="167">
         <f>SUM(W13:W31)</f>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="Z32" s="164">
         <f>SUM(Z13:Z31)</f>
-        <v>3553</v>
+        <v>4053</v>
       </c>
       <c r="AA32" s="162">
         <f>SUM(AA13:AA31)</f>
@@ -6948,25 +6948,25 @@
         <v>65</v>
       </c>
       <c r="B2" s="19">
-        <v>371108</v>
+        <v>398091</v>
       </c>
       <c r="C2" s="18">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D2" s="18">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E2" s="16">
         <f>IFERROR((D2/C2),"")</f>
-        <v>1.5161290322580645</v>
+        <v>1.5223880597014925</v>
       </c>
       <c r="F2" s="17">
         <f>IFERROR((B2/C2),"")</f>
-        <v>5985.6129032258068</v>
+        <v>5941.6567164179105</v>
       </c>
       <c r="G2" s="17">
         <f>IFERROR((B2/D2),"")</f>
-        <v>3947.9574468085107</v>
+        <v>3902.8529411764707</v>
       </c>
       <c r="Q2" s="6" t="s">
         <v>38</v>
@@ -6980,25 +6980,25 @@
         <v>67</v>
       </c>
       <c r="B3" s="19">
-        <v>343511</v>
+        <v>387419</v>
       </c>
       <c r="C3" s="18">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D3" s="18">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="E3" s="16">
         <f t="shared" ref="E3:E20" si="0">IFERROR((D3/C3),"")</f>
-        <v>1.5192307692307692</v>
+        <v>1.5862068965517242</v>
       </c>
       <c r="F3" s="17">
         <f t="shared" ref="F3:F20" si="1">IFERROR((B3/C3),"")</f>
-        <v>6605.9807692307695</v>
+        <v>6679.6379310344828</v>
       </c>
       <c r="G3" s="17">
         <f t="shared" ref="G3:G20" si="2">IFERROR((B3/D3),"")</f>
-        <v>4348.2405063291135</v>
+        <v>4211.076086956522</v>
       </c>
       <c r="Q3" s="6" t="s">
         <v>40</v>
@@ -7012,25 +7012,25 @@
         <v>64</v>
       </c>
       <c r="B4" s="174">
-        <v>290118</v>
+        <v>303438</v>
       </c>
       <c r="C4" s="18">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D4" s="18">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E4" s="16">
         <f t="shared" si="0"/>
-        <v>1.2982456140350878</v>
+        <v>1.2666666666666666</v>
       </c>
       <c r="F4" s="17">
         <f t="shared" si="1"/>
-        <v>5089.7894736842109</v>
+        <v>5057.3</v>
       </c>
       <c r="G4" s="17">
         <f t="shared" si="2"/>
-        <v>3920.5135135135133</v>
+        <v>3992.6052631578946</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -7038,25 +7038,25 @@
         <v>66</v>
       </c>
       <c r="B5" s="175">
-        <v>323678</v>
+        <v>372695</v>
       </c>
       <c r="C5" s="18">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D5" s="18">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E5" s="16">
         <f t="shared" si="0"/>
-        <v>1.76</v>
+        <v>1.736842105263158</v>
       </c>
       <c r="F5" s="17">
         <f t="shared" si="1"/>
-        <v>6473.56</v>
+        <v>6538.5087719298244</v>
       </c>
       <c r="G5" s="17">
         <f t="shared" si="2"/>
-        <v>3678.159090909091</v>
+        <v>3764.5959595959598</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -7064,25 +7064,25 @@
         <v>68</v>
       </c>
       <c r="B6" s="19">
-        <v>222334</v>
+        <v>243467</v>
       </c>
       <c r="C6" s="18">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D6" s="18">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E6" s="16">
         <f t="shared" si="0"/>
-        <v>1.325</v>
+        <v>1.2666666666666666</v>
       </c>
       <c r="F6" s="17">
         <f t="shared" si="1"/>
-        <v>5558.35</v>
+        <v>5410.3777777777777</v>
       </c>
       <c r="G6" s="17">
         <f t="shared" si="2"/>
-        <v>4194.9811320754716</v>
+        <v>4271.3508771929828</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -7090,13 +7090,13 @@
         <v>69</v>
       </c>
       <c r="B7" s="19">
-        <v>-12578</v>
+        <v>-21204</v>
       </c>
       <c r="C7" s="18">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="D7" s="18">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="E7" s="16">
         <f t="shared" si="0"/>
@@ -7104,11 +7104,11 @@
       </c>
       <c r="F7" s="17">
         <f t="shared" si="1"/>
-        <v>3144.5</v>
+        <v>3534</v>
       </c>
       <c r="G7" s="17">
         <f t="shared" si="2"/>
-        <v>3144.5</v>
+        <v>3534</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">

--- a/EKİM SD KARNE.xlsx
+++ b/EKİM SD KARNE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\UYGULAMA İÇİN GEREKLİ DOSYALAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15A92C8-BA31-4935-8C3F-8721E6971174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2929172-3685-4CEE-8EE2-CD1BD78CE7FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2690,11 +2690,11 @@
       </c>
       <c r="B9" s="75">
         <f>I32</f>
-        <v>1683906</v>
+        <v>1711426.03</v>
       </c>
       <c r="C9" s="76">
         <f>IFERROR(B9/A9,)</f>
-        <v>0.56130199999999997</v>
+        <v>0.57047534333333338</v>
       </c>
       <c r="D9" s="168">
         <f>IFERROR(IF(B9&lt;=A9,A4,IF(AND(B9&gt;A9,B9&lt;B1),A4,IF(AND(B9&gt;=B1,B9&lt;C1),B4,IF(AND(B9&gt;=C1,B9&lt;D1),C4,IF(AND(B9&gt;=D1,B9&lt;E1),D4,IF(AND(B9&gt;=E1,B9&lt;F1),E4,IF(AND(B9&gt;=F1,B9&lt;G1),F4,IF(AND(B9&gt;=G1,B9&lt;H1),G4,IF(AND(B9&gt;=H1,B9&lt;I1),H4,IF(AND(B9&gt;=I1,B9&lt;J1),I4,IF(AND(B9&gt;=J1,B9&lt;K1),J4,IF(B9&gt;=K4,K4,K4)))))))))))),)</f>
@@ -2761,27 +2761,27 @@
       </c>
       <c r="H10" s="83">
         <f ca="1">B11-M10</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I10" s="84">
         <f>C11</f>
-        <v>4053</v>
+        <v>4159</v>
       </c>
       <c r="J10" s="85">
         <f ca="1">I10/H10</f>
-        <v>225.16666666666666</v>
+        <v>218.89473684210526</v>
       </c>
       <c r="K10" s="85">
         <f>IFERROR(I10/G10,)</f>
-        <v>810.6</v>
+        <v>831.8</v>
       </c>
       <c r="L10" s="86">
         <f ca="1">IFERROR(J10/G10,)</f>
-        <v>45.033333333333331</v>
+        <v>43.778947368421051</v>
       </c>
       <c r="M10" s="87">
         <f ca="1">(M11-A11)+B11</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N10" s="2">
         <f>LOOKUP(A9,'PRİM HAVUZU (SV SİSTEM)'!$A:$A,'PRİM HAVUZU (SV SİSTEM)'!$C:$C)*A9</f>
@@ -2804,14 +2804,14 @@
     <row r="11" spans="1:58" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="169">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B11" s="170">
         <f ca="1">(N11-M11)+1</f>
         <v>31</v>
       </c>
       <c r="C11" s="171">
-        <v>4053</v>
+        <v>4159</v>
       </c>
       <c r="F11" s="66"/>
       <c r="K11" s="89"/>
@@ -2977,39 +2977,39 @@
       </c>
       <c r="D13" s="107" cm="1">
         <f t="array" ref="D13:D31">DATA!C2:C20</f>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E13" s="107" cm="1">
         <f t="array" ref="E13:E31">DATA!D2:D20</f>
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F13" s="108">
         <f>DATA!E2</f>
-        <v>1.5223880597014925</v>
+        <v>1.5294117647058822</v>
       </c>
       <c r="G13" s="109">
         <f>DATA!F2</f>
-        <v>5941.6567164179105</v>
+        <v>5964.2188235294116</v>
       </c>
       <c r="H13" s="109">
         <f>DATA!G2</f>
-        <v>3902.8529411764707</v>
+        <v>3899.6815384615384</v>
       </c>
       <c r="I13" s="106" cm="1">
         <f t="array" ref="I13:I31">DATA!B2:B20</f>
-        <v>398091</v>
+        <v>405566.88</v>
       </c>
       <c r="J13" s="110">
         <f t="shared" ref="J13:J31" si="3">IFERROR(I13/C13,0)</f>
-        <v>0.83470693548387109</v>
+        <v>0.85038216774193554</v>
       </c>
       <c r="K13" s="111">
         <f>IFERROR(I13/$I$32,)</f>
-        <v>0.236409277002398</v>
-      </c>
-      <c r="L13" s="112" t="str">
+        <v>0.23697599130241112</v>
+      </c>
+      <c r="L13" s="112">
         <f t="shared" ref="L13:L31" si="4">IFERROR(IF(J13&lt;0.85,"",IF(AND(J13&gt;0.85,J13&lt;1),$M$2*AB13*AJ13,$M$2*AB13*AJ13)),"")</f>
-        <v/>
+        <v>7614.0386005464688</v>
       </c>
       <c r="M13" s="113">
         <f t="shared" ref="M13:M31" si="5">IFERROR((($E$9+$F$9)*AC13),"")</f>
@@ -3017,38 +3017,38 @@
       </c>
       <c r="N13" s="114">
         <f>IFERROR(IF(C13-I13&lt;0,"",C13-I13),"")</f>
-        <v>78832.076923076878</v>
+        <v>71356.196923076874</v>
       </c>
       <c r="O13" s="114">
         <f t="shared" ref="O13:O31" si="6">IFERROR(IF(N13/(W13-V13)&gt;0,N13/(W13-V13),""),"")</f>
-        <v>6064.0059171597595</v>
+        <v>5946.3497435897398</v>
       </c>
       <c r="P13" s="110">
         <f t="shared" ref="P13:P31" si="7">IFERROR(I13/C13,0)</f>
-        <v>0.83470693548387109</v>
+        <v>0.85038216774193554</v>
       </c>
       <c r="Q13" s="109">
         <f t="shared" ref="Q13:Q31" si="8">IF(V13="",0,IF(W13=V13,I13,(I13/V13)*(W13-V13)+I13))</f>
-        <v>685601.16666666674</v>
+        <v>661714.38315789471</v>
       </c>
       <c r="R13" s="115">
         <f>IFERROR(Q13/$Q$32,)</f>
-        <v>0.23244897733154324</v>
+        <v>0.23319758452899603</v>
       </c>
       <c r="S13" s="106">
         <f>IFERROR(IF(T13&lt;0.85,"",IF(AND(T13&gt;0.85,T13&lt;1),$M$2*AD13*AK13,$M$2*AD13*AK13)),"")</f>
-        <v>12803.289671421402</v>
+        <v>12844.522955857099</v>
       </c>
       <c r="T13" s="110">
         <f t="shared" ref="T13:T31" si="9">IFERROR(Q13/C13,0)</f>
-        <v>1.4375508333333336</v>
+        <v>1.3874656421052631</v>
       </c>
       <c r="U13" s="116">
         <f t="shared" ref="U13:U31" si="10">IFERROR(D13/Z13,0)</f>
-        <v>8.1736436658716452E-2</v>
+        <v>8.0889890029232747E-2</v>
       </c>
       <c r="V13" s="62">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W13" s="63">
         <v>31</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z13" s="118">
         <f t="shared" ref="Z13:Z31" si="12">(V13/$V$32)*$I$10</f>
-        <v>819.70786516853934</v>
+        <v>840.64893617021266</v>
       </c>
       <c r="AA13" s="119">
         <f t="shared" ref="AA13:AA31" si="13">IFERROR(((Y13/$Y$32)*$A$9),"")</f>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AB13" s="120">
         <f t="shared" ref="AB13:AB31" si="14">I13/$I$32</f>
-        <v>0.236409277002398</v>
+        <v>0.23697599130241112</v>
       </c>
       <c r="AC13" s="121">
         <f>AA13/$C$32</f>
@@ -3075,15 +3075,15 @@
       </c>
       <c r="AD13" s="120">
         <f>Q13/$Q$32</f>
-        <v>0.23244897733154324</v>
+        <v>0.23319758452899603</v>
       </c>
       <c r="AE13" s="120">
         <f t="shared" ref="AE13:AE31" si="15">I13/C13</f>
-        <v>0.83470693548387109</v>
+        <v>0.85038216774193554</v>
       </c>
       <c r="AF13" s="120">
         <f t="shared" ref="AF13:AF31" si="16">Q13/C13</f>
-        <v>1.4375508333333336</v>
+        <v>1.3874656421052631</v>
       </c>
       <c r="AG13" s="120">
         <f>IFERROR(VLOOKUP(A13,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3097,9 +3097,9 @@
         <f>AG13/$AG$32</f>
         <v>0.13043478260869565</v>
       </c>
-      <c r="AJ13" s="121" t="str">
+      <c r="AJ13" s="121">
         <f t="shared" ref="AJ13:AJ31" si="18">IFERROR(LOOKUP(AE13,AL:AL,AM:AM),"")</f>
-        <v/>
+        <v>0.7</v>
       </c>
       <c r="AK13" s="123">
         <f t="shared" ref="AK13:AK31" si="19">IFERROR(LOOKUP(AF13,AL:AL,AM:AM),"")</f>
@@ -3124,33 +3124,33 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D14" s="126">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E14" s="126">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F14" s="127">
         <f>DATA!E3</f>
-        <v>1.5862068965517242</v>
+        <v>1.576271186440678</v>
       </c>
       <c r="G14" s="128">
         <f>DATA!F3</f>
-        <v>6679.6379310344828</v>
+        <v>6705.0954237288133</v>
       </c>
       <c r="H14" s="128">
         <f>DATA!G3</f>
-        <v>4211.076086956522</v>
+        <v>4253.7702150537634</v>
       </c>
       <c r="I14" s="125">
-        <v>387419</v>
+        <v>395600.63</v>
       </c>
       <c r="J14" s="129">
         <f t="shared" si="3"/>
-        <v>0.60924762096774199</v>
+        <v>0.62211389395161298</v>
       </c>
       <c r="K14" s="111">
         <f t="shared" ref="K14:K31" si="21">IFERROR(I14/$I$32,)</f>
-        <v>0.23007163107679407</v>
+        <v>0.23115263123583554</v>
       </c>
       <c r="L14" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3162,38 +3162,38 @@
       </c>
       <c r="N14" s="130">
         <f t="shared" ref="N14:N31" si="22">IFERROR(IF(C14-I14&lt;0,"",C14-I14),"")</f>
-        <v>248478.43589743588</v>
+        <v>240296.80589743587</v>
       </c>
       <c r="O14" s="130">
         <f t="shared" si="6"/>
-        <v>19113.725838264298</v>
+        <v>20024.733824786323</v>
       </c>
       <c r="P14" s="129">
         <f t="shared" si="7"/>
-        <v>0.60924762096774199</v>
+        <v>0.62211389395161298</v>
       </c>
       <c r="Q14" s="109">
         <f t="shared" si="8"/>
-        <v>667221.61111111112</v>
+        <v>645453.65947368415</v>
       </c>
       <c r="R14" s="115">
         <f t="shared" ref="R14:R31" si="23">IFERROR(Q14/$Q$32,)</f>
-        <v>0.22621749888545367</v>
+        <v>0.22746707362827329</v>
       </c>
       <c r="S14" s="106">
         <f t="shared" ref="S14:S31" si="24">IFERROR(IF(T14&lt;0.85,"",IF(AND(T14&gt;0.85,T14&lt;1),$M$2*AD14*AK14,$M$2*AD14*AK14)),"")</f>
-        <v>10798.718526796018</v>
+        <v>10545.146066333122</v>
       </c>
       <c r="T14" s="129">
         <f t="shared" si="9"/>
-        <v>1.0492597916666668</v>
+        <v>1.0150279322368421</v>
       </c>
       <c r="U14" s="131">
         <f t="shared" si="10"/>
-        <v>7.0756915316500801E-2</v>
+        <v>7.0183875172422527E-2</v>
       </c>
       <c r="V14" s="62">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W14" s="64">
         <v>31</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="Z14" s="133">
         <f t="shared" si="12"/>
-        <v>819.70786516853934</v>
+        <v>840.64893617021266</v>
       </c>
       <c r="AA14" s="17">
         <f t="shared" si="13"/>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="AB14" s="134">
         <f t="shared" si="14"/>
-        <v>0.23007163107679407</v>
+        <v>0.23115263123583554</v>
       </c>
       <c r="AC14" s="135">
         <f t="shared" ref="AC14:AC31" si="25">AA14/$C$32</f>
@@ -3220,15 +3220,15 @@
       </c>
       <c r="AD14" s="134">
         <f t="shared" ref="AD14:AD18" si="26">Q14/$Q$32</f>
-        <v>0.22621749888545367</v>
+        <v>0.22746707362827329</v>
       </c>
       <c r="AE14" s="134">
         <f t="shared" si="15"/>
-        <v>0.60924762096774199</v>
+        <v>0.62211389395161298</v>
       </c>
       <c r="AF14" s="134">
         <f t="shared" si="16"/>
-        <v>1.0492597916666668</v>
+        <v>1.0150279322368421</v>
       </c>
       <c r="AG14" s="134">
         <f>IFERROR(VLOOKUP(A14,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="AK14" s="137">
         <f t="shared" si="19"/>
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AL14" s="93">
         <v>0.88</v>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="K15" s="111">
         <f t="shared" si="21"/>
-        <v>0.18019889471265024</v>
+        <v>0.1773012649573876</v>
       </c>
       <c r="L15" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="O15" s="130">
         <f t="shared" si="6"/>
-        <v>23995.893491124261</v>
+        <v>25995.551282051281</v>
       </c>
       <c r="P15" s="129">
         <f t="shared" si="7"/>
@@ -3319,26 +3319,26 @@
       </c>
       <c r="Q15" s="109">
         <f t="shared" si="8"/>
-        <v>535478.82352941181</v>
+        <v>505730</v>
       </c>
       <c r="R15" s="115">
         <f t="shared" si="23"/>
-        <v>0.1815508942571952</v>
-      </c>
-      <c r="S15" s="106">
+        <v>0.17822646360054734</v>
+      </c>
+      <c r="S15" s="106" t="str">
         <f t="shared" si="24"/>
-        <v>6166.5576743398915</v>
+        <v/>
       </c>
       <c r="T15" s="129">
         <f t="shared" si="9"/>
-        <v>0.87015308823529425</v>
+        <v>0.82181124999999999</v>
       </c>
       <c r="U15" s="131">
         <f t="shared" si="10"/>
-        <v>7.750250359211043E-2</v>
+        <v>7.5338623066442262E-2</v>
       </c>
       <c r="V15" s="62">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W15" s="64">
         <v>30</v>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="Z15" s="133">
         <f t="shared" si="12"/>
-        <v>774.16853932584263</v>
+        <v>796.40425531914889</v>
       </c>
       <c r="AA15" s="17">
         <f t="shared" si="13"/>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="AB15" s="134">
         <f t="shared" si="14"/>
-        <v>0.18019889471265024</v>
+        <v>0.1773012649573876</v>
       </c>
       <c r="AC15" s="135">
         <f t="shared" si="25"/>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="AD15" s="134">
         <f t="shared" si="26"/>
-        <v>0.1815508942571952</v>
+        <v>0.17822646360054734</v>
       </c>
       <c r="AE15" s="134">
         <f t="shared" si="15"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="AF15" s="134">
         <f t="shared" si="16"/>
-        <v>0.87015308823529425</v>
+        <v>0.82181124999999999</v>
       </c>
       <c r="AG15" s="134">
         <f>IFERROR(VLOOKUP(A15,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3391,9 +3391,9 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AK15" s="137">
+      <c r="AK15" s="137" t="str">
         <f t="shared" si="19"/>
-        <v>0.74</v>
+        <v/>
       </c>
       <c r="AL15" s="93">
         <v>0.89</v>
@@ -3414,33 +3414,33 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D16" s="126">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E16" s="126">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F16" s="127">
         <f>DATA!E5</f>
-        <v>1.736842105263158</v>
+        <v>1.7241379310344827</v>
       </c>
       <c r="G16" s="128">
         <f>DATA!F5</f>
-        <v>6538.5087719298244</v>
+        <v>6515.1093103448284</v>
       </c>
       <c r="H16" s="128">
         <f>DATA!G5</f>
-        <v>3764.5959595959598</v>
+        <v>3778.7634000000003</v>
       </c>
       <c r="I16" s="125">
-        <v>372695</v>
+        <v>377876.34</v>
       </c>
       <c r="J16" s="129">
         <f t="shared" si="3"/>
-        <v>0.58609294354838715</v>
+        <v>0.59424101854838718</v>
       </c>
       <c r="K16" s="111">
         <f t="shared" si="21"/>
-        <v>0.22132767506024684</v>
+        <v>0.22079618597363512</v>
       </c>
       <c r="L16" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3452,38 +3452,38 @@
       </c>
       <c r="N16" s="130">
         <f t="shared" ref="N16:N25" si="28">IFERROR(IF(C16-I16&lt;0,"",C16-I16),"")</f>
-        <v>263202.43589743588</v>
+        <v>258021.09589743585</v>
       </c>
       <c r="O16" s="130">
         <f t="shared" si="6"/>
-        <v>20246.341222879684</v>
+        <v>21501.757991452989</v>
       </c>
       <c r="P16" s="129">
         <f t="shared" si="7"/>
-        <v>0.58609294354838715</v>
+        <v>0.59424101854838718</v>
       </c>
       <c r="Q16" s="109">
         <f t="shared" si="8"/>
-        <v>641863.61111111112</v>
+        <v>616535.08105263161</v>
       </c>
       <c r="R16" s="115">
         <f t="shared" si="23"/>
-        <v>0.21762002056459326</v>
+        <v>0.21727575422001336</v>
       </c>
       <c r="S16" s="106">
         <f t="shared" si="24"/>
-        <v>9988.7589439148305</v>
+        <v>9175.1205492027239</v>
       </c>
       <c r="T16" s="129">
         <f t="shared" si="9"/>
-        <v>1.0093822916666668</v>
+        <v>0.96955113552631589</v>
       </c>
       <c r="U16" s="131">
         <f t="shared" si="10"/>
-        <v>6.953696850069907E-2</v>
+        <v>6.8994317966110288E-2</v>
       </c>
       <c r="V16" s="62">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W16" s="64">
         <v>31</v>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="Z16" s="133">
         <f t="shared" si="12"/>
-        <v>819.70786516853934</v>
+        <v>840.64893617021266</v>
       </c>
       <c r="AA16" s="17">
         <f t="shared" si="13"/>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="AB16" s="134">
         <f t="shared" si="14"/>
-        <v>0.22132767506024684</v>
+        <v>0.22079618597363512</v>
       </c>
       <c r="AC16" s="135">
         <f t="shared" si="25"/>
@@ -3510,15 +3510,15 @@
       </c>
       <c r="AD16" s="134">
         <f t="shared" si="26"/>
-        <v>0.21762002056459326</v>
+        <v>0.21727575422001336</v>
       </c>
       <c r="AE16" s="134">
         <f t="shared" si="15"/>
-        <v>0.58609294354838715</v>
+        <v>0.59424101854838718</v>
       </c>
       <c r="AF16" s="134">
         <f t="shared" si="16"/>
-        <v>1.0093822916666668</v>
+        <v>0.96955113552631589</v>
       </c>
       <c r="AG16" s="134">
         <f>IFERROR(VLOOKUP(A16,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3538,7 +3538,7 @@
       </c>
       <c r="AK16" s="137">
         <f t="shared" si="19"/>
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AL16" s="93">
         <v>0.9</v>
@@ -3559,33 +3559,33 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D17" s="126">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E17" s="126">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F17" s="127">
         <f>DATA!E6</f>
-        <v>1.2666666666666666</v>
+        <v>1.2826086956521738</v>
       </c>
       <c r="G17" s="128">
         <f>DATA!F6</f>
-        <v>5410.3777777777777</v>
+        <v>5438.003913043478</v>
       </c>
       <c r="H17" s="128">
         <f>DATA!G6</f>
-        <v>4271.3508771929828</v>
+        <v>4239.7996610169494</v>
       </c>
       <c r="I17" s="125">
-        <v>243467</v>
+        <v>250148.18</v>
       </c>
       <c r="J17" s="129">
         <f t="shared" si="3"/>
-        <v>0.38287149193548387</v>
+        <v>0.39337818629032256</v>
       </c>
       <c r="K17" s="111">
         <f t="shared" si="21"/>
-        <v>0.14458467396636154</v>
+        <v>0.14616359434476989</v>
       </c>
       <c r="L17" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3597,23 +3597,23 @@
       </c>
       <c r="N17" s="130">
         <f t="shared" si="28"/>
-        <v>392430.43589743588</v>
+        <v>385749.25589743588</v>
       </c>
       <c r="O17" s="130">
         <f t="shared" si="6"/>
-        <v>30186.956607495067</v>
+        <v>32145.771324786325</v>
       </c>
       <c r="P17" s="129">
         <f t="shared" si="7"/>
-        <v>0.38287149193548387</v>
+        <v>0.39337818629032256</v>
       </c>
       <c r="Q17" s="109">
         <f t="shared" si="8"/>
-        <v>419304.27777777775</v>
+        <v>408136.5042105263</v>
       </c>
       <c r="R17" s="115">
         <f t="shared" si="23"/>
-        <v>0.14216260896121446</v>
+        <v>0.14383312402216994</v>
       </c>
       <c r="S17" s="106" t="str">
         <f t="shared" si="24"/>
@@ -3621,14 +3621,14 @@
       </c>
       <c r="T17" s="129">
         <f t="shared" si="9"/>
-        <v>0.65938979166666667</v>
+        <v>0.64182756710526312</v>
       </c>
       <c r="U17" s="131">
         <f t="shared" si="10"/>
-        <v>5.4897606711078212E-2</v>
+        <v>5.4719631490363331E-2</v>
       </c>
       <c r="V17" s="62">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W17" s="64">
         <v>31</v>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="Z17" s="133">
         <f t="shared" si="12"/>
-        <v>819.70786516853934</v>
+        <v>840.64893617021266</v>
       </c>
       <c r="AA17" s="17">
         <f t="shared" si="13"/>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="AB17" s="134">
         <f t="shared" si="14"/>
-        <v>0.14458467396636154</v>
+        <v>0.14616359434476989</v>
       </c>
       <c r="AC17" s="135">
         <f t="shared" si="25"/>
@@ -3655,15 +3655,15 @@
       </c>
       <c r="AD17" s="134">
         <f t="shared" si="26"/>
-        <v>0.14216260896121446</v>
+        <v>0.14383312402216994</v>
       </c>
       <c r="AE17" s="134">
         <f t="shared" si="15"/>
-        <v>0.38287149193548387</v>
+        <v>0.39337818629032256</v>
       </c>
       <c r="AF17" s="134">
         <f t="shared" si="16"/>
-        <v>0.65938979166666667</v>
+        <v>0.64182756710526312</v>
       </c>
       <c r="AG17" s="134">
         <f>IFERROR(VLOOKUP(A17,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="K18" s="111">
         <f t="shared" si="21"/>
-        <v>-1.2592151818450673E-2</v>
+        <v>-1.2389667814039267E-2</v>
       </c>
       <c r="L18" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="AB18" s="138">
         <f t="shared" si="14"/>
-        <v>-1.2592151818450673E-2</v>
+        <v>-1.2389667814039267E-2</v>
       </c>
       <c r="AC18" s="135">
         <f t="shared" si="25"/>
@@ -5699,31 +5699,31 @@
       </c>
       <c r="D32" s="153">
         <f>SUM(D13:D31)</f>
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E32" s="153">
         <f>SUM(E13:E31)</f>
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="F32" s="154">
         <f>IFERROR(SUM(F13:F31)/G10,)</f>
-        <v>1.6757540789699412</v>
+        <v>1.6758192488999768</v>
       </c>
       <c r="G32" s="155">
         <f>IFERROR(SUM(G13:G31)/G10,)</f>
-        <v>6632.2962394319984</v>
+        <v>6642.7454941293063</v>
       </c>
       <c r="H32" s="155">
         <f>IFERROR(SUM(H13:H31)/G10,)</f>
-        <v>4735.2962256159663</v>
+        <v>4739.7240155380296</v>
       </c>
       <c r="I32" s="155">
         <f>SUM(I13:I31)</f>
-        <v>1683906</v>
+        <v>1711426.03</v>
       </c>
       <c r="J32" s="156">
         <f>IFERROR(I32/C32,)</f>
-        <v>0.56130199999999997</v>
+        <v>0.57047534333333338</v>
       </c>
       <c r="K32" s="156">
         <f>SUM(K13:K31)</f>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="L32" s="155">
         <f>SUM(L13:L31)</f>
-        <v>0</v>
+        <v>7614.0386005464688</v>
       </c>
       <c r="M32" s="155">
         <f>SUM(M13:M31)</f>
@@ -5739,16 +5739,16 @@
       </c>
       <c r="N32" s="155">
         <f>SUM(N13:N31)</f>
-        <v>1316094</v>
+        <v>1288573.9699999997</v>
       </c>
       <c r="O32" s="155">
         <f>SUM(O13:O31)</f>
-        <v>99606.923076923078</v>
+        <v>105614.16416666667</v>
       </c>
       <c r="P32" s="157"/>
       <c r="Q32" s="152">
         <f>SUM(Q13:Q31)</f>
-        <v>2949469.490196079</v>
+        <v>2837569.6278947368</v>
       </c>
       <c r="R32" s="156">
         <f>SUM(R13:R31)</f>
@@ -5756,16 +5756,16 @@
       </c>
       <c r="S32" s="155">
         <f>SUM(S13:S31)</f>
-        <v>39757.324816472144</v>
+        <v>32564.789571392947</v>
       </c>
       <c r="T32" s="158">
         <f>IFERROR(Q32/C32,)</f>
-        <v>0.98315649673202632</v>
+        <v>0.94585654263157892</v>
       </c>
       <c r="U32" s="165"/>
       <c r="V32" s="166">
         <f>SUM(V13:V31)</f>
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="W32" s="167">
         <f>SUM(W13:W31)</f>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="Z32" s="164">
         <f>SUM(Z13:Z31)</f>
-        <v>4053</v>
+        <v>4158.9999999999991</v>
       </c>
       <c r="AA32" s="162">
         <f>SUM(AA13:AA31)</f>
@@ -6948,25 +6948,25 @@
         <v>65</v>
       </c>
       <c r="B2" s="19">
-        <v>398091</v>
+        <v>405566.88</v>
       </c>
       <c r="C2" s="18">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D2" s="18">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E2" s="16">
         <f>IFERROR((D2/C2),"")</f>
-        <v>1.5223880597014925</v>
+        <v>1.5294117647058822</v>
       </c>
       <c r="F2" s="17">
         <f>IFERROR((B2/C2),"")</f>
-        <v>5941.6567164179105</v>
+        <v>5964.2188235294116</v>
       </c>
       <c r="G2" s="17">
         <f>IFERROR((B2/D2),"")</f>
-        <v>3902.8529411764707</v>
+        <v>3899.6815384615384</v>
       </c>
       <c r="Q2" s="6" t="s">
         <v>38</v>
@@ -6980,25 +6980,25 @@
         <v>67</v>
       </c>
       <c r="B3" s="19">
-        <v>387419</v>
+        <v>395600.63</v>
       </c>
       <c r="C3" s="18">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D3" s="18">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E3" s="16">
         <f t="shared" ref="E3:E20" si="0">IFERROR((D3/C3),"")</f>
-        <v>1.5862068965517242</v>
+        <v>1.576271186440678</v>
       </c>
       <c r="F3" s="17">
         <f t="shared" ref="F3:F20" si="1">IFERROR((B3/C3),"")</f>
-        <v>6679.6379310344828</v>
+        <v>6705.0954237288133</v>
       </c>
       <c r="G3" s="17">
         <f t="shared" ref="G3:G20" si="2">IFERROR((B3/D3),"")</f>
-        <v>4211.076086956522</v>
+        <v>4253.7702150537634</v>
       </c>
       <c r="Q3" s="6" t="s">
         <v>40</v>
@@ -7038,25 +7038,25 @@
         <v>66</v>
       </c>
       <c r="B5" s="175">
-        <v>372695</v>
+        <v>377876.34</v>
       </c>
       <c r="C5" s="18">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D5" s="18">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E5" s="16">
         <f t="shared" si="0"/>
-        <v>1.736842105263158</v>
+        <v>1.7241379310344827</v>
       </c>
       <c r="F5" s="17">
         <f t="shared" si="1"/>
-        <v>6538.5087719298244</v>
+        <v>6515.1093103448284</v>
       </c>
       <c r="G5" s="17">
         <f t="shared" si="2"/>
-        <v>3764.5959595959598</v>
+        <v>3778.7634000000003</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -7064,25 +7064,25 @@
         <v>68</v>
       </c>
       <c r="B6" s="19">
-        <v>243467</v>
+        <v>250148.18</v>
       </c>
       <c r="C6" s="18">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D6" s="18">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E6" s="16">
         <f t="shared" si="0"/>
-        <v>1.2666666666666666</v>
+        <v>1.2826086956521738</v>
       </c>
       <c r="F6" s="17">
         <f t="shared" si="1"/>
-        <v>5410.3777777777777</v>
+        <v>5438.003913043478</v>
       </c>
       <c r="G6" s="17">
         <f t="shared" si="2"/>
-        <v>4271.3508771929828</v>
+        <v>4239.7996610169494</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">

--- a/EKİM SD KARNE.xlsx
+++ b/EKİM SD KARNE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\UYGULAMA İÇİN GEREKLİ DOSYALAR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2929172-3685-4CEE-8EE2-CD1BD78CE7FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60970DBA-0DE2-4370-8999-7E9503A82067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2690,11 +2690,11 @@
       </c>
       <c r="B9" s="75">
         <f>I32</f>
-        <v>1711426.03</v>
+        <v>1760781.4599999997</v>
       </c>
       <c r="C9" s="76">
         <f>IFERROR(B9/A9,)</f>
-        <v>0.57047534333333338</v>
+        <v>0.58692715333333323</v>
       </c>
       <c r="D9" s="168">
         <f>IFERROR(IF(B9&lt;=A9,A4,IF(AND(B9&gt;A9,B9&lt;B1),A4,IF(AND(B9&gt;=B1,B9&lt;C1),B4,IF(AND(B9&gt;=C1,B9&lt;D1),C4,IF(AND(B9&gt;=D1,B9&lt;E1),D4,IF(AND(B9&gt;=E1,B9&lt;F1),E4,IF(AND(B9&gt;=F1,B9&lt;G1),F4,IF(AND(B9&gt;=G1,B9&lt;H1),G4,IF(AND(B9&gt;=H1,B9&lt;I1),H4,IF(AND(B9&gt;=I1,B9&lt;J1),I4,IF(AND(B9&gt;=J1,B9&lt;K1),J4,IF(B9&gt;=K4,K4,K4)))))))))))),)</f>
@@ -2761,27 +2761,27 @@
       </c>
       <c r="H10" s="83">
         <f ca="1">B11-M10</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I10" s="84">
         <f>C11</f>
-        <v>4159</v>
+        <v>4257</v>
       </c>
       <c r="J10" s="85">
         <f ca="1">I10/H10</f>
-        <v>218.89473684210526</v>
+        <v>212.85</v>
       </c>
       <c r="K10" s="85">
         <f>IFERROR(I10/G10,)</f>
-        <v>831.8</v>
+        <v>851.4</v>
       </c>
       <c r="L10" s="86">
         <f ca="1">IFERROR(J10/G10,)</f>
-        <v>43.778947368421051</v>
+        <v>42.57</v>
       </c>
       <c r="M10" s="87">
         <f ca="1">(M11-A11)+B11</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N10" s="2">
         <f>LOOKUP(A9,'PRİM HAVUZU (SV SİSTEM)'!$A:$A,'PRİM HAVUZU (SV SİSTEM)'!$C:$C)*A9</f>
@@ -2804,14 +2804,14 @@
     <row r="11" spans="1:58" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="169">
         <f ca="1">TODAY()</f>
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B11" s="170">
         <f ca="1">(N11-M11)+1</f>
         <v>31</v>
       </c>
       <c r="C11" s="171">
-        <v>4159</v>
+        <v>4257</v>
       </c>
       <c r="F11" s="66"/>
       <c r="K11" s="89"/>
@@ -3005,11 +3005,11 @@
       </c>
       <c r="K13" s="111">
         <f>IFERROR(I13/$I$32,)</f>
-        <v>0.23697599130241112</v>
+        <v>0.230333456600571</v>
       </c>
       <c r="L13" s="112">
         <f t="shared" ref="L13:L31" si="4">IFERROR(IF(J13&lt;0.85,"",IF(AND(J13&gt;0.85,J13&lt;1),$M$2*AB13*AJ13,$M$2*AB13*AJ13)),"")</f>
-        <v>7614.0386005464688</v>
+        <v>7400.6139605763465</v>
       </c>
       <c r="M13" s="113">
         <f t="shared" ref="M13:M31" si="5">IFERROR((($E$9+$F$9)*AC13),"")</f>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O13" s="114">
         <f t="shared" ref="O13:O31" si="6">IFERROR(IF(N13/(W13-V13)&gt;0,N13/(W13-V13),""),"")</f>
-        <v>5946.3497435897398</v>
+        <v>6486.9269930069886</v>
       </c>
       <c r="P13" s="110">
         <f t="shared" ref="P13:P31" si="7">IFERROR(I13/C13,0)</f>
@@ -3029,26 +3029,26 @@
       </c>
       <c r="Q13" s="109">
         <f t="shared" ref="Q13:Q31" si="8">IF(V13="",0,IF(W13=V13,I13,(I13/V13)*(W13-V13)+I13))</f>
-        <v>661714.38315789471</v>
+        <v>628628.66399999999</v>
       </c>
       <c r="R13" s="115">
         <f>IFERROR(Q13/$Q$32,)</f>
-        <v>0.23319758452899603</v>
+        <v>0.22682168250540327</v>
       </c>
       <c r="S13" s="106">
         <f>IFERROR(IF(T13&lt;0.85,"",IF(AND(T13&gt;0.85,T13&lt;1),$M$2*AD13*AK13,$M$2*AD13*AK13)),"")</f>
-        <v>12844.522955857099</v>
+        <v>12493.338272397612</v>
       </c>
       <c r="T13" s="110">
         <f t="shared" ref="T13:T31" si="9">IFERROR(Q13/C13,0)</f>
-        <v>1.3874656421052631</v>
+        <v>1.3180923600000001</v>
       </c>
       <c r="U13" s="116">
         <f t="shared" ref="U13:U31" si="10">IFERROR(D13/Z13,0)</f>
-        <v>8.0889890029232747E-2</v>
+        <v>7.9069767441860464E-2</v>
       </c>
       <c r="V13" s="62">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W13" s="63">
         <v>31</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z13" s="118">
         <f t="shared" ref="Z13:Z31" si="12">(V13/$V$32)*$I$10</f>
-        <v>840.64893617021266</v>
+        <v>860</v>
       </c>
       <c r="AA13" s="119">
         <f t="shared" ref="AA13:AA31" si="13">IFERROR(((Y13/$Y$32)*$A$9),"")</f>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AB13" s="120">
         <f t="shared" ref="AB13:AB31" si="14">I13/$I$32</f>
-        <v>0.23697599130241112</v>
+        <v>0.230333456600571</v>
       </c>
       <c r="AC13" s="121">
         <f>AA13/$C$32</f>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AD13" s="120">
         <f>Q13/$Q$32</f>
-        <v>0.23319758452899603</v>
+        <v>0.22682168250540327</v>
       </c>
       <c r="AE13" s="120">
         <f t="shared" ref="AE13:AE31" si="15">I13/C13</f>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AF13" s="120">
         <f t="shared" ref="AF13:AF31" si="16">Q13/C13</f>
-        <v>1.3874656421052631</v>
+        <v>1.3180923600000001</v>
       </c>
       <c r="AG13" s="120">
         <f>IFERROR(VLOOKUP(A13,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3124,33 +3124,33 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D14" s="126">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E14" s="126">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F14" s="127">
         <f>DATA!E3</f>
-        <v>1.576271186440678</v>
+        <v>1.5833333333333333</v>
       </c>
       <c r="G14" s="128">
         <f>DATA!F3</f>
-        <v>6705.0954237288133</v>
+        <v>6742.559666666667</v>
       </c>
       <c r="H14" s="128">
         <f>DATA!G3</f>
-        <v>4253.7702150537634</v>
+        <v>4258.4587368421053</v>
       </c>
       <c r="I14" s="125">
-        <v>395600.63</v>
+        <v>404553.58</v>
       </c>
       <c r="J14" s="129">
         <f t="shared" si="3"/>
-        <v>0.62211389395161298</v>
+        <v>0.63619312983870968</v>
       </c>
       <c r="K14" s="111">
         <f t="shared" ref="K14:K31" si="21">IFERROR(I14/$I$32,)</f>
-        <v>0.23115263123583554</v>
+        <v>0.22975797348525018</v>
       </c>
       <c r="L14" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3162,38 +3162,38 @@
       </c>
       <c r="N14" s="130">
         <f t="shared" ref="N14:N31" si="22">IFERROR(IF(C14-I14&lt;0,"",C14-I14),"")</f>
-        <v>240296.80589743587</v>
+        <v>231343.85589743586</v>
       </c>
       <c r="O14" s="130">
         <f t="shared" si="6"/>
-        <v>20024.733824786323</v>
+        <v>21031.259627039624</v>
       </c>
       <c r="P14" s="129">
         <f t="shared" si="7"/>
-        <v>0.62211389395161298</v>
+        <v>0.63619312983870968</v>
       </c>
       <c r="Q14" s="109">
         <f t="shared" si="8"/>
-        <v>645453.65947368415</v>
+        <v>627058.049</v>
       </c>
       <c r="R14" s="115">
         <f t="shared" ref="R14:R31" si="23">IFERROR(Q14/$Q$32,)</f>
-        <v>0.22746707362827329</v>
+        <v>0.22625497348103046</v>
       </c>
       <c r="S14" s="106">
         <f t="shared" ref="S14:S31" si="24">IFERROR(IF(T14&lt;0.85,"",IF(AND(T14&gt;0.85,T14&lt;1),$M$2*AD14*AK14,$M$2*AD14*AK14)),"")</f>
-        <v>10545.146066333122</v>
+        <v>9969.6991514681267</v>
       </c>
       <c r="T14" s="129">
         <f t="shared" si="9"/>
-        <v>1.0150279322368421</v>
+        <v>0.98609935125000003</v>
       </c>
       <c r="U14" s="131">
         <f t="shared" si="10"/>
-        <v>7.0183875172422527E-2</v>
+        <v>6.9767441860465115E-2</v>
       </c>
       <c r="V14" s="62">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W14" s="64">
         <v>31</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="Z14" s="133">
         <f t="shared" si="12"/>
-        <v>840.64893617021266</v>
+        <v>860</v>
       </c>
       <c r="AA14" s="17">
         <f t="shared" si="13"/>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="AB14" s="134">
         <f t="shared" si="14"/>
-        <v>0.23115263123583554</v>
+        <v>0.22975797348525018</v>
       </c>
       <c r="AC14" s="135">
         <f t="shared" ref="AC14:AC31" si="25">AA14/$C$32</f>
@@ -3220,15 +3220,15 @@
       </c>
       <c r="AD14" s="134">
         <f t="shared" ref="AD14:AD18" si="26">Q14/$Q$32</f>
-        <v>0.22746707362827329</v>
+        <v>0.22625497348103046</v>
       </c>
       <c r="AE14" s="134">
         <f t="shared" si="15"/>
-        <v>0.62211389395161298</v>
+        <v>0.63619312983870968</v>
       </c>
       <c r="AF14" s="134">
         <f t="shared" si="16"/>
-        <v>1.0150279322368421</v>
+        <v>0.98609935125000003</v>
       </c>
       <c r="AG14" s="134">
         <f>IFERROR(VLOOKUP(A14,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="AK14" s="137">
         <f t="shared" si="19"/>
-        <v>1.01</v>
+        <v>0.96</v>
       </c>
       <c r="AL14" s="93">
         <v>0.88</v>
@@ -3269,33 +3269,33 @@
         <v>615384.61538461538</v>
       </c>
       <c r="D15" s="126">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E15" s="126">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F15" s="127">
         <f>DATA!E4</f>
-        <v>1.2666666666666666</v>
+        <v>1.2698412698412698</v>
       </c>
       <c r="G15" s="128">
         <f>DATA!F4</f>
-        <v>5057.3</v>
+        <v>5148.315873015873</v>
       </c>
       <c r="H15" s="128">
         <f>DATA!G4</f>
-        <v>3992.6052631578946</v>
+        <v>4054.2987500000004</v>
       </c>
       <c r="I15" s="125">
-        <v>303438</v>
+        <v>324343.90000000002</v>
       </c>
       <c r="J15" s="129">
         <f t="shared" si="3"/>
-        <v>0.49308675000000002</v>
+        <v>0.52705883750000004</v>
       </c>
       <c r="K15" s="111">
         <f t="shared" si="21"/>
-        <v>0.1773012649573876</v>
+        <v>0.18420451791899267</v>
       </c>
       <c r="L15" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3307,23 +3307,23 @@
       </c>
       <c r="N15" s="130">
         <f t="shared" si="22"/>
-        <v>311946.61538461538</v>
+        <v>291040.71538461535</v>
       </c>
       <c r="O15" s="130">
         <f t="shared" si="6"/>
-        <v>25995.551282051281</v>
+        <v>26458.246853146851</v>
       </c>
       <c r="P15" s="129">
         <f t="shared" si="7"/>
-        <v>0.49308675000000002</v>
+        <v>0.52705883750000004</v>
       </c>
       <c r="Q15" s="109">
         <f t="shared" si="8"/>
-        <v>505730</v>
+        <v>512121.94736842107</v>
       </c>
       <c r="R15" s="115">
         <f t="shared" si="23"/>
-        <v>0.17822646360054734</v>
+        <v>0.18478374977512774</v>
       </c>
       <c r="S15" s="106" t="str">
         <f t="shared" si="24"/>
@@ -3331,14 +3331,14 @@
       </c>
       <c r="T15" s="129">
         <f t="shared" si="9"/>
-        <v>0.82181124999999999</v>
+        <v>0.83219816447368422</v>
       </c>
       <c r="U15" s="131">
         <f t="shared" si="10"/>
-        <v>7.5338623066442262E-2</v>
+        <v>7.711138310893513E-2</v>
       </c>
       <c r="V15" s="62">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W15" s="64">
         <v>30</v>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="Z15" s="133">
         <f t="shared" si="12"/>
-        <v>796.40425531914889</v>
+        <v>817</v>
       </c>
       <c r="AA15" s="17">
         <f t="shared" si="13"/>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="AB15" s="134">
         <f t="shared" si="14"/>
-        <v>0.1773012649573876</v>
+        <v>0.18420451791899267</v>
       </c>
       <c r="AC15" s="135">
         <f t="shared" si="25"/>
@@ -3365,15 +3365,15 @@
       </c>
       <c r="AD15" s="134">
         <f t="shared" si="26"/>
-        <v>0.17822646360054734</v>
+        <v>0.18478374977512774</v>
       </c>
       <c r="AE15" s="134">
         <f t="shared" si="15"/>
-        <v>0.49308675000000002</v>
+        <v>0.52705883750000004</v>
       </c>
       <c r="AF15" s="134">
         <f t="shared" si="16"/>
-        <v>0.82181124999999999</v>
+        <v>0.83219816447368422</v>
       </c>
       <c r="AG15" s="134">
         <f>IFERROR(VLOOKUP(A15,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3414,33 +3414,33 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D16" s="126">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E16" s="126">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F16" s="127">
         <f>DATA!E5</f>
-        <v>1.7241379310344827</v>
+        <v>1.6935483870967742</v>
       </c>
       <c r="G16" s="128">
         <f>DATA!F5</f>
-        <v>6515.1093103448284</v>
+        <v>6409.2406451612896</v>
       </c>
       <c r="H16" s="128">
         <f>DATA!G5</f>
-        <v>3778.7634000000003</v>
+        <v>3784.5039999999999</v>
       </c>
       <c r="I16" s="125">
-        <v>377876.34</v>
+        <v>397372.92</v>
       </c>
       <c r="J16" s="129">
         <f t="shared" si="3"/>
-        <v>0.59424101854838718</v>
+        <v>0.62490096290322583</v>
       </c>
       <c r="K16" s="111">
         <f t="shared" si="21"/>
-        <v>0.22079618597363512</v>
+        <v>0.22567986375776586</v>
       </c>
       <c r="L16" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3452,38 +3452,38 @@
       </c>
       <c r="N16" s="130">
         <f t="shared" ref="N16:N25" si="28">IFERROR(IF(C16-I16&lt;0,"",C16-I16),"")</f>
-        <v>258021.09589743585</v>
+        <v>238524.51589743589</v>
       </c>
       <c r="O16" s="130">
         <f t="shared" si="6"/>
-        <v>21501.757991452989</v>
+        <v>21684.046899766898</v>
       </c>
       <c r="P16" s="129">
         <f t="shared" si="7"/>
-        <v>0.59424101854838718</v>
+        <v>0.62490096290322583</v>
       </c>
       <c r="Q16" s="109">
         <f t="shared" si="8"/>
-        <v>616535.08105263161</v>
+        <v>615928.02599999995</v>
       </c>
       <c r="R16" s="115">
         <f t="shared" si="23"/>
-        <v>0.21727575422001336</v>
+        <v>0.22223904056584948</v>
       </c>
       <c r="S16" s="106">
         <f t="shared" si="24"/>
-        <v>9175.1205492027239</v>
+        <v>9384.7102050146914</v>
       </c>
       <c r="T16" s="129">
         <f t="shared" si="9"/>
-        <v>0.96955113552631589</v>
+        <v>0.96859649249999991</v>
       </c>
       <c r="U16" s="131">
         <f t="shared" si="10"/>
-        <v>6.8994317966110288E-2</v>
+        <v>7.2093023255813959E-2</v>
       </c>
       <c r="V16" s="62">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W16" s="64">
         <v>31</v>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="Z16" s="133">
         <f t="shared" si="12"/>
-        <v>840.64893617021266</v>
+        <v>860</v>
       </c>
       <c r="AA16" s="17">
         <f t="shared" si="13"/>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="AB16" s="134">
         <f t="shared" si="14"/>
-        <v>0.22079618597363512</v>
+        <v>0.22567986375776586</v>
       </c>
       <c r="AC16" s="135">
         <f t="shared" si="25"/>
@@ -3510,15 +3510,15 @@
       </c>
       <c r="AD16" s="134">
         <f t="shared" si="26"/>
-        <v>0.21727575422001336</v>
+        <v>0.22223904056584948</v>
       </c>
       <c r="AE16" s="134">
         <f t="shared" si="15"/>
-        <v>0.59424101854838718</v>
+        <v>0.62490096290322583</v>
       </c>
       <c r="AF16" s="134">
         <f t="shared" si="16"/>
-        <v>0.96955113552631589</v>
+        <v>0.96859649249999991</v>
       </c>
       <c r="AG16" s="134">
         <f>IFERROR(VLOOKUP(A16,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3559,18 +3559,18 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D17" s="126">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E17" s="126">
         <v>59</v>
       </c>
       <c r="F17" s="127">
         <f>DATA!E6</f>
-        <v>1.2826086956521738</v>
+        <v>1.2291666666666667</v>
       </c>
       <c r="G17" s="128">
         <f>DATA!F6</f>
-        <v>5438.003913043478</v>
+        <v>5211.4204166666668</v>
       </c>
       <c r="H17" s="128">
         <f>DATA!G6</f>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="K17" s="111">
         <f t="shared" si="21"/>
-        <v>0.14616359434476989</v>
+        <v>0.14206656855644087</v>
       </c>
       <c r="L17" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="O17" s="130">
         <f t="shared" si="6"/>
-        <v>32145.771324786325</v>
+        <v>35068.11417249417</v>
       </c>
       <c r="P17" s="129">
         <f t="shared" si="7"/>
@@ -3609,11 +3609,11 @@
       </c>
       <c r="Q17" s="109">
         <f t="shared" si="8"/>
-        <v>408136.5042105263</v>
+        <v>387729.679</v>
       </c>
       <c r="R17" s="115">
         <f t="shared" si="23"/>
-        <v>0.14383312402216994</v>
+        <v>0.13990055367258902</v>
       </c>
       <c r="S17" s="106" t="str">
         <f t="shared" si="24"/>
@@ -3621,14 +3621,14 @@
       </c>
       <c r="T17" s="129">
         <f t="shared" si="9"/>
-        <v>0.64182756710526312</v>
+        <v>0.60973618875000002</v>
       </c>
       <c r="U17" s="131">
         <f t="shared" si="10"/>
-        <v>5.4719631490363331E-2</v>
+        <v>5.5813953488372092E-2</v>
       </c>
       <c r="V17" s="62">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W17" s="64">
         <v>31</v>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="Z17" s="133">
         <f t="shared" si="12"/>
-        <v>840.64893617021266</v>
+        <v>860</v>
       </c>
       <c r="AA17" s="17">
         <f t="shared" si="13"/>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="AB17" s="134">
         <f t="shared" si="14"/>
-        <v>0.14616359434476989</v>
+        <v>0.14206656855644087</v>
       </c>
       <c r="AC17" s="135">
         <f t="shared" si="25"/>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="AD17" s="134">
         <f t="shared" si="26"/>
-        <v>0.14383312402216994</v>
+        <v>0.13990055367258902</v>
       </c>
       <c r="AE17" s="134">
         <f t="shared" si="15"/>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="AF17" s="134">
         <f t="shared" si="16"/>
-        <v>0.64182756710526312</v>
+        <v>0.60973618875000002</v>
       </c>
       <c r="AG17" s="134">
         <f>IFERROR(VLOOKUP(A17,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="K18" s="111">
         <f t="shared" si="21"/>
-        <v>-1.2389667814039267E-2</v>
+        <v>-1.2042380319020399E-2</v>
       </c>
       <c r="L18" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="AB18" s="138">
         <f t="shared" si="14"/>
-        <v>-1.2389667814039267E-2</v>
+        <v>-1.2042380319020399E-2</v>
       </c>
       <c r="AC18" s="135">
         <f t="shared" si="25"/>
@@ -5699,31 +5699,31 @@
       </c>
       <c r="D32" s="153">
         <f>SUM(D13:D31)</f>
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="E32" s="153">
         <f>SUM(E13:E31)</f>
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="F32" s="154">
         <f>IFERROR(SUM(F13:F31)/G10,)</f>
-        <v>1.6758192488999768</v>
+        <v>1.6610602843287849</v>
       </c>
       <c r="G32" s="155">
         <f>IFERROR(SUM(G13:G31)/G10,)</f>
-        <v>6642.7454941293063</v>
+        <v>6601.9510850079823</v>
       </c>
       <c r="H32" s="155">
         <f>IFERROR(SUM(H13:H31)/G10,)</f>
-        <v>4739.7240155380296</v>
+        <v>4754.1485372641191</v>
       </c>
       <c r="I32" s="155">
         <f>SUM(I13:I31)</f>
-        <v>1711426.03</v>
+        <v>1760781.4599999997</v>
       </c>
       <c r="J32" s="156">
         <f>IFERROR(I32/C32,)</f>
-        <v>0.57047534333333338</v>
+        <v>0.58692715333333323</v>
       </c>
       <c r="K32" s="156">
         <f>SUM(K13:K31)</f>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="L32" s="155">
         <f>SUM(L13:L31)</f>
-        <v>7614.0386005464688</v>
+        <v>7400.6139605763465</v>
       </c>
       <c r="M32" s="155">
         <f>SUM(M13:M31)</f>
@@ -5739,33 +5739,33 @@
       </c>
       <c r="N32" s="155">
         <f>SUM(N13:N31)</f>
-        <v>1288573.9699999997</v>
+        <v>1239218.5399999998</v>
       </c>
       <c r="O32" s="155">
         <f>SUM(O13:O31)</f>
-        <v>105614.16416666667</v>
+        <v>110728.59454545453</v>
       </c>
       <c r="P32" s="157"/>
       <c r="Q32" s="152">
         <f>SUM(Q13:Q31)</f>
-        <v>2837569.6278947368</v>
+        <v>2771466.3653684212</v>
       </c>
       <c r="R32" s="156">
         <f>SUM(R13:R31)</f>
-        <v>0.99999999999999989</v>
+        <v>1</v>
       </c>
       <c r="S32" s="155">
         <f>SUM(S13:S31)</f>
-        <v>32564.789571392947</v>
+        <v>31847.747628880432</v>
       </c>
       <c r="T32" s="158">
         <f>IFERROR(Q32/C32,)</f>
-        <v>0.94585654263157892</v>
+        <v>0.92382212178947376</v>
       </c>
       <c r="U32" s="165"/>
       <c r="V32" s="166">
         <f>SUM(V13:V31)</f>
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="W32" s="167">
         <f>SUM(W13:W31)</f>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="Z32" s="164">
         <f>SUM(Z13:Z31)</f>
-        <v>4158.9999999999991</v>
+        <v>4257</v>
       </c>
       <c r="AA32" s="162">
         <f>SUM(AA13:AA31)</f>
@@ -6980,25 +6980,25 @@
         <v>67</v>
       </c>
       <c r="B3" s="19">
-        <v>395600.63</v>
+        <v>404553.58</v>
       </c>
       <c r="C3" s="18">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D3" s="18">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E3" s="16">
         <f t="shared" ref="E3:E20" si="0">IFERROR((D3/C3),"")</f>
-        <v>1.576271186440678</v>
+        <v>1.5833333333333333</v>
       </c>
       <c r="F3" s="17">
         <f t="shared" ref="F3:F20" si="1">IFERROR((B3/C3),"")</f>
-        <v>6705.0954237288133</v>
+        <v>6742.559666666667</v>
       </c>
       <c r="G3" s="17">
         <f t="shared" ref="G3:G20" si="2">IFERROR((B3/D3),"")</f>
-        <v>4253.7702150537634</v>
+        <v>4258.4587368421053</v>
       </c>
       <c r="Q3" s="6" t="s">
         <v>40</v>
@@ -7012,25 +7012,25 @@
         <v>64</v>
       </c>
       <c r="B4" s="174">
-        <v>303438</v>
+        <v>324343.90000000002</v>
       </c>
       <c r="C4" s="18">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D4" s="18">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E4" s="16">
         <f t="shared" si="0"/>
-        <v>1.2666666666666666</v>
+        <v>1.2698412698412698</v>
       </c>
       <c r="F4" s="17">
         <f t="shared" si="1"/>
-        <v>5057.3</v>
+        <v>5148.315873015873</v>
       </c>
       <c r="G4" s="17">
         <f t="shared" si="2"/>
-        <v>3992.6052631578946</v>
+        <v>4054.2987500000004</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -7038,25 +7038,25 @@
         <v>66</v>
       </c>
       <c r="B5" s="175">
-        <v>377876.34</v>
+        <v>397372.92</v>
       </c>
       <c r="C5" s="18">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D5" s="18">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E5" s="16">
         <f t="shared" si="0"/>
-        <v>1.7241379310344827</v>
+        <v>1.6935483870967742</v>
       </c>
       <c r="F5" s="17">
         <f t="shared" si="1"/>
-        <v>6515.1093103448284</v>
+        <v>6409.2406451612896</v>
       </c>
       <c r="G5" s="17">
         <f t="shared" si="2"/>
-        <v>3778.7634000000003</v>
+        <v>3784.5039999999999</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -7067,18 +7067,18 @@
         <v>250148.18</v>
       </c>
       <c r="C6" s="18">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D6" s="18">
         <v>59</v>
       </c>
       <c r="E6" s="16">
         <f t="shared" si="0"/>
-        <v>1.2826086956521738</v>
+        <v>1.2291666666666667</v>
       </c>
       <c r="F6" s="17">
         <f t="shared" si="1"/>
-        <v>5438.003913043478</v>
+        <v>5211.4204166666668</v>
       </c>
       <c r="G6" s="17">
         <f t="shared" si="2"/>

--- a/EKİM SD KARNE.xlsx
+++ b/EKİM SD KARNE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\UYGULAMA İÇİN GEREKLİ DOSYALAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60970DBA-0DE2-4370-8999-7E9503A82067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30273D3E-D505-4014-BD6A-DEAAF1B02C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2690,11 +2690,11 @@
       </c>
       <c r="B9" s="75">
         <f>I32</f>
-        <v>1760781.4599999997</v>
+        <v>1773322.88</v>
       </c>
       <c r="C9" s="76">
         <f>IFERROR(B9/A9,)</f>
-        <v>0.58692715333333323</v>
+        <v>0.59110762666666661</v>
       </c>
       <c r="D9" s="168">
         <f>IFERROR(IF(B9&lt;=A9,A4,IF(AND(B9&gt;A9,B9&lt;B1),A4,IF(AND(B9&gt;=B1,B9&lt;C1),B4,IF(AND(B9&gt;=C1,B9&lt;D1),C4,IF(AND(B9&gt;=D1,B9&lt;E1),D4,IF(AND(B9&gt;=E1,B9&lt;F1),E4,IF(AND(B9&gt;=F1,B9&lt;G1),F4,IF(AND(B9&gt;=G1,B9&lt;H1),G4,IF(AND(B9&gt;=H1,B9&lt;I1),H4,IF(AND(B9&gt;=I1,B9&lt;J1),I4,IF(AND(B9&gt;=J1,B9&lt;K1),J4,IF(B9&gt;=K4,K4,K4)))))))))))),)</f>
@@ -2761,27 +2761,27 @@
       </c>
       <c r="H10" s="83">
         <f ca="1">B11-M10</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I10" s="84">
         <f>C11</f>
-        <v>4257</v>
+        <v>4414</v>
       </c>
       <c r="J10" s="85">
         <f ca="1">I10/H10</f>
-        <v>212.85</v>
+        <v>200.63636363636363</v>
       </c>
       <c r="K10" s="85">
         <f>IFERROR(I10/G10,)</f>
-        <v>851.4</v>
+        <v>882.8</v>
       </c>
       <c r="L10" s="86">
         <f ca="1">IFERROR(J10/G10,)</f>
-        <v>42.57</v>
+        <v>40.127272727272725</v>
       </c>
       <c r="M10" s="87">
         <f ca="1">(M11-A11)+B11</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N10" s="2">
         <f>LOOKUP(A9,'PRİM HAVUZU (SV SİSTEM)'!$A:$A,'PRİM HAVUZU (SV SİSTEM)'!$C:$C)*A9</f>
@@ -2804,14 +2804,14 @@
     <row r="11" spans="1:58" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="169">
         <f ca="1">TODAY()</f>
-        <v>46316</v>
+        <v>46318</v>
       </c>
       <c r="B11" s="170">
         <f ca="1">(N11-M11)+1</f>
         <v>31</v>
       </c>
       <c r="C11" s="171">
-        <v>4257</v>
+        <v>4414</v>
       </c>
       <c r="F11" s="66"/>
       <c r="K11" s="89"/>
@@ -3005,11 +3005,11 @@
       </c>
       <c r="K13" s="111">
         <f>IFERROR(I13/$I$32,)</f>
-        <v>0.230333456600571</v>
+        <v>0.22870447597224935</v>
       </c>
       <c r="L13" s="112">
         <f t="shared" ref="L13:L31" si="4">IFERROR(IF(J13&lt;0.85,"",IF(AND(J13&gt;0.85,J13&lt;1),$M$2*AB13*AJ13,$M$2*AB13*AJ13)),"")</f>
-        <v>7400.6139605763465</v>
+        <v>7348.2748129883712</v>
       </c>
       <c r="M13" s="113">
         <f t="shared" ref="M13:M31" si="5">IFERROR((($E$9+$F$9)*AC13),"")</f>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O13" s="114">
         <f t="shared" ref="O13:O31" si="6">IFERROR(IF(N13/(W13-V13)&gt;0,N13/(W13-V13),""),"")</f>
-        <v>6486.9269930069886</v>
+        <v>7928.4663247863191</v>
       </c>
       <c r="P13" s="110">
         <f t="shared" ref="P13:P31" si="7">IFERROR(I13/C13,0)</f>
@@ -3029,26 +3029,26 @@
       </c>
       <c r="Q13" s="109">
         <f t="shared" ref="Q13:Q31" si="8">IF(V13="",0,IF(W13=V13,I13,(I13/V13)*(W13-V13)+I13))</f>
-        <v>628628.66399999999</v>
+        <v>571480.60363636364</v>
       </c>
       <c r="R13" s="115">
         <f>IFERROR(Q13/$Q$32,)</f>
-        <v>0.22682168250540327</v>
+        <v>0.22543881735414673</v>
       </c>
       <c r="S13" s="106">
         <f>IFERROR(IF(T13&lt;0.85,"",IF(AND(T13&gt;0.85,T13&lt;1),$M$2*AD13*AK13,$M$2*AD13*AK13)),"")</f>
-        <v>12493.338272397612</v>
+        <v>12313.693642700848</v>
       </c>
       <c r="T13" s="110">
         <f t="shared" ref="T13:T31" si="9">IFERROR(Q13/C13,0)</f>
-        <v>1.3180923600000001</v>
+        <v>1.1982657818181819</v>
       </c>
       <c r="U13" s="116">
         <f t="shared" ref="U13:U31" si="10">IFERROR(D13/Z13,0)</f>
-        <v>7.9069767441860464E-2</v>
+        <v>7.6327388062775461E-2</v>
       </c>
       <c r="V13" s="62">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="W13" s="63">
         <v>31</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z13" s="118">
         <f t="shared" ref="Z13:Z31" si="12">(V13/$V$32)*$I$10</f>
-        <v>860</v>
+        <v>890.89908256880744</v>
       </c>
       <c r="AA13" s="119">
         <f t="shared" ref="AA13:AA31" si="13">IFERROR(((Y13/$Y$32)*$A$9),"")</f>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AB13" s="120">
         <f t="shared" ref="AB13:AB31" si="14">I13/$I$32</f>
-        <v>0.230333456600571</v>
+        <v>0.22870447597224935</v>
       </c>
       <c r="AC13" s="121">
         <f>AA13/$C$32</f>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AD13" s="120">
         <f>Q13/$Q$32</f>
-        <v>0.22682168250540327</v>
+        <v>0.22543881735414673</v>
       </c>
       <c r="AE13" s="120">
         <f t="shared" ref="AE13:AE31" si="15">I13/C13</f>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AF13" s="120">
         <f t="shared" ref="AF13:AF31" si="16">Q13/C13</f>
-        <v>1.3180923600000001</v>
+        <v>1.1982657818181819</v>
       </c>
       <c r="AG13" s="120">
         <f>IFERROR(VLOOKUP(A13,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AK13" s="123">
         <f t="shared" ref="AK13:AK31" si="19">IFERROR(LOOKUP(AF13,AL:AL,AM:AM),"")</f>
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AL13" s="93">
         <v>0.87</v>
@@ -3124,33 +3124,33 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D14" s="126">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E14" s="126">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F14" s="127">
         <f>DATA!E3</f>
-        <v>1.5833333333333333</v>
+        <v>1.564516129032258</v>
       </c>
       <c r="G14" s="128">
         <f>DATA!F3</f>
-        <v>6742.559666666667</v>
+        <v>6725.9032258064517</v>
       </c>
       <c r="H14" s="128">
         <f>DATA!G3</f>
-        <v>4258.4587368421053</v>
+        <v>4299.0309278350514</v>
       </c>
       <c r="I14" s="125">
-        <v>404553.58</v>
+        <v>417006</v>
       </c>
       <c r="J14" s="129">
         <f t="shared" si="3"/>
-        <v>0.63619312983870968</v>
+        <v>0.65577556451612906</v>
       </c>
       <c r="K14" s="111">
         <f t="shared" ref="K14:K31" si="21">IFERROR(I14/$I$32,)</f>
-        <v>0.22975797348525018</v>
+        <v>0.23515514557619649</v>
       </c>
       <c r="L14" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3162,38 +3162,38 @@
       </c>
       <c r="N14" s="130">
         <f t="shared" ref="N14:N31" si="22">IFERROR(IF(C14-I14&lt;0,"",C14-I14),"")</f>
-        <v>231343.85589743586</v>
+        <v>218891.43589743588</v>
       </c>
       <c r="O14" s="130">
         <f t="shared" si="6"/>
-        <v>21031.259627039624</v>
+        <v>24321.270655270651</v>
       </c>
       <c r="P14" s="129">
         <f t="shared" si="7"/>
-        <v>0.63619312983870968</v>
+        <v>0.65577556451612906</v>
       </c>
       <c r="Q14" s="109">
         <f t="shared" si="8"/>
-        <v>627058.049</v>
+        <v>587599.36363636365</v>
       </c>
       <c r="R14" s="115">
         <f t="shared" ref="R14:R31" si="23">IFERROR(Q14/$Q$32,)</f>
-        <v>0.22625497348103046</v>
+        <v>0.2317973782020448</v>
       </c>
       <c r="S14" s="106">
         <f t="shared" ref="S14:S31" si="24">IFERROR(IF(T14&lt;0.85,"",IF(AND(T14&gt;0.85,T14&lt;1),$M$2*AD14*AK14,$M$2*AD14*AK14)),"")</f>
-        <v>9969.6991514681267</v>
+        <v>8937.1797139580394</v>
       </c>
       <c r="T14" s="129">
         <f t="shared" si="9"/>
-        <v>0.98609935125000003</v>
+        <v>0.92404738636363637</v>
       </c>
       <c r="U14" s="131">
         <f t="shared" si="10"/>
-        <v>6.9767441860465115E-2</v>
+        <v>6.9592618527824682E-2</v>
       </c>
       <c r="V14" s="62">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="W14" s="64">
         <v>31</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="Z14" s="133">
         <f t="shared" si="12"/>
-        <v>860</v>
+        <v>890.89908256880744</v>
       </c>
       <c r="AA14" s="17">
         <f t="shared" si="13"/>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="AB14" s="134">
         <f t="shared" si="14"/>
-        <v>0.22975797348525018</v>
+        <v>0.23515514557619649</v>
       </c>
       <c r="AC14" s="135">
         <f t="shared" ref="AC14:AC31" si="25">AA14/$C$32</f>
@@ -3220,15 +3220,15 @@
       </c>
       <c r="AD14" s="134">
         <f t="shared" ref="AD14:AD18" si="26">Q14/$Q$32</f>
-        <v>0.22625497348103046</v>
+        <v>0.2317973782020448</v>
       </c>
       <c r="AE14" s="134">
         <f t="shared" si="15"/>
-        <v>0.63619312983870968</v>
+        <v>0.65577556451612906</v>
       </c>
       <c r="AF14" s="134">
         <f t="shared" si="16"/>
-        <v>0.98609935125000003</v>
+        <v>0.92404738636363637</v>
       </c>
       <c r="AG14" s="134">
         <f>IFERROR(VLOOKUP(A14,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="AK14" s="137">
         <f t="shared" si="19"/>
-        <v>0.96</v>
+        <v>0.84</v>
       </c>
       <c r="AL14" s="93">
         <v>0.88</v>
@@ -3280,22 +3280,22 @@
       </c>
       <c r="G15" s="128">
         <f>DATA!F4</f>
-        <v>5148.315873015873</v>
+        <v>5148.269841269841</v>
       </c>
       <c r="H15" s="128">
         <f>DATA!G4</f>
-        <v>4054.2987500000004</v>
+        <v>4054.2624999999998</v>
       </c>
       <c r="I15" s="125">
-        <v>324343.90000000002</v>
+        <v>324341</v>
       </c>
       <c r="J15" s="129">
         <f t="shared" si="3"/>
-        <v>0.52705883750000004</v>
+        <v>0.52705412500000004</v>
       </c>
       <c r="K15" s="111">
         <f t="shared" si="21"/>
-        <v>0.18420451791899267</v>
+        <v>0.18290013829855961</v>
       </c>
       <c r="L15" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3307,23 +3307,23 @@
       </c>
       <c r="N15" s="130">
         <f t="shared" si="22"/>
-        <v>291040.71538461535</v>
+        <v>291043.61538461538</v>
       </c>
       <c r="O15" s="130">
         <f t="shared" si="6"/>
-        <v>26458.246853146851</v>
+        <v>32338.179487179485</v>
       </c>
       <c r="P15" s="129">
         <f t="shared" si="7"/>
-        <v>0.52705883750000004</v>
+        <v>0.52705412500000004</v>
       </c>
       <c r="Q15" s="109">
         <f t="shared" si="8"/>
-        <v>512121.94736842107</v>
+        <v>463344.28571428568</v>
       </c>
       <c r="R15" s="115">
         <f t="shared" si="23"/>
-        <v>0.18478374977512774</v>
+        <v>0.18278098527679207</v>
       </c>
       <c r="S15" s="106" t="str">
         <f t="shared" si="24"/>
@@ -3331,14 +3331,14 @@
       </c>
       <c r="T15" s="129">
         <f t="shared" si="9"/>
-        <v>0.83219816447368422</v>
+        <v>0.7529344642857142</v>
       </c>
       <c r="U15" s="131">
         <f t="shared" si="10"/>
-        <v>7.711138310893513E-2</v>
+        <v>7.4082464884458535E-2</v>
       </c>
       <c r="V15" s="62">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="W15" s="64">
         <v>30</v>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="Z15" s="133">
         <f t="shared" si="12"/>
-        <v>817</v>
+        <v>850.40366972477068</v>
       </c>
       <c r="AA15" s="17">
         <f t="shared" si="13"/>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="AB15" s="134">
         <f t="shared" si="14"/>
-        <v>0.18420451791899267</v>
+        <v>0.18290013829855961</v>
       </c>
       <c r="AC15" s="135">
         <f t="shared" si="25"/>
@@ -3365,15 +3365,15 @@
       </c>
       <c r="AD15" s="134">
         <f t="shared" si="26"/>
-        <v>0.18478374977512774</v>
+        <v>0.18278098527679207</v>
       </c>
       <c r="AE15" s="134">
         <f t="shared" si="15"/>
-        <v>0.52705883750000004</v>
+        <v>0.52705412500000004</v>
       </c>
       <c r="AF15" s="134">
         <f t="shared" si="16"/>
-        <v>0.83219816447368422</v>
+        <v>0.7529344642857142</v>
       </c>
       <c r="AG15" s="134">
         <f>IFERROR(VLOOKUP(A15,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3414,33 +3414,33 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D16" s="126">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E16" s="126">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F16" s="127">
         <f>DATA!E5</f>
-        <v>1.6935483870967742</v>
+        <v>1.6507936507936507</v>
       </c>
       <c r="G16" s="128">
         <f>DATA!F5</f>
-        <v>6409.2406451612896</v>
+        <v>6228.1587301587306</v>
       </c>
       <c r="H16" s="128">
         <f>DATA!G5</f>
-        <v>3784.5039999999999</v>
+        <v>3772.8269230769229</v>
       </c>
       <c r="I16" s="125">
-        <v>397372.92</v>
+        <v>392374</v>
       </c>
       <c r="J16" s="129">
         <f t="shared" si="3"/>
-        <v>0.62490096290322583</v>
+        <v>0.61703975806451616</v>
       </c>
       <c r="K16" s="111">
         <f t="shared" si="21"/>
-        <v>0.22567986375776586</v>
+        <v>0.22126483813257969</v>
       </c>
       <c r="L16" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3452,38 +3452,38 @@
       </c>
       <c r="N16" s="130">
         <f t="shared" ref="N16:N25" si="28">IFERROR(IF(C16-I16&lt;0,"",C16-I16),"")</f>
-        <v>238524.51589743589</v>
+        <v>243523.43589743588</v>
       </c>
       <c r="O16" s="130">
         <f t="shared" si="6"/>
-        <v>21684.046899766898</v>
+        <v>27058.159544159542</v>
       </c>
       <c r="P16" s="129">
         <f t="shared" si="7"/>
-        <v>0.62490096290322583</v>
+        <v>0.61703975806451616</v>
       </c>
       <c r="Q16" s="109">
         <f t="shared" si="8"/>
-        <v>615928.02599999995</v>
+        <v>552890.63636363635</v>
       </c>
       <c r="R16" s="115">
         <f t="shared" si="23"/>
-        <v>0.22223904056584948</v>
+        <v>0.21810540969350348</v>
       </c>
       <c r="S16" s="106">
         <f t="shared" si="24"/>
-        <v>9384.7102050146914</v>
+        <v>7207.9475795509024</v>
       </c>
       <c r="T16" s="129">
         <f t="shared" si="9"/>
-        <v>0.96859649249999991</v>
+        <v>0.8694651136363637</v>
       </c>
       <c r="U16" s="131">
         <f t="shared" si="10"/>
-        <v>7.2093023255813959E-2</v>
+        <v>7.0715080116983145E-2</v>
       </c>
       <c r="V16" s="62">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="W16" s="64">
         <v>31</v>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="Z16" s="133">
         <f t="shared" si="12"/>
-        <v>860</v>
+        <v>890.89908256880744</v>
       </c>
       <c r="AA16" s="17">
         <f t="shared" si="13"/>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="AB16" s="134">
         <f t="shared" si="14"/>
-        <v>0.22567986375776586</v>
+        <v>0.22126483813257969</v>
       </c>
       <c r="AC16" s="135">
         <f t="shared" si="25"/>
@@ -3510,15 +3510,15 @@
       </c>
       <c r="AD16" s="134">
         <f t="shared" si="26"/>
-        <v>0.22223904056584948</v>
+        <v>0.21810540969350348</v>
       </c>
       <c r="AE16" s="134">
         <f t="shared" si="15"/>
-        <v>0.62490096290322583</v>
+        <v>0.61703975806451616</v>
       </c>
       <c r="AF16" s="134">
         <f t="shared" si="16"/>
-        <v>0.96859649249999991</v>
+        <v>0.8694651136363637</v>
       </c>
       <c r="AG16" s="134">
         <f>IFERROR(VLOOKUP(A16,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3538,7 +3538,7 @@
       </c>
       <c r="AK16" s="137">
         <f t="shared" si="19"/>
-        <v>0.92</v>
+        <v>0.72</v>
       </c>
       <c r="AL16" s="93">
         <v>0.9</v>
@@ -3559,33 +3559,33 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D17" s="126">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E17" s="126">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F17" s="127">
         <f>DATA!E6</f>
-        <v>1.2291666666666667</v>
+        <v>1.2448979591836735</v>
       </c>
       <c r="G17" s="128">
         <f>DATA!F6</f>
-        <v>5211.4204166666668</v>
+        <v>5208.9591836734689</v>
       </c>
       <c r="H17" s="128">
         <f>DATA!G6</f>
-        <v>4239.7996610169494</v>
+        <v>4184.2459016393441</v>
       </c>
       <c r="I17" s="125">
-        <v>250148.18</v>
+        <v>255239</v>
       </c>
       <c r="J17" s="129">
         <f t="shared" si="3"/>
-        <v>0.39337818629032256</v>
+        <v>0.40138391129032258</v>
       </c>
       <c r="K17" s="111">
         <f t="shared" si="21"/>
-        <v>0.14206656855644087</v>
+        <v>0.1439326153621838</v>
       </c>
       <c r="L17" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3597,23 +3597,23 @@
       </c>
       <c r="N17" s="130">
         <f t="shared" si="28"/>
-        <v>385749.25589743588</v>
+        <v>380658.43589743588</v>
       </c>
       <c r="O17" s="130">
         <f t="shared" si="6"/>
-        <v>35068.11417249417</v>
+        <v>42295.381766381761</v>
       </c>
       <c r="P17" s="129">
         <f t="shared" si="7"/>
-        <v>0.39337818629032256</v>
+        <v>0.40138391129032258</v>
       </c>
       <c r="Q17" s="109">
         <f t="shared" si="8"/>
-        <v>387729.679</v>
+        <v>359654.95454545459</v>
       </c>
       <c r="R17" s="115">
         <f t="shared" si="23"/>
-        <v>0.13990055367258902</v>
+        <v>0.14187740947351288</v>
       </c>
       <c r="S17" s="106" t="str">
         <f t="shared" si="24"/>
@@ -3621,14 +3621,14 @@
       </c>
       <c r="T17" s="129">
         <f t="shared" si="9"/>
-        <v>0.60973618875000002</v>
+        <v>0.56558642045454555</v>
       </c>
       <c r="U17" s="131">
         <f t="shared" si="10"/>
-        <v>5.5813953488372092E-2</v>
+        <v>5.5000617868764666E-2</v>
       </c>
       <c r="V17" s="62">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="W17" s="64">
         <v>31</v>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="Z17" s="133">
         <f t="shared" si="12"/>
-        <v>860</v>
+        <v>890.89908256880744</v>
       </c>
       <c r="AA17" s="17">
         <f t="shared" si="13"/>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="AB17" s="134">
         <f t="shared" si="14"/>
-        <v>0.14206656855644087</v>
+        <v>0.1439326153621838</v>
       </c>
       <c r="AC17" s="135">
         <f t="shared" si="25"/>
@@ -3655,15 +3655,15 @@
       </c>
       <c r="AD17" s="134">
         <f t="shared" si="26"/>
-        <v>0.13990055367258902</v>
+        <v>0.14187740947351288</v>
       </c>
       <c r="AE17" s="134">
         <f t="shared" si="15"/>
-        <v>0.39337818629032256</v>
+        <v>0.40138391129032258</v>
       </c>
       <c r="AF17" s="134">
         <f t="shared" si="16"/>
-        <v>0.60973618875000002</v>
+        <v>0.56558642045454555</v>
       </c>
       <c r="AG17" s="134">
         <f>IFERROR(VLOOKUP(A17,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="K18" s="111">
         <f t="shared" si="21"/>
-        <v>-1.2042380319020399E-2</v>
+        <v>-1.1957213341768873E-2</v>
       </c>
       <c r="L18" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="AB18" s="138">
         <f t="shared" si="14"/>
-        <v>-1.2042380319020399E-2</v>
+        <v>-1.1957213341768873E-2</v>
       </c>
       <c r="AC18" s="135">
         <f t="shared" si="25"/>
@@ -5699,39 +5699,39 @@
       </c>
       <c r="D32" s="153">
         <f>SUM(D13:D31)</f>
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="E32" s="153">
         <f>SUM(E13:E31)</f>
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F32" s="154">
         <f>IFERROR(SUM(F13:F31)/G10,)</f>
-        <v>1.6610602843287849</v>
+        <v>1.6518921547113472</v>
       </c>
       <c r="G32" s="155">
         <f>IFERROR(SUM(G13:G31)/G10,)</f>
-        <v>6601.9510850079823</v>
+        <v>6561.9019608875806</v>
       </c>
       <c r="H32" s="155">
         <f>IFERROR(SUM(H13:H31)/G10,)</f>
-        <v>4754.1485372641191</v>
+        <v>4748.8095582025717</v>
       </c>
       <c r="I32" s="155">
         <f>SUM(I13:I31)</f>
-        <v>1760781.4599999997</v>
+        <v>1773322.88</v>
       </c>
       <c r="J32" s="156">
         <f>IFERROR(I32/C32,)</f>
-        <v>0.58692715333333323</v>
+        <v>0.59110762666666661</v>
       </c>
       <c r="K32" s="156">
         <f>SUM(K13:K31)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="L32" s="155">
         <f>SUM(L13:L31)</f>
-        <v>7400.6139605763465</v>
+        <v>7348.2748129883712</v>
       </c>
       <c r="M32" s="155">
         <f>SUM(M13:M31)</f>
@@ -5739,16 +5739,16 @@
       </c>
       <c r="N32" s="155">
         <f>SUM(N13:N31)</f>
-        <v>1239218.5399999998</v>
+        <v>1226677.1199999999</v>
       </c>
       <c r="O32" s="155">
         <f>SUM(O13:O31)</f>
-        <v>110728.59454545453</v>
+        <v>133941.45777777774</v>
       </c>
       <c r="P32" s="157"/>
       <c r="Q32" s="152">
         <f>SUM(Q13:Q31)</f>
-        <v>2771466.3653684212</v>
+        <v>2534969.843896104</v>
       </c>
       <c r="R32" s="156">
         <f>SUM(R13:R31)</f>
@@ -5756,16 +5756,16 @@
       </c>
       <c r="S32" s="155">
         <f>SUM(S13:S31)</f>
-        <v>31847.747628880432</v>
+        <v>28458.820936209788</v>
       </c>
       <c r="T32" s="158">
         <f>IFERROR(Q32/C32,)</f>
-        <v>0.92382212178947376</v>
+        <v>0.84498994796536797</v>
       </c>
       <c r="U32" s="165"/>
       <c r="V32" s="166">
         <f>SUM(V13:V31)</f>
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="W32" s="167">
         <f>SUM(W13:W31)</f>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="Z32" s="164">
         <f>SUM(Z13:Z31)</f>
-        <v>4257</v>
+        <v>4414</v>
       </c>
       <c r="AA32" s="162">
         <f>SUM(AA13:AA31)</f>
@@ -6980,25 +6980,25 @@
         <v>67</v>
       </c>
       <c r="B3" s="19">
-        <v>404553.58</v>
+        <v>417006</v>
       </c>
       <c r="C3" s="18">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D3" s="18">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E3" s="16">
         <f t="shared" ref="E3:E20" si="0">IFERROR((D3/C3),"")</f>
-        <v>1.5833333333333333</v>
+        <v>1.564516129032258</v>
       </c>
       <c r="F3" s="17">
         <f t="shared" ref="F3:F20" si="1">IFERROR((B3/C3),"")</f>
-        <v>6742.559666666667</v>
+        <v>6725.9032258064517</v>
       </c>
       <c r="G3" s="17">
         <f t="shared" ref="G3:G20" si="2">IFERROR((B3/D3),"")</f>
-        <v>4258.4587368421053</v>
+        <v>4299.0309278350514</v>
       </c>
       <c r="Q3" s="6" t="s">
         <v>40</v>
@@ -7012,7 +7012,7 @@
         <v>64</v>
       </c>
       <c r="B4" s="174">
-        <v>324343.90000000002</v>
+        <v>324341</v>
       </c>
       <c r="C4" s="18">
         <v>63</v>
@@ -7026,11 +7026,11 @@
       </c>
       <c r="F4" s="17">
         <f t="shared" si="1"/>
-        <v>5148.315873015873</v>
+        <v>5148.269841269841</v>
       </c>
       <c r="G4" s="17">
         <f t="shared" si="2"/>
-        <v>4054.2987500000004</v>
+        <v>4054.2624999999998</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -7038,25 +7038,25 @@
         <v>66</v>
       </c>
       <c r="B5" s="175">
-        <v>397372.92</v>
+        <v>392374</v>
       </c>
       <c r="C5" s="18">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D5" s="18">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E5" s="16">
         <f t="shared" si="0"/>
-        <v>1.6935483870967742</v>
+        <v>1.6507936507936507</v>
       </c>
       <c r="F5" s="17">
         <f t="shared" si="1"/>
-        <v>6409.2406451612896</v>
+        <v>6228.1587301587306</v>
       </c>
       <c r="G5" s="17">
         <f t="shared" si="2"/>
-        <v>3784.5039999999999</v>
+        <v>3772.8269230769229</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -7064,25 +7064,25 @@
         <v>68</v>
       </c>
       <c r="B6" s="19">
-        <v>250148.18</v>
+        <v>255239</v>
       </c>
       <c r="C6" s="18">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D6" s="18">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E6" s="16">
         <f t="shared" si="0"/>
-        <v>1.2291666666666667</v>
+        <v>1.2448979591836735</v>
       </c>
       <c r="F6" s="17">
         <f t="shared" si="1"/>
-        <v>5211.4204166666668</v>
+        <v>5208.9591836734689</v>
       </c>
       <c r="G6" s="17">
         <f t="shared" si="2"/>
-        <v>4239.7996610169494</v>
+        <v>4184.2459016393441</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">

--- a/EKİM SD KARNE.xlsx
+++ b/EKİM SD KARNE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\UYGULAMA İÇİN GEREKLİ DOSYALAR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30273D3E-D505-4014-BD6A-DEAAF1B02C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0BB84AB-B01B-4398-AEED-84E70CDDB3BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2690,11 +2690,11 @@
       </c>
       <c r="B9" s="75">
         <f>I32</f>
-        <v>1773322.88</v>
+        <v>1784286.73</v>
       </c>
       <c r="C9" s="76">
         <f>IFERROR(B9/A9,)</f>
-        <v>0.59110762666666661</v>
+        <v>0.59476224333333327</v>
       </c>
       <c r="D9" s="168">
         <f>IFERROR(IF(B9&lt;=A9,A4,IF(AND(B9&gt;A9,B9&lt;B1),A4,IF(AND(B9&gt;=B1,B9&lt;C1),B4,IF(AND(B9&gt;=C1,B9&lt;D1),C4,IF(AND(B9&gt;=D1,B9&lt;E1),D4,IF(AND(B9&gt;=E1,B9&lt;F1),E4,IF(AND(B9&gt;=F1,B9&lt;G1),F4,IF(AND(B9&gt;=G1,B9&lt;H1),G4,IF(AND(B9&gt;=H1,B9&lt;I1),H4,IF(AND(B9&gt;=I1,B9&lt;J1),I4,IF(AND(B9&gt;=J1,B9&lt;K1),J4,IF(B9&gt;=K4,K4,K4)))))))))))),)</f>
@@ -2761,27 +2761,27 @@
       </c>
       <c r="H10" s="83">
         <f ca="1">B11-M10</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I10" s="84">
         <f>C11</f>
-        <v>4414</v>
+        <v>4515</v>
       </c>
       <c r="J10" s="85">
         <f ca="1">I10/H10</f>
-        <v>200.63636363636363</v>
+        <v>196.30434782608697</v>
       </c>
       <c r="K10" s="85">
         <f>IFERROR(I10/G10,)</f>
-        <v>882.8</v>
+        <v>903</v>
       </c>
       <c r="L10" s="86">
         <f ca="1">IFERROR(J10/G10,)</f>
-        <v>40.127272727272725</v>
+        <v>39.260869565217391</v>
       </c>
       <c r="M10" s="87">
         <f ca="1">(M11-A11)+B11</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N10" s="2">
         <f>LOOKUP(A9,'PRİM HAVUZU (SV SİSTEM)'!$A:$A,'PRİM HAVUZU (SV SİSTEM)'!$C:$C)*A9</f>
@@ -2804,14 +2804,14 @@
     <row r="11" spans="1:58" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="169">
         <f ca="1">TODAY()</f>
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="B11" s="170">
         <f ca="1">(N11-M11)+1</f>
         <v>31</v>
       </c>
       <c r="C11" s="171">
-        <v>4414</v>
+        <v>4515</v>
       </c>
       <c r="F11" s="66"/>
       <c r="K11" s="89"/>
@@ -2977,39 +2977,39 @@
       </c>
       <c r="D13" s="107" cm="1">
         <f t="array" ref="D13:D31">DATA!C2:C20</f>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E13" s="107" cm="1">
         <f t="array" ref="E13:E31">DATA!D2:D20</f>
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F13" s="108">
         <f>DATA!E2</f>
-        <v>1.5294117647058822</v>
+        <v>1.536231884057971</v>
       </c>
       <c r="G13" s="109">
         <f>DATA!F2</f>
-        <v>5964.2188235294116</v>
+        <v>5952.8566666666666</v>
       </c>
       <c r="H13" s="109">
         <f>DATA!G2</f>
-        <v>3899.6815384615384</v>
+        <v>3874.9727358490563</v>
       </c>
       <c r="I13" s="106" cm="1">
         <f t="array" ref="I13:I31">DATA!B2:B20</f>
-        <v>405566.88</v>
+        <v>410747.11</v>
       </c>
       <c r="J13" s="110">
         <f t="shared" ref="J13:J31" si="3">IFERROR(I13/C13,0)</f>
-        <v>0.85038216774193554</v>
+        <v>0.86124394032258067</v>
       </c>
       <c r="K13" s="111">
         <f>IFERROR(I13/$I$32,)</f>
-        <v>0.22870447597224935</v>
+        <v>0.23020241259094046</v>
       </c>
       <c r="L13" s="112">
         <f t="shared" ref="L13:L31" si="4">IFERROR(IF(J13&lt;0.85,"",IF(AND(J13&gt;0.85,J13&lt;1),$M$2*AB13*AJ13,$M$2*AB13*AJ13)),"")</f>
-        <v>7348.2748129883712</v>
+        <v>7607.7293313054006</v>
       </c>
       <c r="M13" s="113">
         <f t="shared" ref="M13:M31" si="5">IFERROR((($E$9+$F$9)*AC13),"")</f>
@@ -3017,38 +3017,38 @@
       </c>
       <c r="N13" s="114">
         <f>IFERROR(IF(C13-I13&lt;0,"",C13-I13),"")</f>
-        <v>71356.196923076874</v>
+        <v>66175.966923076892</v>
       </c>
       <c r="O13" s="114">
         <f t="shared" ref="O13:O31" si="6">IFERROR(IF(N13/(W13-V13)&gt;0,N13/(W13-V13),""),"")</f>
-        <v>7928.4663247863191</v>
+        <v>8271.9958653846115</v>
       </c>
       <c r="P13" s="110">
         <f t="shared" ref="P13:P31" si="7">IFERROR(I13/C13,0)</f>
-        <v>0.85038216774193554</v>
+        <v>0.86124394032258067</v>
       </c>
       <c r="Q13" s="109">
         <f t="shared" ref="Q13:Q31" si="8">IF(V13="",0,IF(W13=V13,I13,(I13/V13)*(W13-V13)+I13))</f>
-        <v>571480.60363636364</v>
+        <v>553615.66999999993</v>
       </c>
       <c r="R13" s="115">
         <f>IFERROR(Q13/$Q$32,)</f>
-        <v>0.22543881735414673</v>
+        <v>0.22701197812597146</v>
       </c>
       <c r="S13" s="106">
         <f>IFERROR(IF(T13&lt;0.85,"",IF(AND(T13&gt;0.85,T13&lt;1),$M$2*AD13*AK13,$M$2*AD13*AK13)),"")</f>
-        <v>12313.693642700848</v>
+        <v>12087.025763339225</v>
       </c>
       <c r="T13" s="110">
         <f t="shared" ref="T13:T31" si="9">IFERROR(Q13/C13,0)</f>
-        <v>1.1982657818181819</v>
+        <v>1.1608070500000001</v>
       </c>
       <c r="U13" s="116">
         <f t="shared" ref="U13:U31" si="10">IFERROR(D13/Z13,0)</f>
-        <v>7.6327388062775461E-2</v>
+        <v>7.5747508305647845E-2</v>
       </c>
       <c r="V13" s="62">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W13" s="63">
         <v>31</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z13" s="118">
         <f t="shared" ref="Z13:Z31" si="12">(V13/$V$32)*$I$10</f>
-        <v>890.89908256880744</v>
+        <v>910.92105263157885</v>
       </c>
       <c r="AA13" s="119">
         <f t="shared" ref="AA13:AA31" si="13">IFERROR(((Y13/$Y$32)*$A$9),"")</f>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AB13" s="120">
         <f t="shared" ref="AB13:AB31" si="14">I13/$I$32</f>
-        <v>0.22870447597224935</v>
+        <v>0.23020241259094046</v>
       </c>
       <c r="AC13" s="121">
         <f>AA13/$C$32</f>
@@ -3075,15 +3075,15 @@
       </c>
       <c r="AD13" s="120">
         <f>Q13/$Q$32</f>
-        <v>0.22543881735414673</v>
+        <v>0.22701197812597146</v>
       </c>
       <c r="AE13" s="120">
         <f t="shared" ref="AE13:AE31" si="15">I13/C13</f>
-        <v>0.85038216774193554</v>
+        <v>0.86124394032258067</v>
       </c>
       <c r="AF13" s="120">
         <f t="shared" ref="AF13:AF31" si="16">Q13/C13</f>
-        <v>1.1982657818181819</v>
+        <v>1.1608070500000001</v>
       </c>
       <c r="AG13" s="120">
         <f>IFERROR(VLOOKUP(A13,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3099,11 +3099,11 @@
       </c>
       <c r="AJ13" s="121">
         <f t="shared" ref="AJ13:AJ31" si="18">IFERROR(LOOKUP(AE13,AL:AL,AM:AM),"")</f>
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="AK13" s="123">
         <f t="shared" ref="AK13:AK31" si="19">IFERROR(LOOKUP(AF13,AL:AL,AM:AM),"")</f>
-        <v>1.19</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="AL13" s="93">
         <v>0.87</v>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="K14" s="111">
         <f t="shared" ref="K14:K31" si="21">IFERROR(I14/$I$32,)</f>
-        <v>0.23515514557619649</v>
+        <v>0.23371019522181841</v>
       </c>
       <c r="L14" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="O14" s="130">
         <f t="shared" si="6"/>
-        <v>24321.270655270651</v>
+        <v>27361.429487179485</v>
       </c>
       <c r="P14" s="129">
         <f t="shared" si="7"/>
@@ -3174,26 +3174,26 @@
       </c>
       <c r="Q14" s="109">
         <f t="shared" si="8"/>
-        <v>587599.36363636365</v>
+        <v>562051.56521739135</v>
       </c>
       <c r="R14" s="115">
         <f t="shared" ref="R14:R31" si="23">IFERROR(Q14/$Q$32,)</f>
-        <v>0.2317973782020448</v>
+        <v>0.23047114549484932</v>
       </c>
       <c r="S14" s="106">
         <f t="shared" ref="S14:S31" si="24">IFERROR(IF(T14&lt;0.85,"",IF(AND(T14&gt;0.85,T14&lt;1),$M$2*AD14*AK14,$M$2*AD14*AK14)),"")</f>
-        <v>8937.1797139580394</v>
+        <v>8039.7554394423232</v>
       </c>
       <c r="T14" s="129">
         <f t="shared" si="9"/>
-        <v>0.92404738636363637</v>
+        <v>0.88387141304347838</v>
       </c>
       <c r="U14" s="131">
         <f t="shared" si="10"/>
-        <v>6.9592618527824682E-2</v>
+        <v>6.8062978477538644E-2</v>
       </c>
       <c r="V14" s="62">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W14" s="64">
         <v>31</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="Z14" s="133">
         <f t="shared" si="12"/>
-        <v>890.89908256880744</v>
+        <v>910.92105263157885</v>
       </c>
       <c r="AA14" s="17">
         <f t="shared" si="13"/>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="AB14" s="134">
         <f t="shared" si="14"/>
-        <v>0.23515514557619649</v>
+        <v>0.23371019522181841</v>
       </c>
       <c r="AC14" s="135">
         <f t="shared" ref="AC14:AC31" si="25">AA14/$C$32</f>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="AD14" s="134">
         <f t="shared" ref="AD14:AD18" si="26">Q14/$Q$32</f>
-        <v>0.2317973782020448</v>
+        <v>0.23047114549484932</v>
       </c>
       <c r="AE14" s="134">
         <f t="shared" si="15"/>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="AF14" s="134">
         <f t="shared" si="16"/>
-        <v>0.92404738636363637</v>
+        <v>0.88387141304347838</v>
       </c>
       <c r="AG14" s="134">
         <f>IFERROR(VLOOKUP(A14,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="AK14" s="137">
         <f t="shared" si="19"/>
-        <v>0.84</v>
+        <v>0.76</v>
       </c>
       <c r="AL14" s="93">
         <v>0.88</v>
@@ -3269,33 +3269,33 @@
         <v>615384.61538461538</v>
       </c>
       <c r="D15" s="126">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E15" s="126">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F15" s="127">
         <f>DATA!E4</f>
-        <v>1.2698412698412698</v>
+        <v>1.2424242424242424</v>
       </c>
       <c r="G15" s="128">
         <f>DATA!F4</f>
-        <v>5148.269841269841</v>
+        <v>5001.8881818181817</v>
       </c>
       <c r="H15" s="128">
         <f>DATA!G4</f>
-        <v>4054.2624999999998</v>
+        <v>4025.91</v>
       </c>
       <c r="I15" s="125">
-        <v>324341</v>
+        <v>330124.62</v>
       </c>
       <c r="J15" s="129">
         <f t="shared" si="3"/>
-        <v>0.52705412500000004</v>
+        <v>0.53645250749999995</v>
       </c>
       <c r="K15" s="111">
         <f t="shared" si="21"/>
-        <v>0.18290013829855961</v>
+        <v>0.18501769611882951</v>
       </c>
       <c r="L15" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3307,23 +3307,23 @@
       </c>
       <c r="N15" s="130">
         <f t="shared" si="22"/>
-        <v>291043.61538461538</v>
+        <v>285259.99538461538</v>
       </c>
       <c r="O15" s="130">
         <f t="shared" si="6"/>
-        <v>32338.179487179485</v>
+        <v>35657.499423076923</v>
       </c>
       <c r="P15" s="129">
         <f t="shared" si="7"/>
-        <v>0.52705412500000004</v>
+        <v>0.53645250749999995</v>
       </c>
       <c r="Q15" s="109">
         <f t="shared" si="8"/>
-        <v>463344.28571428568</v>
+        <v>450169.93636363634</v>
       </c>
       <c r="R15" s="115">
         <f t="shared" si="23"/>
-        <v>0.18278098527679207</v>
+        <v>0.18459370513618553</v>
       </c>
       <c r="S15" s="106" t="str">
         <f t="shared" si="24"/>
@@ -3331,14 +3331,14 @@
       </c>
       <c r="T15" s="129">
         <f t="shared" si="9"/>
-        <v>0.7529344642857142</v>
+        <v>0.73152614659090909</v>
       </c>
       <c r="U15" s="131">
         <f t="shared" si="10"/>
-        <v>7.4082464884458535E-2</v>
+        <v>7.5747508305647845E-2</v>
       </c>
       <c r="V15" s="62">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W15" s="64">
         <v>30</v>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="Z15" s="133">
         <f t="shared" si="12"/>
-        <v>850.40366972477068</v>
+        <v>871.31578947368416</v>
       </c>
       <c r="AA15" s="17">
         <f t="shared" si="13"/>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="AB15" s="134">
         <f t="shared" si="14"/>
-        <v>0.18290013829855961</v>
+        <v>0.18501769611882951</v>
       </c>
       <c r="AC15" s="135">
         <f t="shared" si="25"/>
@@ -3365,15 +3365,15 @@
       </c>
       <c r="AD15" s="134">
         <f t="shared" si="26"/>
-        <v>0.18278098527679207</v>
+        <v>0.18459370513618553</v>
       </c>
       <c r="AE15" s="134">
         <f t="shared" si="15"/>
-        <v>0.52705412500000004</v>
+        <v>0.53645250749999995</v>
       </c>
       <c r="AF15" s="134">
         <f t="shared" si="16"/>
-        <v>0.7529344642857142</v>
+        <v>0.73152614659090909</v>
       </c>
       <c r="AG15" s="134">
         <f>IFERROR(VLOOKUP(A15,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="K16" s="111">
         <f t="shared" si="21"/>
-        <v>0.22126483813257969</v>
+        <v>0.21990523910918736</v>
       </c>
       <c r="L16" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="O16" s="130">
         <f t="shared" si="6"/>
-        <v>27058.159544159542</v>
+        <v>30440.429487179485</v>
       </c>
       <c r="P16" s="129">
         <f t="shared" si="7"/>
@@ -3464,26 +3464,26 @@
       </c>
       <c r="Q16" s="109">
         <f t="shared" si="8"/>
-        <v>552890.63636363635</v>
+        <v>528851.91304347827</v>
       </c>
       <c r="R16" s="115">
         <f t="shared" si="23"/>
-        <v>0.21810540969350348</v>
-      </c>
-      <c r="S16" s="106">
+        <v>0.2168575158208659</v>
+      </c>
+      <c r="S16" s="106" t="str">
         <f t="shared" si="24"/>
-        <v>7207.9475795509024</v>
+        <v/>
       </c>
       <c r="T16" s="129">
         <f t="shared" si="9"/>
-        <v>0.8694651136363637</v>
+        <v>0.83166228260869568</v>
       </c>
       <c r="U16" s="131">
         <f t="shared" si="10"/>
-        <v>7.0715080116983145E-2</v>
+        <v>6.9160768452982815E-2</v>
       </c>
       <c r="V16" s="62">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W16" s="64">
         <v>31</v>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="Z16" s="133">
         <f t="shared" si="12"/>
-        <v>890.89908256880744</v>
+        <v>910.92105263157885</v>
       </c>
       <c r="AA16" s="17">
         <f t="shared" si="13"/>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="AB16" s="134">
         <f t="shared" si="14"/>
-        <v>0.22126483813257969</v>
+        <v>0.21990523910918736</v>
       </c>
       <c r="AC16" s="135">
         <f t="shared" si="25"/>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AD16" s="134">
         <f t="shared" si="26"/>
-        <v>0.21810540969350348</v>
+        <v>0.2168575158208659</v>
       </c>
       <c r="AE16" s="134">
         <f t="shared" si="15"/>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="AF16" s="134">
         <f t="shared" si="16"/>
-        <v>0.8694651136363637</v>
+        <v>0.83166228260869568</v>
       </c>
       <c r="AG16" s="134">
         <f>IFERROR(VLOOKUP(A16,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3536,9 +3536,9 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AK16" s="137">
+      <c r="AK16" s="137" t="str">
         <f t="shared" si="19"/>
-        <v>0.72</v>
+        <v/>
       </c>
       <c r="AL16" s="93">
         <v>0.9</v>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="K17" s="111">
         <f t="shared" si="21"/>
-        <v>0.1439326153621838</v>
+        <v>0.14304819719193898</v>
       </c>
       <c r="L17" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="O17" s="130">
         <f t="shared" si="6"/>
-        <v>42295.381766381761</v>
+        <v>47582.304487179485</v>
       </c>
       <c r="P17" s="129">
         <f t="shared" si="7"/>
@@ -3609,11 +3609,11 @@
       </c>
       <c r="Q17" s="109">
         <f t="shared" si="8"/>
-        <v>359654.95454545459</v>
+        <v>344017.78260869568</v>
       </c>
       <c r="R17" s="115">
         <f t="shared" si="23"/>
-        <v>0.14187740947351288</v>
+        <v>0.14106565542212784</v>
       </c>
       <c r="S17" s="106" t="str">
         <f t="shared" si="24"/>
@@ -3621,14 +3621,14 @@
       </c>
       <c r="T17" s="129">
         <f t="shared" si="9"/>
-        <v>0.56558642045454555</v>
+        <v>0.54099570652173923</v>
       </c>
       <c r="U17" s="131">
         <f t="shared" si="10"/>
-        <v>5.5000617868764666E-2</v>
+        <v>5.3791708796764412E-2</v>
       </c>
       <c r="V17" s="62">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W17" s="64">
         <v>31</v>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="Z17" s="133">
         <f t="shared" si="12"/>
-        <v>890.89908256880744</v>
+        <v>910.92105263157885</v>
       </c>
       <c r="AA17" s="17">
         <f t="shared" si="13"/>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="AB17" s="134">
         <f t="shared" si="14"/>
-        <v>0.1439326153621838</v>
+        <v>0.14304819719193898</v>
       </c>
       <c r="AC17" s="135">
         <f t="shared" si="25"/>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="AD17" s="134">
         <f t="shared" si="26"/>
-        <v>0.14187740947351288</v>
+        <v>0.14106565542212784</v>
       </c>
       <c r="AE17" s="134">
         <f t="shared" si="15"/>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="AF17" s="134">
         <f t="shared" si="16"/>
-        <v>0.56558642045454555</v>
+        <v>0.54099570652173923</v>
       </c>
       <c r="AG17" s="134">
         <f>IFERROR(VLOOKUP(A17,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="K18" s="111">
         <f t="shared" si="21"/>
-        <v>-1.1957213341768873E-2</v>
+        <v>-1.1883740232714728E-2</v>
       </c>
       <c r="L18" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="AB18" s="138">
         <f t="shared" si="14"/>
-        <v>-1.1957213341768873E-2</v>
+        <v>-1.1883740232714728E-2</v>
       </c>
       <c r="AC18" s="135">
         <f t="shared" si="25"/>
@@ -5699,31 +5699,31 @@
       </c>
       <c r="D32" s="153">
         <f>SUM(D13:D31)</f>
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E32" s="153">
         <f>SUM(E13:E31)</f>
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="F32" s="154">
         <f>IFERROR(SUM(F13:F31)/G10,)</f>
-        <v>1.6518921547113472</v>
+        <v>1.6477727730983589</v>
       </c>
       <c r="G32" s="155">
         <f>IFERROR(SUM(G13:G31)/G10,)</f>
-        <v>6561.9019608875806</v>
+        <v>6530.3531976246995</v>
       </c>
       <c r="H32" s="155">
         <f>IFERROR(SUM(H13:H31)/G10,)</f>
-        <v>4748.8095582025717</v>
+        <v>4738.1972976800744</v>
       </c>
       <c r="I32" s="155">
         <f>SUM(I13:I31)</f>
-        <v>1773322.88</v>
+        <v>1784286.73</v>
       </c>
       <c r="J32" s="156">
         <f>IFERROR(I32/C32,)</f>
-        <v>0.59110762666666661</v>
+        <v>0.59476224333333327</v>
       </c>
       <c r="K32" s="156">
         <f>SUM(K13:K31)</f>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="L32" s="155">
         <f>SUM(L13:L31)</f>
-        <v>7348.2748129883712</v>
+        <v>7607.7293313054006</v>
       </c>
       <c r="M32" s="155">
         <f>SUM(M13:M31)</f>
@@ -5739,16 +5739,16 @@
       </c>
       <c r="N32" s="155">
         <f>SUM(N13:N31)</f>
-        <v>1226677.1199999999</v>
+        <v>1215713.27</v>
       </c>
       <c r="O32" s="155">
         <f>SUM(O13:O31)</f>
-        <v>133941.45777777774</v>
+        <v>149313.65875</v>
       </c>
       <c r="P32" s="157"/>
       <c r="Q32" s="152">
         <f>SUM(Q13:Q31)</f>
-        <v>2534969.843896104</v>
+        <v>2438706.8672332014</v>
       </c>
       <c r="R32" s="156">
         <f>SUM(R13:R31)</f>
@@ -5756,16 +5756,16 @@
       </c>
       <c r="S32" s="155">
         <f>SUM(S13:S31)</f>
-        <v>28458.820936209788</v>
+        <v>20126.781202781549</v>
       </c>
       <c r="T32" s="158">
         <f>IFERROR(Q32/C32,)</f>
-        <v>0.84498994796536797</v>
+        <v>0.81290228907773376</v>
       </c>
       <c r="U32" s="165"/>
       <c r="V32" s="166">
         <f>SUM(V13:V31)</f>
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="W32" s="167">
         <f>SUM(W13:W31)</f>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="Z32" s="164">
         <f>SUM(Z13:Z31)</f>
-        <v>4414</v>
+        <v>4514.9999999999991</v>
       </c>
       <c r="AA32" s="162">
         <f>SUM(AA13:AA31)</f>
@@ -6948,25 +6948,25 @@
         <v>65</v>
       </c>
       <c r="B2" s="19">
-        <v>405566.88</v>
+        <v>410747.11</v>
       </c>
       <c r="C2" s="18">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D2" s="18">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E2" s="16">
         <f>IFERROR((D2/C2),"")</f>
-        <v>1.5294117647058822</v>
+        <v>1.536231884057971</v>
       </c>
       <c r="F2" s="17">
         <f>IFERROR((B2/C2),"")</f>
-        <v>5964.2188235294116</v>
+        <v>5952.8566666666666</v>
       </c>
       <c r="G2" s="17">
         <f>IFERROR((B2/D2),"")</f>
-        <v>3899.6815384615384</v>
+        <v>3874.9727358490563</v>
       </c>
       <c r="Q2" s="6" t="s">
         <v>38</v>
@@ -7012,25 +7012,25 @@
         <v>64</v>
       </c>
       <c r="B4" s="174">
-        <v>324341</v>
+        <v>330124.62</v>
       </c>
       <c r="C4" s="18">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D4" s="18">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E4" s="16">
         <f t="shared" si="0"/>
-        <v>1.2698412698412698</v>
+        <v>1.2424242424242424</v>
       </c>
       <c r="F4" s="17">
         <f t="shared" si="1"/>
-        <v>5148.269841269841</v>
+        <v>5001.8881818181817</v>
       </c>
       <c r="G4" s="17">
         <f t="shared" si="2"/>
-        <v>4054.2624999999998</v>
+        <v>4025.91</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">

--- a/EKİM SD KARNE.xlsx
+++ b/EKİM SD KARNE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\UYGULAMA İÇİN GEREKLİ DOSYALAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0BB84AB-B01B-4398-AEED-84E70CDDB3BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0FB50A9-9EEE-4990-AEDB-56BF68056D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2690,11 +2690,11 @@
       </c>
       <c r="B9" s="75">
         <f>I32</f>
-        <v>1784286.73</v>
+        <v>1892270</v>
       </c>
       <c r="C9" s="76">
         <f>IFERROR(B9/A9,)</f>
-        <v>0.59476224333333327</v>
+        <v>0.63075666666666663</v>
       </c>
       <c r="D9" s="168">
         <f>IFERROR(IF(B9&lt;=A9,A4,IF(AND(B9&gt;A9,B9&lt;B1),A4,IF(AND(B9&gt;=B1,B9&lt;C1),B4,IF(AND(B9&gt;=C1,B9&lt;D1),C4,IF(AND(B9&gt;=D1,B9&lt;E1),D4,IF(AND(B9&gt;=E1,B9&lt;F1),E4,IF(AND(B9&gt;=F1,B9&lt;G1),F4,IF(AND(B9&gt;=G1,B9&lt;H1),G4,IF(AND(B9&gt;=H1,B9&lt;I1),H4,IF(AND(B9&gt;=I1,B9&lt;J1),I4,IF(AND(B9&gt;=J1,B9&lt;K1),J4,IF(B9&gt;=K4,K4,K4)))))))))))),)</f>
@@ -2761,27 +2761,27 @@
       </c>
       <c r="H10" s="83">
         <f ca="1">B11-M10</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I10" s="84">
         <f>C11</f>
-        <v>4515</v>
+        <v>4805</v>
       </c>
       <c r="J10" s="85">
         <f ca="1">I10/H10</f>
-        <v>196.30434782608697</v>
+        <v>200.20833333333334</v>
       </c>
       <c r="K10" s="85">
         <f>IFERROR(I10/G10,)</f>
-        <v>903</v>
+        <v>961</v>
       </c>
       <c r="L10" s="86">
         <f ca="1">IFERROR(J10/G10,)</f>
-        <v>39.260869565217391</v>
+        <v>40.041666666666671</v>
       </c>
       <c r="M10" s="87">
         <f ca="1">(M11-A11)+B11</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N10" s="2">
         <f>LOOKUP(A9,'PRİM HAVUZU (SV SİSTEM)'!$A:$A,'PRİM HAVUZU (SV SİSTEM)'!$C:$C)*A9</f>
@@ -2804,14 +2804,14 @@
     <row r="11" spans="1:58" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="169">
         <f ca="1">TODAY()</f>
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="B11" s="170">
         <f ca="1">(N11-M11)+1</f>
         <v>31</v>
       </c>
       <c r="C11" s="171">
-        <v>4515</v>
+        <v>4805</v>
       </c>
       <c r="F11" s="66"/>
       <c r="K11" s="89"/>
@@ -2977,39 +2977,39 @@
       </c>
       <c r="D13" s="107" cm="1">
         <f t="array" ref="D13:D31">DATA!C2:C20</f>
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E13" s="107" cm="1">
         <f t="array" ref="E13:E31">DATA!D2:D20</f>
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F13" s="108">
         <f>DATA!E2</f>
-        <v>1.536231884057971</v>
+        <v>1.5211267605633803</v>
       </c>
       <c r="G13" s="109">
         <f>DATA!F2</f>
-        <v>5952.8566666666666</v>
+        <v>5937.5211267605637</v>
       </c>
       <c r="H13" s="109">
         <f>DATA!G2</f>
-        <v>3874.9727358490563</v>
+        <v>3903.3703703703704</v>
       </c>
       <c r="I13" s="106" cm="1">
         <f t="array" ref="I13:I31">DATA!B2:B20</f>
-        <v>410747.11</v>
+        <v>421564</v>
       </c>
       <c r="J13" s="110">
         <f t="shared" ref="J13:J31" si="3">IFERROR(I13/C13,0)</f>
-        <v>0.86124394032258067</v>
+        <v>0.88392451612903233</v>
       </c>
       <c r="K13" s="111">
         <f>IFERROR(I13/$I$32,)</f>
-        <v>0.23020241259094046</v>
+        <v>0.2227821611080871</v>
       </c>
       <c r="L13" s="112">
         <f t="shared" ref="L13:L31" si="4">IFERROR(IF(J13&lt;0.85,"",IF(AND(J13&gt;0.85,J13&lt;1),$M$2*AB13*AJ13,$M$2*AB13*AJ13)),"")</f>
-        <v>7607.7293313054006</v>
+        <v>7771.5329080945103</v>
       </c>
       <c r="M13" s="113">
         <f t="shared" ref="M13:M31" si="5">IFERROR((($E$9+$F$9)*AC13),"")</f>
@@ -3017,38 +3017,38 @@
       </c>
       <c r="N13" s="114">
         <f>IFERROR(IF(C13-I13&lt;0,"",C13-I13),"")</f>
-        <v>66175.966923076892</v>
+        <v>55359.076923076878</v>
       </c>
       <c r="O13" s="114">
         <f t="shared" ref="O13:O31" si="6">IFERROR(IF(N13/(W13-V13)&gt;0,N13/(W13-V13),""),"")</f>
-        <v>8271.9958653846115</v>
+        <v>7908.439560439554</v>
       </c>
       <c r="P13" s="110">
         <f t="shared" ref="P13:P31" si="7">IFERROR(I13/C13,0)</f>
-        <v>0.86124394032258067</v>
+        <v>0.88392451612903233</v>
       </c>
       <c r="Q13" s="109">
         <f t="shared" ref="Q13:Q31" si="8">IF(V13="",0,IF(W13=V13,I13,(I13/V13)*(W13-V13)+I13))</f>
-        <v>553615.66999999993</v>
+        <v>544520.16666666663</v>
       </c>
       <c r="R13" s="115">
         <f>IFERROR(Q13/$Q$32,)</f>
-        <v>0.22701197812597146</v>
+        <v>0.21990806744259903</v>
       </c>
       <c r="S13" s="106">
         <f>IFERROR(IF(T13&lt;0.85,"",IF(AND(T13&gt;0.85,T13&lt;1),$M$2*AD13*AK13,$M$2*AD13*AK13)),"")</f>
-        <v>12087.025763339225</v>
+        <v>11506.909537001437</v>
       </c>
       <c r="T13" s="110">
         <f t="shared" ref="T13:T31" si="9">IFERROR(Q13/C13,0)</f>
-        <v>1.1608070500000001</v>
+        <v>1.1417358333333334</v>
       </c>
       <c r="U13" s="116">
         <f t="shared" ref="U13:U31" si="10">IFERROR(D13/Z13,0)</f>
-        <v>7.5747508305647845E-2</v>
+        <v>7.326569545612209E-2</v>
       </c>
       <c r="V13" s="62">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W13" s="63">
         <v>31</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z13" s="118">
         <f t="shared" ref="Z13:Z31" si="12">(V13/$V$32)*$I$10</f>
-        <v>910.92105263157885</v>
+        <v>969.07563025210084</v>
       </c>
       <c r="AA13" s="119">
         <f t="shared" ref="AA13:AA31" si="13">IFERROR(((Y13/$Y$32)*$A$9),"")</f>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AB13" s="120">
         <f t="shared" ref="AB13:AB31" si="14">I13/$I$32</f>
-        <v>0.23020241259094046</v>
+        <v>0.2227821611080871</v>
       </c>
       <c r="AC13" s="121">
         <f>AA13/$C$32</f>
@@ -3075,15 +3075,15 @@
       </c>
       <c r="AD13" s="120">
         <f>Q13/$Q$32</f>
-        <v>0.22701197812597146</v>
+        <v>0.21990806744259903</v>
       </c>
       <c r="AE13" s="120">
         <f t="shared" ref="AE13:AE31" si="15">I13/C13</f>
-        <v>0.86124394032258067</v>
+        <v>0.88392451612903233</v>
       </c>
       <c r="AF13" s="120">
         <f t="shared" ref="AF13:AF31" si="16">Q13/C13</f>
-        <v>1.1608070500000001</v>
+        <v>1.1417358333333334</v>
       </c>
       <c r="AG13" s="120">
         <f>IFERROR(VLOOKUP(A13,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3099,11 +3099,11 @@
       </c>
       <c r="AJ13" s="121">
         <f t="shared" ref="AJ13:AJ31" si="18">IFERROR(LOOKUP(AE13,AL:AL,AM:AM),"")</f>
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
       <c r="AK13" s="123">
         <f t="shared" ref="AK13:AK31" si="19">IFERROR(LOOKUP(AF13,AL:AL,AM:AM),"")</f>
-        <v>1.1599999999999999</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="AL13" s="93">
         <v>0.87</v>
@@ -3124,33 +3124,33 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D14" s="126">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E14" s="126">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="F14" s="127">
         <f>DATA!E3</f>
-        <v>1.564516129032258</v>
+        <v>1.5555555555555556</v>
       </c>
       <c r="G14" s="128">
         <f>DATA!F3</f>
-        <v>6725.9032258064517</v>
+        <v>6461.791666666667</v>
       </c>
       <c r="H14" s="128">
         <f>DATA!G3</f>
-        <v>4299.0309278350514</v>
+        <v>4154.0089285714284</v>
       </c>
       <c r="I14" s="125">
-        <v>417006</v>
+        <v>465249</v>
       </c>
       <c r="J14" s="129">
         <f t="shared" si="3"/>
-        <v>0.65577556451612906</v>
+        <v>0.73164157258064522</v>
       </c>
       <c r="K14" s="111">
         <f t="shared" ref="K14:K31" si="21">IFERROR(I14/$I$32,)</f>
-        <v>0.23371019522181841</v>
+        <v>0.24586819005744423</v>
       </c>
       <c r="L14" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3162,38 +3162,38 @@
       </c>
       <c r="N14" s="130">
         <f t="shared" ref="N14:N31" si="22">IFERROR(IF(C14-I14&lt;0,"",C14-I14),"")</f>
-        <v>218891.43589743588</v>
+        <v>170648.43589743588</v>
       </c>
       <c r="O14" s="130">
         <f t="shared" si="6"/>
-        <v>27361.429487179485</v>
+        <v>24378.347985347984</v>
       </c>
       <c r="P14" s="129">
         <f t="shared" si="7"/>
-        <v>0.65577556451612906</v>
+        <v>0.73164157258064522</v>
       </c>
       <c r="Q14" s="109">
         <f t="shared" si="8"/>
-        <v>562051.56521739135</v>
+        <v>600946.625</v>
       </c>
       <c r="R14" s="115">
         <f t="shared" ref="R14:R31" si="23">IFERROR(Q14/$Q$32,)</f>
-        <v>0.23047114549484932</v>
+        <v>0.24269626550085341</v>
       </c>
       <c r="S14" s="106">
         <f t="shared" ref="S14:S31" si="24">IFERROR(IF(T14&lt;0.85,"",IF(AND(T14&gt;0.85,T14&lt;1),$M$2*AD14*AK14,$M$2*AD14*AK14)),"")</f>
-        <v>8039.7554394423232</v>
+        <v>9802.9875561104709</v>
       </c>
       <c r="T14" s="129">
         <f t="shared" si="9"/>
-        <v>0.88387141304347838</v>
+        <v>0.94503703125000005</v>
       </c>
       <c r="U14" s="131">
         <f t="shared" si="10"/>
-        <v>6.8062978477538644E-2</v>
+        <v>7.4297606659729454E-2</v>
       </c>
       <c r="V14" s="62">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W14" s="64">
         <v>31</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="Z14" s="133">
         <f t="shared" si="12"/>
-        <v>910.92105263157885</v>
+        <v>969.07563025210084</v>
       </c>
       <c r="AA14" s="17">
         <f t="shared" si="13"/>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="AB14" s="134">
         <f t="shared" si="14"/>
-        <v>0.23371019522181841</v>
+        <v>0.24586819005744423</v>
       </c>
       <c r="AC14" s="135">
         <f t="shared" ref="AC14:AC31" si="25">AA14/$C$32</f>
@@ -3220,15 +3220,15 @@
       </c>
       <c r="AD14" s="134">
         <f t="shared" ref="AD14:AD18" si="26">Q14/$Q$32</f>
-        <v>0.23047114549484932</v>
+        <v>0.24269626550085341</v>
       </c>
       <c r="AE14" s="134">
         <f t="shared" si="15"/>
-        <v>0.65577556451612906</v>
+        <v>0.73164157258064522</v>
       </c>
       <c r="AF14" s="134">
         <f t="shared" si="16"/>
-        <v>0.88387141304347838</v>
+        <v>0.94503703125000005</v>
       </c>
       <c r="AG14" s="134">
         <f>IFERROR(VLOOKUP(A14,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="AK14" s="137">
         <f t="shared" si="19"/>
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="AL14" s="93">
         <v>0.88</v>
@@ -3269,33 +3269,33 @@
         <v>615384.61538461538</v>
       </c>
       <c r="D15" s="126">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E15" s="126">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F15" s="127">
         <f>DATA!E4</f>
-        <v>1.2424242424242424</v>
+        <v>1.2608695652173914</v>
       </c>
       <c r="G15" s="128">
         <f>DATA!F4</f>
-        <v>5001.8881818181817</v>
+        <v>5206.623188405797</v>
       </c>
       <c r="H15" s="128">
         <f>DATA!G4</f>
-        <v>4025.91</v>
+        <v>4129.3908045977014</v>
       </c>
       <c r="I15" s="125">
-        <v>330124.62</v>
+        <v>359257</v>
       </c>
       <c r="J15" s="129">
         <f t="shared" si="3"/>
-        <v>0.53645250749999995</v>
+        <v>0.58379262499999995</v>
       </c>
       <c r="K15" s="111">
         <f t="shared" si="21"/>
-        <v>0.18501769611882951</v>
+        <v>0.18985504182806892</v>
       </c>
       <c r="L15" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3307,23 +3307,23 @@
       </c>
       <c r="N15" s="130">
         <f t="shared" si="22"/>
-        <v>285259.99538461538</v>
+        <v>256127.61538461538</v>
       </c>
       <c r="O15" s="130">
         <f t="shared" si="6"/>
-        <v>35657.499423076923</v>
+        <v>36589.659340659338</v>
       </c>
       <c r="P15" s="129">
         <f t="shared" si="7"/>
-        <v>0.53645250749999995</v>
+        <v>0.58379262499999995</v>
       </c>
       <c r="Q15" s="109">
         <f t="shared" si="8"/>
-        <v>450169.93636363634</v>
+        <v>468596.08695652173</v>
       </c>
       <c r="R15" s="115">
         <f t="shared" si="23"/>
-        <v>0.18459370513618553</v>
+        <v>0.1892456261530065</v>
       </c>
       <c r="S15" s="106" t="str">
         <f t="shared" si="24"/>
@@ -3331,14 +3331,14 @@
       </c>
       <c r="T15" s="129">
         <f t="shared" si="9"/>
-        <v>0.73152614659090909</v>
+        <v>0.76146864130434777</v>
       </c>
       <c r="U15" s="131">
         <f t="shared" si="10"/>
-        <v>7.5747508305647845E-2</v>
+        <v>7.4297606659729454E-2</v>
       </c>
       <c r="V15" s="62">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W15" s="64">
         <v>30</v>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="Z15" s="133">
         <f t="shared" si="12"/>
-        <v>871.31578947368416</v>
+        <v>928.69747899159665</v>
       </c>
       <c r="AA15" s="17">
         <f t="shared" si="13"/>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="AB15" s="134">
         <f t="shared" si="14"/>
-        <v>0.18501769611882951</v>
+        <v>0.18985504182806892</v>
       </c>
       <c r="AC15" s="135">
         <f t="shared" si="25"/>
@@ -3365,15 +3365,15 @@
       </c>
       <c r="AD15" s="134">
         <f t="shared" si="26"/>
-        <v>0.18459370513618553</v>
+        <v>0.1892456261530065</v>
       </c>
       <c r="AE15" s="134">
         <f t="shared" si="15"/>
-        <v>0.53645250749999995</v>
+        <v>0.58379262499999995</v>
       </c>
       <c r="AF15" s="134">
         <f t="shared" si="16"/>
-        <v>0.73152614659090909</v>
+        <v>0.76146864130434777</v>
       </c>
       <c r="AG15" s="134">
         <f>IFERROR(VLOOKUP(A15,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3414,33 +3414,33 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D16" s="126">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E16" s="126">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F16" s="127">
         <f>DATA!E5</f>
-        <v>1.6507936507936507</v>
+        <v>1.6515151515151516</v>
       </c>
       <c r="G16" s="128">
         <f>DATA!F5</f>
-        <v>6228.1587301587306</v>
+        <v>6244.924242424242</v>
       </c>
       <c r="H16" s="128">
         <f>DATA!G5</f>
-        <v>3772.8269230769229</v>
+        <v>3781.330275229358</v>
       </c>
       <c r="I16" s="125">
-        <v>392374</v>
+        <v>412165</v>
       </c>
       <c r="J16" s="129">
         <f t="shared" si="3"/>
-        <v>0.61703975806451616</v>
+        <v>0.64816270161290324</v>
       </c>
       <c r="K16" s="111">
         <f t="shared" si="21"/>
-        <v>0.21990523910918736</v>
+        <v>0.217815110951397</v>
       </c>
       <c r="L16" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3452,23 +3452,23 @@
       </c>
       <c r="N16" s="130">
         <f t="shared" ref="N16:N25" si="28">IFERROR(IF(C16-I16&lt;0,"",C16-I16),"")</f>
-        <v>243523.43589743588</v>
+        <v>223732.43589743588</v>
       </c>
       <c r="O16" s="130">
         <f t="shared" si="6"/>
-        <v>30440.429487179485</v>
+        <v>31961.776556776553</v>
       </c>
       <c r="P16" s="129">
         <f t="shared" si="7"/>
-        <v>0.61703975806451616</v>
+        <v>0.64816270161290324</v>
       </c>
       <c r="Q16" s="109">
         <f t="shared" si="8"/>
-        <v>528851.91304347827</v>
+        <v>532379.79166666663</v>
       </c>
       <c r="R16" s="115">
         <f t="shared" si="23"/>
-        <v>0.2168575158208659</v>
+        <v>0.21500509677647719</v>
       </c>
       <c r="S16" s="106" t="str">
         <f t="shared" si="24"/>
@@ -3476,14 +3476,14 @@
       </c>
       <c r="T16" s="129">
         <f t="shared" si="9"/>
-        <v>0.83166228260869568</v>
+        <v>0.83721015624999995</v>
       </c>
       <c r="U16" s="131">
         <f t="shared" si="10"/>
-        <v>6.9160768452982815E-2</v>
+        <v>6.8106139438085328E-2</v>
       </c>
       <c r="V16" s="62">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W16" s="64">
         <v>31</v>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="Z16" s="133">
         <f t="shared" si="12"/>
-        <v>910.92105263157885</v>
+        <v>969.07563025210084</v>
       </c>
       <c r="AA16" s="17">
         <f t="shared" si="13"/>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="AB16" s="134">
         <f t="shared" si="14"/>
-        <v>0.21990523910918736</v>
+        <v>0.217815110951397</v>
       </c>
       <c r="AC16" s="135">
         <f t="shared" si="25"/>
@@ -3510,15 +3510,15 @@
       </c>
       <c r="AD16" s="134">
         <f t="shared" si="26"/>
-        <v>0.2168575158208659</v>
+        <v>0.21500509677647719</v>
       </c>
       <c r="AE16" s="134">
         <f t="shared" si="15"/>
-        <v>0.61703975806451616</v>
+        <v>0.64816270161290324</v>
       </c>
       <c r="AF16" s="134">
         <f t="shared" si="16"/>
-        <v>0.83166228260869568</v>
+        <v>0.83721015624999995</v>
       </c>
       <c r="AG16" s="134">
         <f>IFERROR(VLOOKUP(A16,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="K17" s="111">
         <f t="shared" si="21"/>
-        <v>0.14304819719193898</v>
+        <v>0.13488508510941885</v>
       </c>
       <c r="L17" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="O17" s="130">
         <f t="shared" si="6"/>
-        <v>47582.304487179485</v>
+        <v>54379.776556776553</v>
       </c>
       <c r="P17" s="129">
         <f t="shared" si="7"/>
@@ -3609,11 +3609,11 @@
       </c>
       <c r="Q17" s="109">
         <f t="shared" si="8"/>
-        <v>344017.78260869568</v>
+        <v>329683.70833333337</v>
       </c>
       <c r="R17" s="115">
         <f t="shared" si="23"/>
-        <v>0.14106565542212784</v>
+        <v>0.13314494412706385</v>
       </c>
       <c r="S17" s="106" t="str">
         <f t="shared" si="24"/>
@@ -3621,14 +3621,14 @@
       </c>
       <c r="T17" s="129">
         <f t="shared" si="9"/>
-        <v>0.54099570652173923</v>
+        <v>0.51845421875000008</v>
       </c>
       <c r="U17" s="131">
         <f t="shared" si="10"/>
-        <v>5.3791708796764412E-2</v>
+        <v>5.0563648976760321E-2</v>
       </c>
       <c r="V17" s="62">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W17" s="64">
         <v>31</v>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="Z17" s="133">
         <f t="shared" si="12"/>
-        <v>910.92105263157885</v>
+        <v>969.07563025210084</v>
       </c>
       <c r="AA17" s="17">
         <f t="shared" si="13"/>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="AB17" s="134">
         <f t="shared" si="14"/>
-        <v>0.14304819719193898</v>
+        <v>0.13488508510941885</v>
       </c>
       <c r="AC17" s="135">
         <f t="shared" si="25"/>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="AD17" s="134">
         <f t="shared" si="26"/>
-        <v>0.14106565542212784</v>
+        <v>0.13314494412706385</v>
       </c>
       <c r="AE17" s="134">
         <f t="shared" si="15"/>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="AF17" s="134">
         <f t="shared" si="16"/>
-        <v>0.54099570652173923</v>
+        <v>0.51845421875000008</v>
       </c>
       <c r="AG17" s="134">
         <f>IFERROR(VLOOKUP(A17,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="K18" s="111">
         <f t="shared" si="21"/>
-        <v>-1.1883740232714728E-2</v>
+        <v>-1.1205589054416125E-2</v>
       </c>
       <c r="L18" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="AB18" s="138">
         <f t="shared" si="14"/>
-        <v>-1.1883740232714728E-2</v>
+        <v>-1.1205589054416125E-2</v>
       </c>
       <c r="AC18" s="135">
         <f t="shared" si="25"/>
@@ -5699,39 +5699,39 @@
       </c>
       <c r="D32" s="153">
         <f>SUM(D13:D31)</f>
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="E32" s="153">
         <f>SUM(E13:E31)</f>
-        <v>444</v>
+        <v>471</v>
       </c>
       <c r="F32" s="154">
         <f>IFERROR(SUM(F13:F31)/G10,)</f>
-        <v>1.6477727730983589</v>
+        <v>1.6467929984070302</v>
       </c>
       <c r="G32" s="155">
         <f>IFERROR(SUM(G13:G31)/G10,)</f>
-        <v>6530.3531976246995</v>
+        <v>6518.7638815861474</v>
       </c>
       <c r="H32" s="155">
         <f>IFERROR(SUM(H13:H31)/G10,)</f>
-        <v>4738.1972976800744</v>
+        <v>4737.2692560816404</v>
       </c>
       <c r="I32" s="155">
         <f>SUM(I13:I31)</f>
-        <v>1784286.73</v>
+        <v>1892270</v>
       </c>
       <c r="J32" s="156">
         <f>IFERROR(I32/C32,)</f>
-        <v>0.59476224333333327</v>
+        <v>0.63075666666666663</v>
       </c>
       <c r="K32" s="156">
         <f>SUM(K13:K31)</f>
-        <v>1</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="L32" s="155">
         <f>SUM(L13:L31)</f>
-        <v>7607.7293313054006</v>
+        <v>7771.5329080945103</v>
       </c>
       <c r="M32" s="155">
         <f>SUM(M13:M31)</f>
@@ -5739,16 +5739,16 @@
       </c>
       <c r="N32" s="155">
         <f>SUM(N13:N31)</f>
-        <v>1215713.27</v>
+        <v>1107730</v>
       </c>
       <c r="O32" s="155">
         <f>SUM(O13:O31)</f>
-        <v>149313.65875</v>
+        <v>155217.99999999997</v>
       </c>
       <c r="P32" s="157"/>
       <c r="Q32" s="152">
         <f>SUM(Q13:Q31)</f>
-        <v>2438706.8672332014</v>
+        <v>2476126.3786231885</v>
       </c>
       <c r="R32" s="156">
         <f>SUM(R13:R31)</f>
@@ -5756,16 +5756,16 @@
       </c>
       <c r="S32" s="155">
         <f>SUM(S13:S31)</f>
-        <v>20126.781202781549</v>
+        <v>21309.897093111907</v>
       </c>
       <c r="T32" s="158">
         <f>IFERROR(Q32/C32,)</f>
-        <v>0.81290228907773376</v>
+        <v>0.82537545954106284</v>
       </c>
       <c r="U32" s="165"/>
       <c r="V32" s="166">
         <f>SUM(V13:V31)</f>
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="W32" s="167">
         <f>SUM(W13:W31)</f>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="Z32" s="164">
         <f>SUM(Z13:Z31)</f>
-        <v>4514.9999999999991</v>
+        <v>4805</v>
       </c>
       <c r="AA32" s="162">
         <f>SUM(AA13:AA31)</f>
@@ -6948,25 +6948,25 @@
         <v>65</v>
       </c>
       <c r="B2" s="19">
-        <v>410747.11</v>
+        <v>421564</v>
       </c>
       <c r="C2" s="18">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D2" s="18">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E2" s="16">
         <f>IFERROR((D2/C2),"")</f>
-        <v>1.536231884057971</v>
+        <v>1.5211267605633803</v>
       </c>
       <c r="F2" s="17">
         <f>IFERROR((B2/C2),"")</f>
-        <v>5952.8566666666666</v>
+        <v>5937.5211267605637</v>
       </c>
       <c r="G2" s="17">
         <f>IFERROR((B2/D2),"")</f>
-        <v>3874.9727358490563</v>
+        <v>3903.3703703703704</v>
       </c>
       <c r="Q2" s="6" t="s">
         <v>38</v>
@@ -6980,25 +6980,25 @@
         <v>67</v>
       </c>
       <c r="B3" s="19">
-        <v>417006</v>
+        <v>465249</v>
       </c>
       <c r="C3" s="18">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D3" s="18">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="E3" s="16">
         <f t="shared" ref="E3:E20" si="0">IFERROR((D3/C3),"")</f>
-        <v>1.564516129032258</v>
+        <v>1.5555555555555556</v>
       </c>
       <c r="F3" s="17">
         <f t="shared" ref="F3:F20" si="1">IFERROR((B3/C3),"")</f>
-        <v>6725.9032258064517</v>
+        <v>6461.791666666667</v>
       </c>
       <c r="G3" s="17">
         <f t="shared" ref="G3:G20" si="2">IFERROR((B3/D3),"")</f>
-        <v>4299.0309278350514</v>
+        <v>4154.0089285714284</v>
       </c>
       <c r="Q3" s="6" t="s">
         <v>40</v>
@@ -7012,25 +7012,25 @@
         <v>64</v>
       </c>
       <c r="B4" s="174">
-        <v>330124.62</v>
+        <v>359257</v>
       </c>
       <c r="C4" s="18">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D4" s="18">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E4" s="16">
         <f t="shared" si="0"/>
-        <v>1.2424242424242424</v>
+        <v>1.2608695652173914</v>
       </c>
       <c r="F4" s="17">
         <f t="shared" si="1"/>
-        <v>5001.8881818181817</v>
+        <v>5206.623188405797</v>
       </c>
       <c r="G4" s="17">
         <f t="shared" si="2"/>
-        <v>4025.91</v>
+        <v>4129.3908045977014</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -7038,25 +7038,25 @@
         <v>66</v>
       </c>
       <c r="B5" s="175">
-        <v>392374</v>
+        <v>412165</v>
       </c>
       <c r="C5" s="18">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D5" s="18">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E5" s="16">
         <f t="shared" si="0"/>
-        <v>1.6507936507936507</v>
+        <v>1.6515151515151516</v>
       </c>
       <c r="F5" s="17">
         <f t="shared" si="1"/>
-        <v>6228.1587301587306</v>
+        <v>6244.924242424242</v>
       </c>
       <c r="G5" s="17">
         <f t="shared" si="2"/>
-        <v>3772.8269230769229</v>
+        <v>3781.330275229358</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">

--- a/EKİM SD KARNE.xlsx
+++ b/EKİM SD KARNE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\UYGULAMA İÇİN GEREKLİ DOSYALAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0FB50A9-9EEE-4990-AEDB-56BF68056D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88423AF3-F90E-46A7-8BF1-4323FAA12362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2690,11 +2690,11 @@
       </c>
       <c r="B9" s="75">
         <f>I32</f>
-        <v>1892270</v>
+        <v>2045514</v>
       </c>
       <c r="C9" s="76">
         <f>IFERROR(B9/A9,)</f>
-        <v>0.63075666666666663</v>
+        <v>0.68183800000000006</v>
       </c>
       <c r="D9" s="168">
         <f>IFERROR(IF(B9&lt;=A9,A4,IF(AND(B9&gt;A9,B9&lt;B1),A4,IF(AND(B9&gt;=B1,B9&lt;C1),B4,IF(AND(B9&gt;=C1,B9&lt;D1),C4,IF(AND(B9&gt;=D1,B9&lt;E1),D4,IF(AND(B9&gt;=E1,B9&lt;F1),E4,IF(AND(B9&gt;=F1,B9&lt;G1),F4,IF(AND(B9&gt;=G1,B9&lt;H1),G4,IF(AND(B9&gt;=H1,B9&lt;I1),H4,IF(AND(B9&gt;=I1,B9&lt;J1),I4,IF(AND(B9&gt;=J1,B9&lt;K1),J4,IF(B9&gt;=K4,K4,K4)))))))))))),)</f>
@@ -2761,27 +2761,27 @@
       </c>
       <c r="H10" s="83">
         <f ca="1">B11-M10</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I10" s="84">
         <f>C11</f>
-        <v>4805</v>
+        <v>5117</v>
       </c>
       <c r="J10" s="85">
         <f ca="1">I10/H10</f>
-        <v>200.20833333333334</v>
+        <v>204.68</v>
       </c>
       <c r="K10" s="85">
         <f>IFERROR(I10/G10,)</f>
-        <v>961</v>
+        <v>1023.4</v>
       </c>
       <c r="L10" s="86">
         <f ca="1">IFERROR(J10/G10,)</f>
-        <v>40.041666666666671</v>
+        <v>40.936</v>
       </c>
       <c r="M10" s="87">
         <f ca="1">(M11-A11)+B11</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N10" s="2">
         <f>LOOKUP(A9,'PRİM HAVUZU (SV SİSTEM)'!$A:$A,'PRİM HAVUZU (SV SİSTEM)'!$C:$C)*A9</f>
@@ -2804,14 +2804,14 @@
     <row r="11" spans="1:58" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="169">
         <f ca="1">TODAY()</f>
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="B11" s="170">
         <f ca="1">(N11-M11)+1</f>
         <v>31</v>
       </c>
       <c r="C11" s="171">
-        <v>4805</v>
+        <v>5117</v>
       </c>
       <c r="F11" s="66"/>
       <c r="K11" s="89"/>
@@ -2977,39 +2977,39 @@
       </c>
       <c r="D13" s="107" cm="1">
         <f t="array" ref="D13:D31">DATA!C2:C20</f>
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E13" s="107" cm="1">
         <f t="array" ref="E13:E31">DATA!D2:D20</f>
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F13" s="108">
         <f>DATA!E2</f>
-        <v>1.5211267605633803</v>
+        <v>1.52</v>
       </c>
       <c r="G13" s="109">
         <f>DATA!F2</f>
-        <v>5937.5211267605637</v>
+        <v>5993.44</v>
       </c>
       <c r="H13" s="109">
         <f>DATA!G2</f>
-        <v>3903.3703703703704</v>
+        <v>3943.0526315789475</v>
       </c>
       <c r="I13" s="106" cm="1">
         <f t="array" ref="I13:I31">DATA!B2:B20</f>
-        <v>421564</v>
+        <v>449508</v>
       </c>
       <c r="J13" s="110">
         <f t="shared" ref="J13:J31" si="3">IFERROR(I13/C13,0)</f>
-        <v>0.88392451612903233</v>
+        <v>0.94251677419354851</v>
       </c>
       <c r="K13" s="111">
         <f>IFERROR(I13/$I$32,)</f>
-        <v>0.2227821611080871</v>
+        <v>0.21975307917716524</v>
       </c>
       <c r="L13" s="112">
         <f t="shared" ref="L13:L31" si="4">IFERROR(IF(J13&lt;0.85,"",IF(AND(J13&gt;0.85,J13&lt;1),$M$2*AB13*AJ13,$M$2*AB13*AJ13)),"")</f>
-        <v>7771.5329080945103</v>
+        <v>8876.2663741240576</v>
       </c>
       <c r="M13" s="113">
         <f t="shared" ref="M13:M31" si="5">IFERROR((($E$9+$F$9)*AC13),"")</f>
@@ -3017,38 +3017,38 @@
       </c>
       <c r="N13" s="114">
         <f>IFERROR(IF(C13-I13&lt;0,"",C13-I13),"")</f>
-        <v>55359.076923076878</v>
+        <v>27415.076923076878</v>
       </c>
       <c r="O13" s="114">
         <f t="shared" ref="O13:O31" si="6">IFERROR(IF(N13/(W13-V13)&gt;0,N13/(W13-V13),""),"")</f>
-        <v>7908.439560439554</v>
+        <v>4569.17948717948</v>
       </c>
       <c r="P13" s="110">
         <f t="shared" ref="P13:P31" si="7">IFERROR(I13/C13,0)</f>
-        <v>0.88392451612903233</v>
+        <v>0.94251677419354851</v>
       </c>
       <c r="Q13" s="109">
         <f t="shared" ref="Q13:Q31" si="8">IF(V13="",0,IF(W13=V13,I13,(I13/V13)*(W13-V13)+I13))</f>
-        <v>544520.16666666663</v>
+        <v>557389.92000000004</v>
       </c>
       <c r="R13" s="115">
         <f>IFERROR(Q13/$Q$32,)</f>
-        <v>0.21990806744259903</v>
+        <v>0.21714892624731755</v>
       </c>
       <c r="S13" s="106">
         <f>IFERROR(IF(T13&lt;0.85,"",IF(AND(T13&gt;0.85,T13&lt;1),$M$2*AD13*AK13,$M$2*AD13*AK13)),"")</f>
-        <v>11506.909537001437</v>
+        <v>11561.877429112175</v>
       </c>
       <c r="T13" s="110">
         <f t="shared" ref="T13:T31" si="9">IFERROR(Q13/C13,0)</f>
-        <v>1.1417358333333334</v>
+        <v>1.1687208000000002</v>
       </c>
       <c r="U13" s="116">
         <f t="shared" ref="U13:U31" si="10">IFERROR(D13/Z13,0)</f>
-        <v>7.326569545612209E-2</v>
+        <v>7.2698846980652737E-2</v>
       </c>
       <c r="V13" s="62">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="W13" s="63">
         <v>31</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z13" s="118">
         <f t="shared" ref="Z13:Z31" si="12">(V13/$V$32)*$I$10</f>
-        <v>969.07563025210084</v>
+        <v>1031.6532258064515</v>
       </c>
       <c r="AA13" s="119">
         <f t="shared" ref="AA13:AA31" si="13">IFERROR(((Y13/$Y$32)*$A$9),"")</f>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AB13" s="120">
         <f t="shared" ref="AB13:AB31" si="14">I13/$I$32</f>
-        <v>0.2227821611080871</v>
+        <v>0.21975307917716524</v>
       </c>
       <c r="AC13" s="121">
         <f>AA13/$C$32</f>
@@ -3075,15 +3075,15 @@
       </c>
       <c r="AD13" s="120">
         <f>Q13/$Q$32</f>
-        <v>0.21990806744259903</v>
+        <v>0.21714892624731755</v>
       </c>
       <c r="AE13" s="120">
         <f t="shared" ref="AE13:AE31" si="15">I13/C13</f>
-        <v>0.88392451612903233</v>
+        <v>0.94251677419354851</v>
       </c>
       <c r="AF13" s="120">
         <f t="shared" ref="AF13:AF31" si="16">Q13/C13</f>
-        <v>1.1417358333333334</v>
+        <v>1.1687208000000002</v>
       </c>
       <c r="AG13" s="120">
         <f>IFERROR(VLOOKUP(A13,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3099,11 +3099,11 @@
       </c>
       <c r="AJ13" s="121">
         <f t="shared" ref="AJ13:AJ31" si="18">IFERROR(LOOKUP(AE13,AL:AL,AM:AM),"")</f>
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="AK13" s="123">
         <f t="shared" ref="AK13:AK31" si="19">IFERROR(LOOKUP(AF13,AL:AL,AM:AM),"")</f>
-        <v>1.1399999999999999</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="AL13" s="93">
         <v>0.87</v>
@@ -3124,33 +3124,33 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D14" s="126">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E14" s="126">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F14" s="127">
         <f>DATA!E3</f>
-        <v>1.5555555555555556</v>
+        <v>1.5384615384615385</v>
       </c>
       <c r="G14" s="128">
         <f>DATA!F3</f>
-        <v>6461.791666666667</v>
+        <v>6406.4102564102568</v>
       </c>
       <c r="H14" s="128">
         <f>DATA!G3</f>
-        <v>4154.0089285714284</v>
+        <v>4164.166666666667</v>
       </c>
       <c r="I14" s="125">
-        <v>465249</v>
+        <v>499700</v>
       </c>
       <c r="J14" s="129">
         <f t="shared" si="3"/>
-        <v>0.73164157258064522</v>
+        <v>0.78581854838709675</v>
       </c>
       <c r="K14" s="111">
         <f t="shared" ref="K14:K31" si="21">IFERROR(I14/$I$32,)</f>
-        <v>0.24586819005744423</v>
+        <v>0.24429067706209784</v>
       </c>
       <c r="L14" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3162,38 +3162,38 @@
       </c>
       <c r="N14" s="130">
         <f t="shared" ref="N14:N31" si="22">IFERROR(IF(C14-I14&lt;0,"",C14-I14),"")</f>
-        <v>170648.43589743588</v>
+        <v>136197.43589743588</v>
       </c>
       <c r="O14" s="130">
         <f t="shared" si="6"/>
-        <v>24378.347985347984</v>
+        <v>22699.572649572645</v>
       </c>
       <c r="P14" s="129">
         <f t="shared" si="7"/>
-        <v>0.73164157258064522</v>
+        <v>0.78581854838709675</v>
       </c>
       <c r="Q14" s="109">
         <f t="shared" si="8"/>
-        <v>600946.625</v>
+        <v>619628</v>
       </c>
       <c r="R14" s="115">
         <f t="shared" ref="R14:R31" si="23">IFERROR(Q14/$Q$32,)</f>
-        <v>0.24269626550085341</v>
+        <v>0.24139574478270592</v>
       </c>
       <c r="S14" s="106">
         <f t="shared" ref="S14:S31" si="24">IFERROR(IF(T14&lt;0.85,"",IF(AND(T14&gt;0.85,T14&lt;1),$M$2*AD14*AK14,$M$2*AD14*AK14)),"")</f>
-        <v>9802.9875561104709</v>
+        <v>10415.260804394629</v>
       </c>
       <c r="T14" s="129">
         <f t="shared" si="9"/>
-        <v>0.94503703125000005</v>
+        <v>0.97441500000000003</v>
       </c>
       <c r="U14" s="131">
         <f t="shared" si="10"/>
-        <v>7.4297606659729454E-2</v>
+        <v>7.560680085987885E-2</v>
       </c>
       <c r="V14" s="62">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="W14" s="64">
         <v>31</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="Z14" s="133">
         <f t="shared" si="12"/>
-        <v>969.07563025210084</v>
+        <v>1031.6532258064515</v>
       </c>
       <c r="AA14" s="17">
         <f t="shared" si="13"/>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="AB14" s="134">
         <f t="shared" si="14"/>
-        <v>0.24586819005744423</v>
+        <v>0.24429067706209784</v>
       </c>
       <c r="AC14" s="135">
         <f t="shared" ref="AC14:AC31" si="25">AA14/$C$32</f>
@@ -3220,15 +3220,15 @@
       </c>
       <c r="AD14" s="134">
         <f t="shared" ref="AD14:AD18" si="26">Q14/$Q$32</f>
-        <v>0.24269626550085341</v>
+        <v>0.24139574478270592</v>
       </c>
       <c r="AE14" s="134">
         <f t="shared" si="15"/>
-        <v>0.73164157258064522</v>
+        <v>0.78581854838709675</v>
       </c>
       <c r="AF14" s="134">
         <f t="shared" si="16"/>
-        <v>0.94503703125000005</v>
+        <v>0.97441500000000003</v>
       </c>
       <c r="AG14" s="134">
         <f>IFERROR(VLOOKUP(A14,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="AK14" s="137">
         <f t="shared" si="19"/>
-        <v>0.88</v>
+        <v>0.94</v>
       </c>
       <c r="AL14" s="93">
         <v>0.88</v>
@@ -3269,33 +3269,33 @@
         <v>615384.61538461538</v>
       </c>
       <c r="D15" s="126">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E15" s="126">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="F15" s="127">
         <f>DATA!E4</f>
-        <v>1.2608695652173914</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="G15" s="128">
         <f>DATA!F4</f>
-        <v>5206.623188405797</v>
+        <v>5500.2666666666664</v>
       </c>
       <c r="H15" s="128">
         <f>DATA!G4</f>
-        <v>4129.3908045977014</v>
+        <v>4125.2</v>
       </c>
       <c r="I15" s="125">
-        <v>359257</v>
+        <v>412520</v>
       </c>
       <c r="J15" s="129">
         <f t="shared" si="3"/>
-        <v>0.58379262499999995</v>
+        <v>0.67034499999999997</v>
       </c>
       <c r="K15" s="111">
         <f t="shared" si="21"/>
-        <v>0.18985504182806892</v>
+        <v>0.2016705825528449</v>
       </c>
       <c r="L15" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3307,23 +3307,23 @@
       </c>
       <c r="N15" s="130">
         <f t="shared" si="22"/>
-        <v>256127.61538461538</v>
+        <v>202864.61538461538</v>
       </c>
       <c r="O15" s="130">
         <f t="shared" si="6"/>
-        <v>36589.659340659338</v>
+        <v>33810.769230769227</v>
       </c>
       <c r="P15" s="129">
         <f t="shared" si="7"/>
-        <v>0.58379262499999995</v>
+        <v>0.67034499999999997</v>
       </c>
       <c r="Q15" s="109">
         <f t="shared" si="8"/>
-        <v>468596.08695652173</v>
+        <v>515650</v>
       </c>
       <c r="R15" s="115">
         <f t="shared" si="23"/>
-        <v>0.1892456261530065</v>
+        <v>0.20088781623361485</v>
       </c>
       <c r="S15" s="106" t="str">
         <f t="shared" si="24"/>
@@ -3331,14 +3331,14 @@
       </c>
       <c r="T15" s="129">
         <f t="shared" si="9"/>
-        <v>0.76146864130434777</v>
+        <v>0.83793125000000002</v>
       </c>
       <c r="U15" s="131">
         <f t="shared" si="10"/>
-        <v>7.4297606659729454E-2</v>
+        <v>7.5727965604846584E-2</v>
       </c>
       <c r="V15" s="62">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W15" s="64">
         <v>30</v>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="Z15" s="133">
         <f t="shared" si="12"/>
-        <v>928.69747899159665</v>
+        <v>990.38709677419354</v>
       </c>
       <c r="AA15" s="17">
         <f t="shared" si="13"/>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="AB15" s="134">
         <f t="shared" si="14"/>
-        <v>0.18985504182806892</v>
+        <v>0.2016705825528449</v>
       </c>
       <c r="AC15" s="135">
         <f t="shared" si="25"/>
@@ -3365,15 +3365,15 @@
       </c>
       <c r="AD15" s="134">
         <f t="shared" si="26"/>
-        <v>0.1892456261530065</v>
+        <v>0.20088781623361485</v>
       </c>
       <c r="AE15" s="134">
         <f t="shared" si="15"/>
-        <v>0.58379262499999995</v>
+        <v>0.67034499999999997</v>
       </c>
       <c r="AF15" s="134">
         <f t="shared" si="16"/>
-        <v>0.76146864130434777</v>
+        <v>0.83793125000000002</v>
       </c>
       <c r="AG15" s="134">
         <f>IFERROR(VLOOKUP(A15,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3414,33 +3414,33 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D16" s="126">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E16" s="126">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F16" s="127">
         <f>DATA!E5</f>
-        <v>1.6515151515151516</v>
+        <v>1.6527777777777777</v>
       </c>
       <c r="G16" s="128">
         <f>DATA!F5</f>
-        <v>6244.924242424242</v>
+        <v>6351.291666666667</v>
       </c>
       <c r="H16" s="128">
         <f>DATA!G5</f>
-        <v>3781.330275229358</v>
+        <v>3842.798319327731</v>
       </c>
       <c r="I16" s="125">
-        <v>412165</v>
+        <v>457293</v>
       </c>
       <c r="J16" s="129">
         <f t="shared" si="3"/>
-        <v>0.64816270161290324</v>
+        <v>0.71913012096774198</v>
       </c>
       <c r="K16" s="111">
         <f t="shared" si="21"/>
-        <v>0.217815110951397</v>
+        <v>0.2235589685526474</v>
       </c>
       <c r="L16" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3452,38 +3452,38 @@
       </c>
       <c r="N16" s="130">
         <f t="shared" ref="N16:N25" si="28">IFERROR(IF(C16-I16&lt;0,"",C16-I16),"")</f>
-        <v>223732.43589743588</v>
+        <v>178604.43589743588</v>
       </c>
       <c r="O16" s="130">
         <f t="shared" si="6"/>
-        <v>31961.776556776553</v>
+        <v>29767.405982905981</v>
       </c>
       <c r="P16" s="129">
         <f t="shared" si="7"/>
-        <v>0.64816270161290324</v>
+        <v>0.71913012096774198</v>
       </c>
       <c r="Q16" s="109">
         <f t="shared" si="8"/>
-        <v>532379.79166666663</v>
+        <v>567043.32000000007</v>
       </c>
       <c r="R16" s="115">
         <f t="shared" si="23"/>
-        <v>0.21500509677647719</v>
-      </c>
-      <c r="S16" s="106" t="str">
+        <v>0.22090971446651581</v>
+      </c>
+      <c r="S16" s="106">
         <f t="shared" si="24"/>
-        <v/>
+        <v>7909.0095973301986</v>
       </c>
       <c r="T16" s="129">
         <f t="shared" si="9"/>
-        <v>0.83721015624999995</v>
+        <v>0.89172135000000008</v>
       </c>
       <c r="U16" s="131">
         <f t="shared" si="10"/>
-        <v>6.8106139438085328E-2</v>
+        <v>6.9790893101426624E-2</v>
       </c>
       <c r="V16" s="62">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="W16" s="64">
         <v>31</v>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="Z16" s="133">
         <f t="shared" si="12"/>
-        <v>969.07563025210084</v>
+        <v>1031.6532258064515</v>
       </c>
       <c r="AA16" s="17">
         <f t="shared" si="13"/>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="AB16" s="134">
         <f t="shared" si="14"/>
-        <v>0.217815110951397</v>
+        <v>0.2235589685526474</v>
       </c>
       <c r="AC16" s="135">
         <f t="shared" si="25"/>
@@ -3510,15 +3510,15 @@
       </c>
       <c r="AD16" s="134">
         <f t="shared" si="26"/>
-        <v>0.21500509677647719</v>
+        <v>0.22090971446651581</v>
       </c>
       <c r="AE16" s="134">
         <f t="shared" si="15"/>
-        <v>0.64816270161290324</v>
+        <v>0.71913012096774198</v>
       </c>
       <c r="AF16" s="134">
         <f t="shared" si="16"/>
-        <v>0.83721015624999995</v>
+        <v>0.89172135000000008</v>
       </c>
       <c r="AG16" s="134">
         <f>IFERROR(VLOOKUP(A16,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3536,9 +3536,9 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AK16" s="137" t="str">
+      <c r="AK16" s="137">
         <f t="shared" si="19"/>
-        <v/>
+        <v>0.78</v>
       </c>
       <c r="AL16" s="93">
         <v>0.9</v>
@@ -3559,33 +3559,33 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D17" s="126">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E17" s="126">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F17" s="127">
         <f>DATA!E6</f>
-        <v>1.2448979591836735</v>
+        <v>1.2</v>
       </c>
       <c r="G17" s="128">
         <f>DATA!F6</f>
-        <v>5208.9591836734689</v>
+        <v>4953.9399999999996</v>
       </c>
       <c r="H17" s="128">
         <f>DATA!G6</f>
-        <v>4184.2459016393441</v>
+        <v>4128.2833333333338</v>
       </c>
       <c r="I17" s="125">
-        <v>255239</v>
+        <v>247697</v>
       </c>
       <c r="J17" s="129">
         <f t="shared" si="3"/>
-        <v>0.40138391129032258</v>
+        <v>0.38952350806451613</v>
       </c>
       <c r="K17" s="111">
         <f t="shared" si="21"/>
-        <v>0.13488508510941885</v>
+        <v>0.12109279134730928</v>
       </c>
       <c r="L17" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3597,23 +3597,23 @@
       </c>
       <c r="N17" s="130">
         <f t="shared" si="28"/>
-        <v>380658.43589743588</v>
+        <v>388200.43589743588</v>
       </c>
       <c r="O17" s="130">
         <f t="shared" si="6"/>
-        <v>54379.776556776553</v>
+        <v>64700.072649572649</v>
       </c>
       <c r="P17" s="129">
         <f t="shared" si="7"/>
-        <v>0.40138391129032258</v>
+        <v>0.38952350806451613</v>
       </c>
       <c r="Q17" s="109">
         <f t="shared" si="8"/>
-        <v>329683.70833333337</v>
+        <v>307144.28000000003</v>
       </c>
       <c r="R17" s="115">
         <f t="shared" si="23"/>
-        <v>0.13314494412706385</v>
+        <v>0.11965779826984574</v>
       </c>
       <c r="S17" s="106" t="str">
         <f t="shared" si="24"/>
@@ -3621,14 +3621,14 @@
       </c>
       <c r="T17" s="129">
         <f t="shared" si="9"/>
-        <v>0.51845421875000008</v>
+        <v>0.48300915000000005</v>
       </c>
       <c r="U17" s="131">
         <f t="shared" si="10"/>
-        <v>5.0563648976760321E-2</v>
+        <v>4.8465897987101825E-2</v>
       </c>
       <c r="V17" s="62">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="W17" s="64">
         <v>31</v>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="Z17" s="133">
         <f t="shared" si="12"/>
-        <v>969.07563025210084</v>
+        <v>1031.6532258064515</v>
       </c>
       <c r="AA17" s="17">
         <f t="shared" si="13"/>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="AB17" s="134">
         <f t="shared" si="14"/>
-        <v>0.13488508510941885</v>
+        <v>0.12109279134730928</v>
       </c>
       <c r="AC17" s="135">
         <f t="shared" si="25"/>
@@ -3655,15 +3655,15 @@
       </c>
       <c r="AD17" s="134">
         <f t="shared" si="26"/>
-        <v>0.13314494412706385</v>
+        <v>0.11965779826984574</v>
       </c>
       <c r="AE17" s="134">
         <f t="shared" si="15"/>
-        <v>0.40138391129032258</v>
+        <v>0.38952350806451613</v>
       </c>
       <c r="AF17" s="134">
         <f t="shared" si="16"/>
-        <v>0.51845421875000008</v>
+        <v>0.48300915000000005</v>
       </c>
       <c r="AG17" s="134">
         <f>IFERROR(VLOOKUP(A17,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="K18" s="111">
         <f t="shared" si="21"/>
-        <v>-1.1205589054416125E-2</v>
+        <v>-1.0366098692064684E-2</v>
       </c>
       <c r="L18" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="AB18" s="138">
         <f t="shared" si="14"/>
-        <v>-1.1205589054416125E-2</v>
+        <v>-1.0366098692064684E-2</v>
       </c>
       <c r="AC18" s="135">
         <f t="shared" si="25"/>
@@ -5699,31 +5699,31 @@
       </c>
       <c r="D32" s="153">
         <f>SUM(D13:D31)</f>
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="E32" s="153">
         <f>SUM(E13:E31)</f>
-        <v>471</v>
+        <v>507</v>
       </c>
       <c r="F32" s="154">
         <f>IFERROR(SUM(F13:F31)/G10,)</f>
-        <v>1.6467929984070302</v>
+        <v>1.64891452991453</v>
       </c>
       <c r="G32" s="155">
         <f>IFERROR(SUM(G13:G31)/G10,)</f>
-        <v>6518.7638815861474</v>
+        <v>6547.8697179487181</v>
       </c>
       <c r="H32" s="155">
         <f>IFERROR(SUM(H13:H31)/G10,)</f>
-        <v>4737.2692560816404</v>
+        <v>4747.5001901813357</v>
       </c>
       <c r="I32" s="155">
         <f>SUM(I13:I31)</f>
-        <v>1892270</v>
+        <v>2045514</v>
       </c>
       <c r="J32" s="156">
         <f>IFERROR(I32/C32,)</f>
-        <v>0.63075666666666663</v>
+        <v>0.68183800000000006</v>
       </c>
       <c r="K32" s="156">
         <f>SUM(K13:K31)</f>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="L32" s="155">
         <f>SUM(L13:L31)</f>
-        <v>7771.5329080945103</v>
+        <v>8876.2663741240576</v>
       </c>
       <c r="M32" s="155">
         <f>SUM(M13:M31)</f>
@@ -5739,33 +5739,33 @@
       </c>
       <c r="N32" s="155">
         <f>SUM(N13:N31)</f>
-        <v>1107730</v>
+        <v>954485.99999999988</v>
       </c>
       <c r="O32" s="155">
         <f>SUM(O13:O31)</f>
-        <v>155217.99999999997</v>
+        <v>155546.99999999997</v>
       </c>
       <c r="P32" s="157"/>
       <c r="Q32" s="152">
         <f>SUM(Q13:Q31)</f>
-        <v>2476126.3786231885</v>
+        <v>2566855.5200000005</v>
       </c>
       <c r="R32" s="156">
         <f>SUM(R13:R31)</f>
-        <v>1</v>
+        <v>0.99999999999999978</v>
       </c>
       <c r="S32" s="155">
         <f>SUM(S13:S31)</f>
-        <v>21309.897093111907</v>
+        <v>29886.147830837002</v>
       </c>
       <c r="T32" s="158">
         <f>IFERROR(Q32/C32,)</f>
-        <v>0.82537545954106284</v>
+        <v>0.85561850666666683</v>
       </c>
       <c r="U32" s="165"/>
       <c r="V32" s="166">
         <f>SUM(V13:V31)</f>
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="W32" s="167">
         <f>SUM(W13:W31)</f>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="Z32" s="164">
         <f>SUM(Z13:Z31)</f>
-        <v>4805</v>
+        <v>5117</v>
       </c>
       <c r="AA32" s="162">
         <f>SUM(AA13:AA31)</f>
@@ -6948,25 +6948,25 @@
         <v>65</v>
       </c>
       <c r="B2" s="19">
-        <v>421564</v>
+        <v>449508</v>
       </c>
       <c r="C2" s="18">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D2" s="18">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E2" s="16">
         <f>IFERROR((D2/C2),"")</f>
-        <v>1.5211267605633803</v>
+        <v>1.52</v>
       </c>
       <c r="F2" s="17">
         <f>IFERROR((B2/C2),"")</f>
-        <v>5937.5211267605637</v>
+        <v>5993.44</v>
       </c>
       <c r="G2" s="17">
         <f>IFERROR((B2/D2),"")</f>
-        <v>3903.3703703703704</v>
+        <v>3943.0526315789475</v>
       </c>
       <c r="Q2" s="6" t="s">
         <v>38</v>
@@ -6980,25 +6980,25 @@
         <v>67</v>
       </c>
       <c r="B3" s="19">
-        <v>465249</v>
+        <v>499700</v>
       </c>
       <c r="C3" s="18">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D3" s="18">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="E3" s="16">
         <f t="shared" ref="E3:E20" si="0">IFERROR((D3/C3),"")</f>
-        <v>1.5555555555555556</v>
+        <v>1.5384615384615385</v>
       </c>
       <c r="F3" s="17">
         <f t="shared" ref="F3:F20" si="1">IFERROR((B3/C3),"")</f>
-        <v>6461.791666666667</v>
+        <v>6406.4102564102568</v>
       </c>
       <c r="G3" s="17">
         <f t="shared" ref="G3:G20" si="2">IFERROR((B3/D3),"")</f>
-        <v>4154.0089285714284</v>
+        <v>4164.166666666667</v>
       </c>
       <c r="Q3" s="6" t="s">
         <v>40</v>
@@ -7012,25 +7012,25 @@
         <v>64</v>
       </c>
       <c r="B4" s="174">
-        <v>359257</v>
+        <v>412520</v>
       </c>
       <c r="C4" s="18">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D4" s="18">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E4" s="16">
         <f t="shared" si="0"/>
-        <v>1.2608695652173914</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="F4" s="17">
         <f t="shared" si="1"/>
-        <v>5206.623188405797</v>
+        <v>5500.2666666666664</v>
       </c>
       <c r="G4" s="17">
         <f t="shared" si="2"/>
-        <v>4129.3908045977014</v>
+        <v>4125.2</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -7038,25 +7038,25 @@
         <v>66</v>
       </c>
       <c r="B5" s="175">
-        <v>412165</v>
+        <v>457293</v>
       </c>
       <c r="C5" s="18">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D5" s="18">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="E5" s="16">
         <f t="shared" si="0"/>
-        <v>1.6515151515151516</v>
+        <v>1.6527777777777777</v>
       </c>
       <c r="F5" s="17">
         <f t="shared" si="1"/>
-        <v>6244.924242424242</v>
+        <v>6351.291666666667</v>
       </c>
       <c r="G5" s="17">
         <f t="shared" si="2"/>
-        <v>3781.330275229358</v>
+        <v>3842.798319327731</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -7064,25 +7064,25 @@
         <v>68</v>
       </c>
       <c r="B6" s="19">
-        <v>255239</v>
+        <v>247697</v>
       </c>
       <c r="C6" s="18">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D6" s="18">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6" s="16">
         <f t="shared" si="0"/>
-        <v>1.2448979591836735</v>
+        <v>1.2</v>
       </c>
       <c r="F6" s="17">
         <f t="shared" si="1"/>
-        <v>5208.9591836734689</v>
+        <v>4953.9399999999996</v>
       </c>
       <c r="G6" s="17">
         <f t="shared" si="2"/>
-        <v>4184.2459016393441</v>
+        <v>4128.2833333333338</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">

--- a/EKİM SD KARNE.xlsx
+++ b/EKİM SD KARNE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\UYGULAMA İÇİN GEREKLİ DOSYALAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88423AF3-F90E-46A7-8BF1-4323FAA12362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34086876-C49C-4527-B86C-725EF7216BF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2690,11 +2690,11 @@
       </c>
       <c r="B9" s="75">
         <f>I32</f>
-        <v>2045514</v>
+        <v>2168640.6700000004</v>
       </c>
       <c r="C9" s="76">
         <f>IFERROR(B9/A9,)</f>
-        <v>0.68183800000000006</v>
+        <v>0.72288022333333346</v>
       </c>
       <c r="D9" s="168">
         <f>IFERROR(IF(B9&lt;=A9,A4,IF(AND(B9&gt;A9,B9&lt;B1),A4,IF(AND(B9&gt;=B1,B9&lt;C1),B4,IF(AND(B9&gt;=C1,B9&lt;D1),C4,IF(AND(B9&gt;=D1,B9&lt;E1),D4,IF(AND(B9&gt;=E1,B9&lt;F1),E4,IF(AND(B9&gt;=F1,B9&lt;G1),F4,IF(AND(B9&gt;=G1,B9&lt;H1),G4,IF(AND(B9&gt;=H1,B9&lt;I1),H4,IF(AND(B9&gt;=I1,B9&lt;J1),I4,IF(AND(B9&gt;=J1,B9&lt;K1),J4,IF(B9&gt;=K4,K4,K4)))))))))))),)</f>
@@ -2761,27 +2761,27 @@
       </c>
       <c r="H10" s="83">
         <f ca="1">B11-M10</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I10" s="84">
         <f>C11</f>
-        <v>5117</v>
+        <v>5274</v>
       </c>
       <c r="J10" s="85">
         <f ca="1">I10/H10</f>
-        <v>204.68</v>
+        <v>202.84615384615384</v>
       </c>
       <c r="K10" s="85">
         <f>IFERROR(I10/G10,)</f>
-        <v>1023.4</v>
+        <v>1054.8</v>
       </c>
       <c r="L10" s="86">
         <f ca="1">IFERROR(J10/G10,)</f>
-        <v>40.936</v>
+        <v>40.569230769230771</v>
       </c>
       <c r="M10" s="87">
         <f ca="1">(M11-A11)+B11</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N10" s="2">
         <f>LOOKUP(A9,'PRİM HAVUZU (SV SİSTEM)'!$A:$A,'PRİM HAVUZU (SV SİSTEM)'!$C:$C)*A9</f>
@@ -2804,14 +2804,14 @@
     <row r="11" spans="1:58" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="169">
         <f ca="1">TODAY()</f>
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="B11" s="170">
         <f ca="1">(N11-M11)+1</f>
         <v>31</v>
       </c>
       <c r="C11" s="171">
-        <v>5117</v>
+        <v>5274</v>
       </c>
       <c r="F11" s="66"/>
       <c r="K11" s="89"/>
@@ -2977,39 +2977,39 @@
       </c>
       <c r="D13" s="107" cm="1">
         <f t="array" ref="D13:D31">DATA!C2:C20</f>
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E13" s="107" cm="1">
         <f t="array" ref="E13:E31">DATA!D2:D20</f>
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F13" s="108">
         <f>DATA!E2</f>
-        <v>1.52</v>
+        <v>1.5249999999999999</v>
       </c>
       <c r="G13" s="109">
         <f>DATA!F2</f>
-        <v>5993.44</v>
+        <v>5956.5827499999996</v>
       </c>
       <c r="H13" s="109">
         <f>DATA!G2</f>
-        <v>3943.0526315789475</v>
+        <v>3905.9559016393441</v>
       </c>
       <c r="I13" s="106" cm="1">
         <f t="array" ref="I13:I31">DATA!B2:B20</f>
-        <v>449508</v>
+        <v>476526.62</v>
       </c>
       <c r="J13" s="110">
         <f t="shared" ref="J13:J31" si="3">IFERROR(I13/C13,0)</f>
-        <v>0.94251677419354851</v>
+        <v>0.99916871935483875</v>
       </c>
       <c r="K13" s="111">
         <f>IFERROR(I13/$I$32,)</f>
-        <v>0.21975307917716524</v>
+        <v>0.21973516709893665</v>
       </c>
       <c r="L13" s="112">
         <f t="shared" ref="L13:L31" si="4">IFERROR(IF(J13&lt;0.85,"",IF(AND(J13&gt;0.85,J13&lt;1),$M$2*AB13*AJ13,$M$2*AB13*AJ13)),"")</f>
-        <v>8876.2663741240576</v>
+        <v>9884.1272864443672</v>
       </c>
       <c r="M13" s="113">
         <f t="shared" ref="M13:M31" si="5">IFERROR((($E$9+$F$9)*AC13),"")</f>
@@ -3017,38 +3017,38 @@
       </c>
       <c r="N13" s="114">
         <f>IFERROR(IF(C13-I13&lt;0,"",C13-I13),"")</f>
-        <v>27415.076923076878</v>
+        <v>396.45692307688296</v>
       </c>
       <c r="O13" s="114">
         <f t="shared" ref="O13:O31" si="6">IFERROR(IF(N13/(W13-V13)&gt;0,N13/(W13-V13),""),"")</f>
-        <v>4569.17948717948</v>
+        <v>79.291384615376586</v>
       </c>
       <c r="P13" s="110">
         <f t="shared" ref="P13:P31" si="7">IFERROR(I13/C13,0)</f>
-        <v>0.94251677419354851</v>
+        <v>0.99916871935483875</v>
       </c>
       <c r="Q13" s="109">
         <f t="shared" ref="Q13:Q31" si="8">IF(V13="",0,IF(W13=V13,I13,(I13/V13)*(W13-V13)+I13))</f>
-        <v>557389.92000000004</v>
+        <v>568166.3546153846</v>
       </c>
       <c r="R13" s="115">
         <f>IFERROR(Q13/$Q$32,)</f>
-        <v>0.21714892624731755</v>
+        <v>0.21681744723052498</v>
       </c>
       <c r="S13" s="106">
         <f>IFERROR(IF(T13&lt;0.85,"",IF(AND(T13&gt;0.85,T13&lt;1),$M$2*AD13*AK13,$M$2*AD13*AK13)),"")</f>
-        <v>11561.877429112175</v>
+        <v>11842.785785178505</v>
       </c>
       <c r="T13" s="110">
         <f t="shared" ref="T13:T31" si="9">IFERROR(Q13/C13,0)</f>
-        <v>1.1687208000000002</v>
+        <v>1.19131655</v>
       </c>
       <c r="U13" s="116">
         <f t="shared" ref="U13:U31" si="10">IFERROR(D13/Z13,0)</f>
-        <v>7.2698846980652737E-2</v>
+        <v>7.5260348297890953E-2</v>
       </c>
       <c r="V13" s="62">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W13" s="63">
         <v>31</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z13" s="118">
         <f t="shared" ref="Z13:Z31" si="12">(V13/$V$32)*$I$10</f>
-        <v>1031.6532258064515</v>
+        <v>1062.9767441860465</v>
       </c>
       <c r="AA13" s="119">
         <f t="shared" ref="AA13:AA31" si="13">IFERROR(((Y13/$Y$32)*$A$9),"")</f>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AB13" s="120">
         <f t="shared" ref="AB13:AB31" si="14">I13/$I$32</f>
-        <v>0.21975307917716524</v>
+        <v>0.21973516709893665</v>
       </c>
       <c r="AC13" s="121">
         <f>AA13/$C$32</f>
@@ -3075,15 +3075,15 @@
       </c>
       <c r="AD13" s="120">
         <f>Q13/$Q$32</f>
-        <v>0.21714892624731755</v>
+        <v>0.21681744723052498</v>
       </c>
       <c r="AE13" s="120">
         <f t="shared" ref="AE13:AE31" si="15">I13/C13</f>
-        <v>0.94251677419354851</v>
+        <v>0.99916871935483875</v>
       </c>
       <c r="AF13" s="120">
         <f t="shared" ref="AF13:AF31" si="16">Q13/C13</f>
-        <v>1.1687208000000002</v>
+        <v>1.19131655</v>
       </c>
       <c r="AG13" s="120">
         <f>IFERROR(VLOOKUP(A13,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3099,11 +3099,11 @@
       </c>
       <c r="AJ13" s="121">
         <f t="shared" ref="AJ13:AJ31" si="18">IFERROR(LOOKUP(AE13,AL:AL,AM:AM),"")</f>
-        <v>0.88</v>
+        <v>0.98</v>
       </c>
       <c r="AK13" s="123">
         <f t="shared" ref="AK13:AK31" si="19">IFERROR(LOOKUP(AF13,AL:AL,AM:AM),"")</f>
-        <v>1.1599999999999999</v>
+        <v>1.19</v>
       </c>
       <c r="AL13" s="93">
         <v>0.87</v>
@@ -3124,37 +3124,37 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D14" s="126">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="E14" s="126">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="F14" s="127">
         <f>DATA!E3</f>
-        <v>1.5384615384615385</v>
+        <v>1.558139534883721</v>
       </c>
       <c r="G14" s="128">
         <f>DATA!F3</f>
-        <v>6406.4102564102568</v>
+        <v>6435.2613953488371</v>
       </c>
       <c r="H14" s="128">
         <f>DATA!G3</f>
-        <v>4164.166666666667</v>
+        <v>4130.0931343283582</v>
       </c>
       <c r="I14" s="125">
-        <v>499700</v>
+        <v>553432.48</v>
       </c>
       <c r="J14" s="129">
         <f t="shared" si="3"/>
-        <v>0.78581854838709675</v>
+        <v>0.87031720645161292</v>
       </c>
       <c r="K14" s="111">
         <f t="shared" ref="K14:K31" si="21">IFERROR(I14/$I$32,)</f>
-        <v>0.24429067706209784</v>
-      </c>
-      <c r="L14" s="112" t="str">
+        <v>0.25519787010173517</v>
+      </c>
+      <c r="L14" s="112">
         <f t="shared" si="4"/>
-        <v/>
+        <v>8668.0508558755373</v>
       </c>
       <c r="M14" s="113">
         <f t="shared" si="5"/>
@@ -3162,38 +3162,38 @@
       </c>
       <c r="N14" s="130">
         <f t="shared" ref="N14:N31" si="22">IFERROR(IF(C14-I14&lt;0,"",C14-I14),"")</f>
-        <v>136197.43589743588</v>
+        <v>82464.955897435895</v>
       </c>
       <c r="O14" s="130">
         <f t="shared" si="6"/>
-        <v>22699.572649572645</v>
+        <v>16492.99117948718</v>
       </c>
       <c r="P14" s="129">
         <f t="shared" si="7"/>
-        <v>0.78581854838709675</v>
+        <v>0.87031720645161292</v>
       </c>
       <c r="Q14" s="109">
         <f t="shared" si="8"/>
-        <v>619628</v>
+        <v>659861.80307692301</v>
       </c>
       <c r="R14" s="115">
         <f t="shared" ref="R14:R31" si="23">IFERROR(Q14/$Q$32,)</f>
-        <v>0.24139574478270592</v>
+        <v>0.25180926414574401</v>
       </c>
       <c r="S14" s="106">
         <f t="shared" ref="S14:S31" si="24">IFERROR(IF(T14&lt;0.85,"",IF(AND(T14&gt;0.85,T14&lt;1),$M$2*AD14*AK14,$M$2*AD14*AK14)),"")</f>
-        <v>10415.260804394629</v>
+        <v>11904.786581018339</v>
       </c>
       <c r="T14" s="129">
         <f t="shared" si="9"/>
-        <v>0.97441500000000003</v>
+        <v>1.0376858999999998</v>
       </c>
       <c r="U14" s="131">
         <f t="shared" si="10"/>
-        <v>7.560680085987885E-2</v>
+        <v>8.0904874420232781E-2</v>
       </c>
       <c r="V14" s="62">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W14" s="64">
         <v>31</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="Z14" s="133">
         <f t="shared" si="12"/>
-        <v>1031.6532258064515</v>
+        <v>1062.9767441860465</v>
       </c>
       <c r="AA14" s="17">
         <f t="shared" si="13"/>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="AB14" s="134">
         <f t="shared" si="14"/>
-        <v>0.24429067706209784</v>
+        <v>0.25519787010173517</v>
       </c>
       <c r="AC14" s="135">
         <f t="shared" ref="AC14:AC31" si="25">AA14/$C$32</f>
@@ -3220,15 +3220,15 @@
       </c>
       <c r="AD14" s="134">
         <f t="shared" ref="AD14:AD18" si="26">Q14/$Q$32</f>
-        <v>0.24139574478270592</v>
+        <v>0.25180926414574401</v>
       </c>
       <c r="AE14" s="134">
         <f t="shared" si="15"/>
-        <v>0.78581854838709675</v>
+        <v>0.87031720645161292</v>
       </c>
       <c r="AF14" s="134">
         <f t="shared" si="16"/>
-        <v>0.97441500000000003</v>
+        <v>1.0376858999999998</v>
       </c>
       <c r="AG14" s="134">
         <f>IFERROR(VLOOKUP(A14,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3242,13 +3242,13 @@
         <f t="shared" ref="AI14:AI17" si="27">AG14/$AG$32</f>
         <v>0.17391304347826086</v>
       </c>
-      <c r="AJ14" s="135" t="str">
+      <c r="AJ14" s="135">
         <f t="shared" si="18"/>
-        <v/>
+        <v>0.74</v>
       </c>
       <c r="AK14" s="137">
         <f t="shared" si="19"/>
-        <v>0.94</v>
+        <v>1.03</v>
       </c>
       <c r="AL14" s="93">
         <v>0.88</v>
@@ -3280,22 +3280,22 @@
       </c>
       <c r="G15" s="128">
         <f>DATA!F4</f>
-        <v>5500.2666666666664</v>
+        <v>5500.2728000000006</v>
       </c>
       <c r="H15" s="128">
         <f>DATA!G4</f>
-        <v>4125.2</v>
+        <v>4125.2046</v>
       </c>
       <c r="I15" s="125">
-        <v>412520</v>
+        <v>412520.46</v>
       </c>
       <c r="J15" s="129">
         <f t="shared" si="3"/>
-        <v>0.67034499999999997</v>
+        <v>0.67034574750000009</v>
       </c>
       <c r="K15" s="111">
         <f t="shared" si="21"/>
-        <v>0.2016705825528449</v>
+        <v>0.19022075243106085</v>
       </c>
       <c r="L15" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3307,23 +3307,23 @@
       </c>
       <c r="N15" s="130">
         <f t="shared" si="22"/>
-        <v>202864.61538461538</v>
+        <v>202864.15538461535</v>
       </c>
       <c r="O15" s="130">
         <f t="shared" si="6"/>
-        <v>33810.769230769227</v>
+        <v>40572.831076923074</v>
       </c>
       <c r="P15" s="129">
         <f t="shared" si="7"/>
-        <v>0.67034499999999997</v>
+        <v>0.67034574750000009</v>
       </c>
       <c r="Q15" s="109">
         <f t="shared" si="8"/>
-        <v>515650</v>
+        <v>495024.55200000003</v>
       </c>
       <c r="R15" s="115">
         <f t="shared" si="23"/>
-        <v>0.20088781623361485</v>
+        <v>0.18890587027760627</v>
       </c>
       <c r="S15" s="106" t="str">
         <f t="shared" si="24"/>
@@ -3331,14 +3331,14 @@
       </c>
       <c r="T15" s="129">
         <f t="shared" si="9"/>
-        <v>0.83793125000000002</v>
+        <v>0.80441489700000002</v>
       </c>
       <c r="U15" s="131">
         <f t="shared" si="10"/>
-        <v>7.5727965604846584E-2</v>
+        <v>7.3378839590443681E-2</v>
       </c>
       <c r="V15" s="62">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="W15" s="64">
         <v>30</v>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="Z15" s="133">
         <f t="shared" si="12"/>
-        <v>990.38709677419354</v>
+        <v>1022.093023255814</v>
       </c>
       <c r="AA15" s="17">
         <f t="shared" si="13"/>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="AB15" s="134">
         <f t="shared" si="14"/>
-        <v>0.2016705825528449</v>
+        <v>0.19022075243106085</v>
       </c>
       <c r="AC15" s="135">
         <f t="shared" si="25"/>
@@ -3365,15 +3365,15 @@
       </c>
       <c r="AD15" s="134">
         <f t="shared" si="26"/>
-        <v>0.20088781623361485</v>
+        <v>0.18890587027760627</v>
       </c>
       <c r="AE15" s="134">
         <f t="shared" si="15"/>
-        <v>0.67034499999999997</v>
+        <v>0.67034574750000009</v>
       </c>
       <c r="AF15" s="134">
         <f t="shared" si="16"/>
-        <v>0.83793125000000002</v>
+        <v>0.80441489700000002</v>
       </c>
       <c r="AG15" s="134">
         <f>IFERROR(VLOOKUP(A15,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3414,33 +3414,33 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D16" s="126">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E16" s="126">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F16" s="127">
         <f>DATA!E5</f>
-        <v>1.6527777777777777</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="G16" s="128">
         <f>DATA!F5</f>
-        <v>6351.291666666667</v>
+        <v>6353.98</v>
       </c>
       <c r="H16" s="128">
         <f>DATA!G5</f>
-        <v>3842.798319327731</v>
+        <v>3894.3748387096771</v>
       </c>
       <c r="I16" s="125">
-        <v>457293</v>
+        <v>482902.48</v>
       </c>
       <c r="J16" s="129">
         <f t="shared" si="3"/>
-        <v>0.71913012096774198</v>
+        <v>0.75940309354838709</v>
       </c>
       <c r="K16" s="111">
         <f t="shared" si="21"/>
-        <v>0.2235589685526474</v>
+        <v>0.22267519311993716</v>
       </c>
       <c r="L16" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3452,38 +3452,38 @@
       </c>
       <c r="N16" s="130">
         <f t="shared" ref="N16:N25" si="28">IFERROR(IF(C16-I16&lt;0,"",C16-I16),"")</f>
-        <v>178604.43589743588</v>
+        <v>152994.9558974359</v>
       </c>
       <c r="O16" s="130">
         <f t="shared" si="6"/>
-        <v>29767.405982905981</v>
+        <v>30598.99117948718</v>
       </c>
       <c r="P16" s="129">
         <f t="shared" si="7"/>
-        <v>0.71913012096774198</v>
+        <v>0.75940309354838709</v>
       </c>
       <c r="Q16" s="109">
         <f t="shared" si="8"/>
-        <v>567043.32000000007</v>
+        <v>575768.34153846151</v>
       </c>
       <c r="R16" s="115">
         <f t="shared" si="23"/>
-        <v>0.22090971446651581</v>
+        <v>0.21971843456487206</v>
       </c>
       <c r="S16" s="106">
         <f t="shared" si="24"/>
-        <v>7909.0095973301986</v>
+        <v>8068.0609172221029</v>
       </c>
       <c r="T16" s="129">
         <f t="shared" si="9"/>
-        <v>0.89172135000000008</v>
+        <v>0.90544214999999995</v>
       </c>
       <c r="U16" s="131">
         <f t="shared" si="10"/>
-        <v>6.9790893101426624E-2</v>
+        <v>7.149733088299641E-2</v>
       </c>
       <c r="V16" s="62">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W16" s="64">
         <v>31</v>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="Z16" s="133">
         <f t="shared" si="12"/>
-        <v>1031.6532258064515</v>
+        <v>1062.9767441860465</v>
       </c>
       <c r="AA16" s="17">
         <f t="shared" si="13"/>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="AB16" s="134">
         <f t="shared" si="14"/>
-        <v>0.2235589685526474</v>
+        <v>0.22267519311993716</v>
       </c>
       <c r="AC16" s="135">
         <f t="shared" si="25"/>
@@ -3510,15 +3510,15 @@
       </c>
       <c r="AD16" s="134">
         <f t="shared" si="26"/>
-        <v>0.22090971446651581</v>
+        <v>0.21971843456487206</v>
       </c>
       <c r="AE16" s="134">
         <f t="shared" si="15"/>
-        <v>0.71913012096774198</v>
+        <v>0.75940309354838709</v>
       </c>
       <c r="AF16" s="134">
         <f t="shared" si="16"/>
-        <v>0.89172135000000008</v>
+        <v>0.90544214999999995</v>
       </c>
       <c r="AG16" s="134">
         <f>IFERROR(VLOOKUP(A16,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3538,7 +3538,7 @@
       </c>
       <c r="AK16" s="137">
         <f t="shared" si="19"/>
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AL16" s="93">
         <v>0.9</v>
@@ -3559,33 +3559,33 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D17" s="126">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E17" s="126">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F17" s="127">
         <f>DATA!E6</f>
-        <v>1.2</v>
+        <v>1.2452830188679245</v>
       </c>
       <c r="G17" s="128">
         <f>DATA!F6</f>
-        <v>4953.9399999999996</v>
+        <v>5090.2015094339622</v>
       </c>
       <c r="H17" s="128">
         <f>DATA!G6</f>
-        <v>4128.2833333333338</v>
+        <v>4087.5860606060605</v>
       </c>
       <c r="I17" s="125">
-        <v>247697</v>
+        <v>269780.68</v>
       </c>
       <c r="J17" s="129">
         <f t="shared" si="3"/>
-        <v>0.38952350806451613</v>
+        <v>0.42425187580645163</v>
       </c>
       <c r="K17" s="111">
         <f t="shared" si="21"/>
-        <v>0.12109279134730928</v>
+        <v>0.12440082109130599</v>
       </c>
       <c r="L17" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3597,23 +3597,23 @@
       </c>
       <c r="N17" s="130">
         <f t="shared" si="28"/>
-        <v>388200.43589743588</v>
+        <v>366116.75589743588</v>
       </c>
       <c r="O17" s="130">
         <f t="shared" si="6"/>
-        <v>64700.072649572649</v>
+        <v>73223.351179487174</v>
       </c>
       <c r="P17" s="129">
         <f t="shared" si="7"/>
-        <v>0.38952350806451613</v>
+        <v>0.42425187580645163</v>
       </c>
       <c r="Q17" s="109">
         <f t="shared" si="8"/>
-        <v>307144.28000000003</v>
+        <v>321661.58</v>
       </c>
       <c r="R17" s="115">
         <f t="shared" si="23"/>
-        <v>0.11965779826984574</v>
+        <v>0.12274898378125267</v>
       </c>
       <c r="S17" s="106" t="str">
         <f t="shared" si="24"/>
@@ -3621,14 +3621,14 @@
       </c>
       <c r="T17" s="129">
         <f t="shared" si="9"/>
-        <v>0.48300915000000005</v>
+        <v>0.50583877500000007</v>
       </c>
       <c r="U17" s="131">
         <f t="shared" si="10"/>
-        <v>4.8465897987101825E-2</v>
+        <v>4.9859980747352761E-2</v>
       </c>
       <c r="V17" s="62">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W17" s="64">
         <v>31</v>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="Z17" s="133">
         <f t="shared" si="12"/>
-        <v>1031.6532258064515</v>
+        <v>1062.9767441860465</v>
       </c>
       <c r="AA17" s="17">
         <f t="shared" si="13"/>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="AB17" s="134">
         <f t="shared" si="14"/>
-        <v>0.12109279134730928</v>
+        <v>0.12440082109130599</v>
       </c>
       <c r="AC17" s="135">
         <f t="shared" si="25"/>
@@ -3655,15 +3655,15 @@
       </c>
       <c r="AD17" s="134">
         <f t="shared" si="26"/>
-        <v>0.11965779826984574</v>
+        <v>0.12274898378125267</v>
       </c>
       <c r="AE17" s="134">
         <f t="shared" si="15"/>
-        <v>0.38952350806451613</v>
+        <v>0.42425187580645163</v>
       </c>
       <c r="AF17" s="134">
         <f t="shared" si="16"/>
-        <v>0.48300915000000005</v>
+        <v>0.50583877500000007</v>
       </c>
       <c r="AG17" s="134">
         <f>IFERROR(VLOOKUP(A17,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3704,10 +3704,10 @@
         <v>0</v>
       </c>
       <c r="D18" s="126">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="E18" s="126">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="F18" s="127">
         <f>DATA!E7</f>
@@ -3715,14 +3715,14 @@
       </c>
       <c r="G18" s="128">
         <f>DATA!F7</f>
-        <v>3534</v>
+        <v>3788.8642857142854</v>
       </c>
       <c r="H18" s="128">
         <f>DATA!G7</f>
-        <v>3534</v>
+        <v>3788.8642857142854</v>
       </c>
       <c r="I18" s="125">
-        <v>-21204</v>
+        <v>-26522.05</v>
       </c>
       <c r="J18" s="129">
         <f t="shared" si="3"/>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="K18" s="111">
         <f t="shared" si="21"/>
-        <v>-1.0366098692064684E-2</v>
+        <v>-1.2229803842975976E-2</v>
       </c>
       <c r="L18" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="N18" s="130">
         <f t="shared" si="28"/>
-        <v>21204</v>
+        <v>26522.05</v>
       </c>
       <c r="O18" s="130" t="str">
         <f t="shared" si="6"/>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="AB18" s="138">
         <f t="shared" si="14"/>
-        <v>-1.0366098692064684E-2</v>
+        <v>-1.2229803842975976E-2</v>
       </c>
       <c r="AC18" s="135">
         <f t="shared" si="25"/>
@@ -5699,39 +5699,39 @@
       </c>
       <c r="D32" s="153">
         <f>SUM(D13:D31)</f>
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="E32" s="153">
         <f>SUM(E13:E31)</f>
-        <v>507</v>
+        <v>539</v>
       </c>
       <c r="F32" s="154">
         <f>IFERROR(SUM(F13:F31)/G10,)</f>
-        <v>1.64891452991453</v>
+        <v>1.6586669668906802</v>
       </c>
       <c r="G32" s="155">
         <f>IFERROR(SUM(G13:G31)/G10,)</f>
-        <v>6547.8697179487181</v>
+        <v>6625.032548099417</v>
       </c>
       <c r="H32" s="155">
         <f>IFERROR(SUM(H13:H31)/G10,)</f>
-        <v>4747.5001901813357</v>
+        <v>4786.4157641995453</v>
       </c>
       <c r="I32" s="155">
         <f>SUM(I13:I31)</f>
-        <v>2045514</v>
+        <v>2168640.6700000004</v>
       </c>
       <c r="J32" s="156">
         <f>IFERROR(I32/C32,)</f>
-        <v>0.68183800000000006</v>
+        <v>0.72288022333333346</v>
       </c>
       <c r="K32" s="156">
         <f>SUM(K13:K31)</f>
-        <v>0.99999999999999989</v>
+        <v>0.99999999999999978</v>
       </c>
       <c r="L32" s="155">
         <f>SUM(L13:L31)</f>
-        <v>8876.2663741240576</v>
+        <v>18552.178142319906</v>
       </c>
       <c r="M32" s="155">
         <f>SUM(M13:M31)</f>
@@ -5739,33 +5739,33 @@
       </c>
       <c r="N32" s="155">
         <f>SUM(N13:N31)</f>
-        <v>954485.99999999988</v>
+        <v>831359.33</v>
       </c>
       <c r="O32" s="155">
         <f>SUM(O13:O31)</f>
-        <v>155546.99999999997</v>
+        <v>160967.45600000001</v>
       </c>
       <c r="P32" s="157"/>
       <c r="Q32" s="152">
         <f>SUM(Q13:Q31)</f>
-        <v>2566855.5200000005</v>
+        <v>2620482.6312307692</v>
       </c>
       <c r="R32" s="156">
         <f>SUM(R13:R31)</f>
-        <v>0.99999999999999978</v>
+        <v>1</v>
       </c>
       <c r="S32" s="155">
         <f>SUM(S13:S31)</f>
-        <v>29886.147830837002</v>
+        <v>31815.633283418945</v>
       </c>
       <c r="T32" s="158">
         <f>IFERROR(Q32/C32,)</f>
-        <v>0.85561850666666683</v>
+        <v>0.87349421041025643</v>
       </c>
       <c r="U32" s="165"/>
       <c r="V32" s="166">
         <f>SUM(V13:V31)</f>
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="W32" s="167">
         <f>SUM(W13:W31)</f>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="Z32" s="164">
         <f>SUM(Z13:Z31)</f>
-        <v>5117</v>
+        <v>5274</v>
       </c>
       <c r="AA32" s="162">
         <f>SUM(AA13:AA31)</f>
@@ -6948,25 +6948,25 @@
         <v>65</v>
       </c>
       <c r="B2" s="19">
-        <v>449508</v>
+        <v>476526.62</v>
       </c>
       <c r="C2" s="18">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D2" s="18">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E2" s="16">
         <f>IFERROR((D2/C2),"")</f>
-        <v>1.52</v>
+        <v>1.5249999999999999</v>
       </c>
       <c r="F2" s="17">
         <f>IFERROR((B2/C2),"")</f>
-        <v>5993.44</v>
+        <v>5956.5827499999996</v>
       </c>
       <c r="G2" s="17">
         <f>IFERROR((B2/D2),"")</f>
-        <v>3943.0526315789475</v>
+        <v>3905.9559016393441</v>
       </c>
       <c r="Q2" s="6" t="s">
         <v>38</v>
@@ -6980,25 +6980,25 @@
         <v>67</v>
       </c>
       <c r="B3" s="19">
-        <v>499700</v>
+        <v>553432.48</v>
       </c>
       <c r="C3" s="18">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D3" s="18">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E3" s="16">
         <f t="shared" ref="E3:E20" si="0">IFERROR((D3/C3),"")</f>
-        <v>1.5384615384615385</v>
+        <v>1.558139534883721</v>
       </c>
       <c r="F3" s="17">
         <f t="shared" ref="F3:F20" si="1">IFERROR((B3/C3),"")</f>
-        <v>6406.4102564102568</v>
+        <v>6435.2613953488371</v>
       </c>
       <c r="G3" s="17">
         <f t="shared" ref="G3:G20" si="2">IFERROR((B3/D3),"")</f>
-        <v>4164.166666666667</v>
+        <v>4130.0931343283582</v>
       </c>
       <c r="Q3" s="6" t="s">
         <v>40</v>
@@ -7012,7 +7012,7 @@
         <v>64</v>
       </c>
       <c r="B4" s="174">
-        <v>412520</v>
+        <v>412520.46</v>
       </c>
       <c r="C4" s="18">
         <v>75</v>
@@ -7026,11 +7026,11 @@
       </c>
       <c r="F4" s="17">
         <f t="shared" si="1"/>
-        <v>5500.2666666666664</v>
+        <v>5500.2728000000006</v>
       </c>
       <c r="G4" s="17">
         <f t="shared" si="2"/>
-        <v>4125.2</v>
+        <v>4125.2046</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -7038,25 +7038,25 @@
         <v>66</v>
       </c>
       <c r="B5" s="175">
-        <v>457293</v>
+        <v>482902.48</v>
       </c>
       <c r="C5" s="18">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D5" s="18">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E5" s="16">
         <f t="shared" si="0"/>
-        <v>1.6527777777777777</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="F5" s="17">
         <f t="shared" si="1"/>
-        <v>6351.291666666667</v>
+        <v>6353.98</v>
       </c>
       <c r="G5" s="17">
         <f t="shared" si="2"/>
-        <v>3842.798319327731</v>
+        <v>3894.3748387096771</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -7064,25 +7064,25 @@
         <v>68</v>
       </c>
       <c r="B6" s="19">
-        <v>247697</v>
+        <v>269780.68</v>
       </c>
       <c r="C6" s="18">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D6" s="18">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E6" s="16">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>1.2452830188679245</v>
       </c>
       <c r="F6" s="17">
         <f t="shared" si="1"/>
-        <v>4953.9399999999996</v>
+        <v>5090.2015094339622</v>
       </c>
       <c r="G6" s="17">
         <f t="shared" si="2"/>
-        <v>4128.2833333333338</v>
+        <v>4087.5860606060605</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -7090,13 +7090,13 @@
         <v>69</v>
       </c>
       <c r="B7" s="19">
-        <v>-21204</v>
+        <v>-26522.05</v>
       </c>
       <c r="C7" s="18">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="D7" s="18">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="E7" s="16">
         <f t="shared" si="0"/>
@@ -7104,11 +7104,11 @@
       </c>
       <c r="F7" s="17">
         <f t="shared" si="1"/>
-        <v>3534</v>
+        <v>3788.8642857142854</v>
       </c>
       <c r="G7" s="17">
         <f t="shared" si="2"/>
-        <v>3534</v>
+        <v>3788.8642857142854</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">

--- a/EKİM SD KARNE.xlsx
+++ b/EKİM SD KARNE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\UYGULAMA İÇİN GEREKLİ DOSYALAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34086876-C49C-4527-B86C-725EF7216BF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D959C2-724B-4DA9-BED9-916D7C381E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SD KARNE" sheetId="1" r:id="rId1"/>
@@ -2690,11 +2690,11 @@
       </c>
       <c r="B9" s="75">
         <f>I32</f>
-        <v>2168640.6700000004</v>
+        <v>2247519.41</v>
       </c>
       <c r="C9" s="76">
         <f>IFERROR(B9/A9,)</f>
-        <v>0.72288022333333346</v>
+        <v>0.74917313666666674</v>
       </c>
       <c r="D9" s="168">
         <f>IFERROR(IF(B9&lt;=A9,A4,IF(AND(B9&gt;A9,B9&lt;B1),A4,IF(AND(B9&gt;=B1,B9&lt;C1),B4,IF(AND(B9&gt;=C1,B9&lt;D1),C4,IF(AND(B9&gt;=D1,B9&lt;E1),D4,IF(AND(B9&gt;=E1,B9&lt;F1),E4,IF(AND(B9&gt;=F1,B9&lt;G1),F4,IF(AND(B9&gt;=G1,B9&lt;H1),G4,IF(AND(B9&gt;=H1,B9&lt;I1),H4,IF(AND(B9&gt;=I1,B9&lt;J1),I4,IF(AND(B9&gt;=J1,B9&lt;K1),J4,IF(B9&gt;=K4,K4,K4)))))))))))),)</f>
@@ -2761,27 +2761,27 @@
       </c>
       <c r="H10" s="83">
         <f ca="1">B11-M10</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I10" s="84">
         <f>C11</f>
-        <v>5274</v>
+        <v>5390</v>
       </c>
       <c r="J10" s="85">
         <f ca="1">I10/H10</f>
-        <v>202.84615384615384</v>
+        <v>199.62962962962962</v>
       </c>
       <c r="K10" s="85">
         <f>IFERROR(I10/G10,)</f>
-        <v>1054.8</v>
+        <v>1078</v>
       </c>
       <c r="L10" s="86">
         <f ca="1">IFERROR(J10/G10,)</f>
-        <v>40.569230769230771</v>
+        <v>39.925925925925924</v>
       </c>
       <c r="M10" s="87">
         <f ca="1">(M11-A11)+B11</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N10" s="2">
         <f>LOOKUP(A9,'PRİM HAVUZU (SV SİSTEM)'!$A:$A,'PRİM HAVUZU (SV SİSTEM)'!$C:$C)*A9</f>
@@ -2804,14 +2804,14 @@
     <row r="11" spans="1:58" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="169">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="B11" s="170">
         <f ca="1">(N11-M11)+1</f>
         <v>31</v>
       </c>
       <c r="C11" s="171">
-        <v>5274</v>
+        <v>5390</v>
       </c>
       <c r="F11" s="66"/>
       <c r="K11" s="89"/>
@@ -2977,75 +2977,75 @@
       </c>
       <c r="D13" s="107" cm="1">
         <f t="array" ref="D13:D31">DATA!C2:C20</f>
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E13" s="107" cm="1">
         <f t="array" ref="E13:E31">DATA!D2:D20</f>
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F13" s="108">
         <f>DATA!E2</f>
-        <v>1.5249999999999999</v>
+        <v>1.5121951219512195</v>
       </c>
       <c r="G13" s="109">
         <f>DATA!F2</f>
-        <v>5956.5827499999996</v>
+        <v>5902.6829268292686</v>
       </c>
       <c r="H13" s="109">
         <f>DATA!G2</f>
-        <v>3905.9559016393441</v>
+        <v>3903.3870967741937</v>
       </c>
       <c r="I13" s="106" cm="1">
         <f t="array" ref="I13:I31">DATA!B2:B20</f>
-        <v>476526.62</v>
+        <v>484020</v>
       </c>
       <c r="J13" s="110">
         <f t="shared" ref="J13:J31" si="3">IFERROR(I13/C13,0)</f>
-        <v>0.99916871935483875</v>
+        <v>1.0148806451612904</v>
       </c>
       <c r="K13" s="111">
         <f>IFERROR(I13/$I$32,)</f>
-        <v>0.21973516709893665</v>
+        <v>0.21535742821460216</v>
       </c>
       <c r="L13" s="112">
         <f t="shared" ref="L13:L31" si="4">IFERROR(IF(J13&lt;0.85,"",IF(AND(J13&gt;0.85,J13&lt;1),$M$2*AB13*AJ13,$M$2*AB13*AJ13)),"")</f>
-        <v>9884.1272864443672</v>
+        <v>9983.7550146007416</v>
       </c>
       <c r="M13" s="113">
         <f t="shared" ref="M13:M31" si="5">IFERROR((($E$9+$F$9)*AC13),"")</f>
         <v>7296.9230769230762</v>
       </c>
-      <c r="N13" s="114">
+      <c r="N13" s="114" t="str">
         <f>IFERROR(IF(C13-I13&lt;0,"",C13-I13),"")</f>
-        <v>396.45692307688296</v>
-      </c>
-      <c r="O13" s="114">
+        <v/>
+      </c>
+      <c r="O13" s="114" t="str">
         <f t="shared" ref="O13:O31" si="6">IFERROR(IF(N13/(W13-V13)&gt;0,N13/(W13-V13),""),"")</f>
-        <v>79.291384615376586</v>
+        <v/>
       </c>
       <c r="P13" s="110">
         <f t="shared" ref="P13:P31" si="7">IFERROR(I13/C13,0)</f>
-        <v>0.99916871935483875</v>
+        <v>1.0148806451612904</v>
       </c>
       <c r="Q13" s="109">
         <f t="shared" ref="Q13:Q31" si="8">IF(V13="",0,IF(W13=V13,I13,(I13/V13)*(W13-V13)+I13))</f>
-        <v>568166.3546153846</v>
+        <v>577100.76923076925</v>
       </c>
       <c r="R13" s="115">
         <f>IFERROR(Q13/$Q$32,)</f>
-        <v>0.21681744723052498</v>
+        <v>0.21259691097954184</v>
       </c>
       <c r="S13" s="106">
         <f>IFERROR(IF(T13&lt;0.85,"",IF(AND(T13&gt;0.85,T13&lt;1),$M$2*AD13*AK13,$M$2*AD13*AK13)),"")</f>
-        <v>11842.785785178505</v>
+        <v>11709.837856753164</v>
       </c>
       <c r="T13" s="110">
         <f t="shared" ref="T13:T31" si="9">IFERROR(Q13/C13,0)</f>
-        <v>1.19131655</v>
+        <v>1.2100500000000001</v>
       </c>
       <c r="U13" s="116">
         <f t="shared" ref="U13:U31" si="10">IFERROR(D13/Z13,0)</f>
-        <v>7.5260348297890953E-2</v>
+        <v>7.5481661195946917E-2</v>
       </c>
       <c r="V13" s="62">
         <v>26</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z13" s="118">
         <f t="shared" ref="Z13:Z31" si="12">(V13/$V$32)*$I$10</f>
-        <v>1062.9767441860465</v>
+        <v>1086.3565891472867</v>
       </c>
       <c r="AA13" s="119">
         <f t="shared" ref="AA13:AA31" si="13">IFERROR(((Y13/$Y$32)*$A$9),"")</f>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AB13" s="120">
         <f t="shared" ref="AB13:AB31" si="14">I13/$I$32</f>
-        <v>0.21973516709893665</v>
+        <v>0.21535742821460216</v>
       </c>
       <c r="AC13" s="121">
         <f>AA13/$C$32</f>
@@ -3075,15 +3075,15 @@
       </c>
       <c r="AD13" s="120">
         <f>Q13/$Q$32</f>
-        <v>0.21681744723052498</v>
+        <v>0.21259691097954184</v>
       </c>
       <c r="AE13" s="120">
         <f t="shared" ref="AE13:AE31" si="15">I13/C13</f>
-        <v>0.99916871935483875</v>
+        <v>1.0148806451612904</v>
       </c>
       <c r="AF13" s="120">
         <f t="shared" ref="AF13:AF31" si="16">Q13/C13</f>
-        <v>1.19131655</v>
+        <v>1.2100500000000001</v>
       </c>
       <c r="AG13" s="120">
         <f>IFERROR(VLOOKUP(A13,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3099,11 +3099,11 @@
       </c>
       <c r="AJ13" s="121">
         <f t="shared" ref="AJ13:AJ31" si="18">IFERROR(LOOKUP(AE13,AL:AL,AM:AM),"")</f>
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="AK13" s="123">
         <f t="shared" ref="AK13:AK31" si="19">IFERROR(LOOKUP(AF13,AL:AL,AM:AM),"")</f>
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AL13" s="93">
         <v>0.87</v>
@@ -3124,37 +3124,37 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D14" s="126">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E14" s="126">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F14" s="127">
         <f>DATA!E3</f>
-        <v>1.558139534883721</v>
+        <v>1.5632183908045978</v>
       </c>
       <c r="G14" s="128">
         <f>DATA!F3</f>
-        <v>6435.2613953488371</v>
+        <v>6424.4942528735628</v>
       </c>
       <c r="H14" s="128">
         <f>DATA!G3</f>
-        <v>4130.0931343283582</v>
+        <v>4109.786764705882</v>
       </c>
       <c r="I14" s="125">
-        <v>553432.48</v>
+        <v>558931</v>
       </c>
       <c r="J14" s="129">
         <f t="shared" si="3"/>
-        <v>0.87031720645161292</v>
+        <v>0.87896407258064524</v>
       </c>
       <c r="K14" s="111">
         <f t="shared" ref="K14:K31" si="21">IFERROR(I14/$I$32,)</f>
-        <v>0.25519787010173517</v>
+        <v>0.24868795237679392</v>
       </c>
       <c r="L14" s="112">
         <f t="shared" si="4"/>
-        <v>8668.0508558755373</v>
+        <v>8446.9349904301835</v>
       </c>
       <c r="M14" s="113">
         <f t="shared" si="5"/>
@@ -3162,35 +3162,35 @@
       </c>
       <c r="N14" s="130">
         <f t="shared" ref="N14:N31" si="22">IFERROR(IF(C14-I14&lt;0,"",C14-I14),"")</f>
-        <v>82464.955897435895</v>
+        <v>76966.435897435877</v>
       </c>
       <c r="O14" s="130">
         <f t="shared" si="6"/>
-        <v>16492.99117948718</v>
+        <v>15393.287179487175</v>
       </c>
       <c r="P14" s="129">
         <f t="shared" si="7"/>
-        <v>0.87031720645161292</v>
+        <v>0.87896407258064524</v>
       </c>
       <c r="Q14" s="109">
         <f t="shared" si="8"/>
-        <v>659861.80307692301</v>
+        <v>666417.73076923075</v>
       </c>
       <c r="R14" s="115">
         <f t="shared" ref="R14:R31" si="23">IFERROR(Q14/$Q$32,)</f>
-        <v>0.25180926414574401</v>
+        <v>0.24550019431161171</v>
       </c>
       <c r="S14" s="106">
         <f t="shared" ref="S14:S31" si="24">IFERROR(IF(T14&lt;0.85,"",IF(AND(T14&gt;0.85,T14&lt;1),$M$2*AD14*AK14,$M$2*AD14*AK14)),"")</f>
-        <v>11904.786581018339</v>
+        <v>11719.197275659097</v>
       </c>
       <c r="T14" s="129">
         <f t="shared" si="9"/>
-        <v>1.0376858999999998</v>
+        <v>1.047995625</v>
       </c>
       <c r="U14" s="131">
         <f t="shared" si="10"/>
-        <v>8.0904874420232781E-2</v>
+        <v>8.0084201512772943E-2</v>
       </c>
       <c r="V14" s="62">
         <v>26</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="Z14" s="133">
         <f t="shared" si="12"/>
-        <v>1062.9767441860465</v>
+        <v>1086.3565891472867</v>
       </c>
       <c r="AA14" s="17">
         <f t="shared" si="13"/>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="AB14" s="134">
         <f t="shared" si="14"/>
-        <v>0.25519787010173517</v>
+        <v>0.24868795237679392</v>
       </c>
       <c r="AC14" s="135">
         <f t="shared" ref="AC14:AC31" si="25">AA14/$C$32</f>
@@ -3220,15 +3220,15 @@
       </c>
       <c r="AD14" s="134">
         <f t="shared" ref="AD14:AD18" si="26">Q14/$Q$32</f>
-        <v>0.25180926414574401</v>
+        <v>0.24550019431161171</v>
       </c>
       <c r="AE14" s="134">
         <f t="shared" si="15"/>
-        <v>0.87031720645161292</v>
+        <v>0.87896407258064524</v>
       </c>
       <c r="AF14" s="134">
         <f t="shared" si="16"/>
-        <v>1.0376858999999998</v>
+        <v>1.047995625</v>
       </c>
       <c r="AG14" s="134">
         <f>IFERROR(VLOOKUP(A14,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="AK14" s="137">
         <f t="shared" si="19"/>
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AL14" s="93">
         <v>0.88</v>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="K15" s="111">
         <f t="shared" si="21"/>
-        <v>0.19022075243106085</v>
+        <v>0.1835447819336074</v>
       </c>
       <c r="L15" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="R15" s="115">
         <f t="shared" si="23"/>
-        <v>0.18890587027760627</v>
+        <v>0.18236102986746891</v>
       </c>
       <c r="S15" s="106" t="str">
         <f t="shared" si="24"/>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="U15" s="131">
         <f t="shared" si="10"/>
-        <v>7.3378839590443681E-2</v>
+        <v>7.179962894248608E-2</v>
       </c>
       <c r="V15" s="62">
         <v>25</v>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="Z15" s="133">
         <f t="shared" si="12"/>
-        <v>1022.093023255814</v>
+        <v>1044.5736434108528</v>
       </c>
       <c r="AA15" s="17">
         <f t="shared" si="13"/>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="AB15" s="134">
         <f t="shared" si="14"/>
-        <v>0.19022075243106085</v>
+        <v>0.1835447819336074</v>
       </c>
       <c r="AC15" s="135">
         <f t="shared" si="25"/>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="AD15" s="134">
         <f t="shared" si="26"/>
-        <v>0.18890587027760627</v>
+        <v>0.18236102986746891</v>
       </c>
       <c r="AE15" s="134">
         <f t="shared" si="15"/>
@@ -3414,33 +3414,33 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D16" s="126">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="E16" s="126">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="F16" s="127">
         <f>DATA!E5</f>
-        <v>1.631578947368421</v>
+        <v>1.6506024096385543</v>
       </c>
       <c r="G16" s="128">
         <f>DATA!F5</f>
-        <v>6353.98</v>
+        <v>6420.3012048192768</v>
       </c>
       <c r="H16" s="128">
         <f>DATA!G5</f>
-        <v>3894.3748387096771</v>
+        <v>3889.6715328467153</v>
       </c>
       <c r="I16" s="125">
-        <v>482902.48</v>
+        <v>532885</v>
       </c>
       <c r="J16" s="129">
         <f t="shared" si="3"/>
-        <v>0.75940309354838709</v>
+        <v>0.8380046370967742</v>
       </c>
       <c r="K16" s="111">
         <f t="shared" si="21"/>
-        <v>0.22267519311993716</v>
+        <v>0.23709917593103233</v>
       </c>
       <c r="L16" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3452,35 +3452,35 @@
       </c>
       <c r="N16" s="130">
         <f t="shared" ref="N16:N25" si="28">IFERROR(IF(C16-I16&lt;0,"",C16-I16),"")</f>
-        <v>152994.9558974359</v>
+        <v>103012.43589743588</v>
       </c>
       <c r="O16" s="130">
         <f t="shared" si="6"/>
-        <v>30598.99117948718</v>
+        <v>20602.487179487176</v>
       </c>
       <c r="P16" s="129">
         <f t="shared" si="7"/>
-        <v>0.75940309354838709</v>
+        <v>0.8380046370967742</v>
       </c>
       <c r="Q16" s="109">
         <f t="shared" si="8"/>
-        <v>575768.34153846151</v>
+        <v>635362.88461538462</v>
       </c>
       <c r="R16" s="115">
         <f t="shared" si="23"/>
-        <v>0.21971843456487206</v>
+        <v>0.23405996633885615</v>
       </c>
       <c r="S16" s="106">
         <f t="shared" si="24"/>
-        <v>8068.0609172221029</v>
+        <v>10528.485405854428</v>
       </c>
       <c r="T16" s="129">
         <f t="shared" si="9"/>
-        <v>0.90544214999999995</v>
+        <v>0.99915937500000007</v>
       </c>
       <c r="U16" s="131">
         <f t="shared" si="10"/>
-        <v>7.149733088299641E-2</v>
+        <v>7.6402169259312119E-2</v>
       </c>
       <c r="V16" s="62">
         <v>26</v>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="Z16" s="133">
         <f t="shared" si="12"/>
-        <v>1062.9767441860465</v>
+        <v>1086.3565891472867</v>
       </c>
       <c r="AA16" s="17">
         <f t="shared" si="13"/>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="AB16" s="134">
         <f t="shared" si="14"/>
-        <v>0.22267519311993716</v>
+        <v>0.23709917593103233</v>
       </c>
       <c r="AC16" s="135">
         <f t="shared" si="25"/>
@@ -3510,15 +3510,15 @@
       </c>
       <c r="AD16" s="134">
         <f t="shared" si="26"/>
-        <v>0.21971843456487206</v>
+        <v>0.23405996633885615</v>
       </c>
       <c r="AE16" s="134">
         <f t="shared" si="15"/>
-        <v>0.75940309354838709</v>
+        <v>0.8380046370967742</v>
       </c>
       <c r="AF16" s="134">
         <f t="shared" si="16"/>
-        <v>0.90544214999999995</v>
+        <v>0.99915937500000007</v>
       </c>
       <c r="AG16" s="134">
         <f>IFERROR(VLOOKUP(A16,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3538,7 +3538,7 @@
       </c>
       <c r="AK16" s="137">
         <f t="shared" si="19"/>
-        <v>0.8</v>
+        <v>0.98</v>
       </c>
       <c r="AL16" s="93">
         <v>0.9</v>
@@ -3559,33 +3559,33 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D17" s="126">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E17" s="126">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F17" s="127">
         <f>DATA!E6</f>
-        <v>1.2452830188679245</v>
+        <v>1.2413793103448276</v>
       </c>
       <c r="G17" s="128">
         <f>DATA!F6</f>
-        <v>5090.2015094339622</v>
+        <v>4925.6034482758623</v>
       </c>
       <c r="H17" s="128">
         <f>DATA!G6</f>
-        <v>4087.5860606060605</v>
+        <v>3967.8472222222222</v>
       </c>
       <c r="I17" s="125">
-        <v>269780.68</v>
+        <v>285685</v>
       </c>
       <c r="J17" s="129">
         <f t="shared" si="3"/>
-        <v>0.42425187580645163</v>
+        <v>0.44926270161290321</v>
       </c>
       <c r="K17" s="111">
         <f t="shared" si="21"/>
-        <v>0.12440082109130599</v>
+        <v>0.12711124928616299</v>
       </c>
       <c r="L17" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3597,23 +3597,23 @@
       </c>
       <c r="N17" s="130">
         <f t="shared" si="28"/>
-        <v>366116.75589743588</v>
+        <v>350212.43589743588</v>
       </c>
       <c r="O17" s="130">
         <f t="shared" si="6"/>
-        <v>73223.351179487174</v>
+        <v>70042.487179487172</v>
       </c>
       <c r="P17" s="129">
         <f t="shared" si="7"/>
-        <v>0.42425187580645163</v>
+        <v>0.44926270161290321</v>
       </c>
       <c r="Q17" s="109">
         <f t="shared" si="8"/>
-        <v>321661.58</v>
+        <v>340624.42307692306</v>
       </c>
       <c r="R17" s="115">
         <f t="shared" si="23"/>
-        <v>0.12274898378125267</v>
+        <v>0.12548189850252139</v>
       </c>
       <c r="S17" s="106" t="str">
         <f t="shared" si="24"/>
@@ -3621,11 +3621,11 @@
       </c>
       <c r="T17" s="129">
         <f t="shared" si="9"/>
-        <v>0.50583877500000007</v>
+        <v>0.53565937500000005</v>
       </c>
       <c r="U17" s="131">
         <f t="shared" si="10"/>
-        <v>4.9859980747352761E-2</v>
+        <v>5.3389467675181962E-2</v>
       </c>
       <c r="V17" s="62">
         <v>26</v>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="Z17" s="133">
         <f t="shared" si="12"/>
-        <v>1062.9767441860465</v>
+        <v>1086.3565891472867</v>
       </c>
       <c r="AA17" s="17">
         <f t="shared" si="13"/>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="AB17" s="134">
         <f t="shared" si="14"/>
-        <v>0.12440082109130599</v>
+        <v>0.12711124928616299</v>
       </c>
       <c r="AC17" s="135">
         <f t="shared" si="25"/>
@@ -3655,15 +3655,15 @@
       </c>
       <c r="AD17" s="134">
         <f t="shared" si="26"/>
-        <v>0.12274898378125267</v>
+        <v>0.12548189850252139</v>
       </c>
       <c r="AE17" s="134">
         <f t="shared" si="15"/>
-        <v>0.42425187580645163</v>
+        <v>0.44926270161290321</v>
       </c>
       <c r="AF17" s="134">
         <f t="shared" si="16"/>
-        <v>0.50583877500000007</v>
+        <v>0.53565937500000005</v>
       </c>
       <c r="AG17" s="134">
         <f>IFERROR(VLOOKUP(A17,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="K18" s="111">
         <f t="shared" si="21"/>
-        <v>-1.2229803842975976E-2</v>
+        <v>-1.1800587742198852E-2</v>
       </c>
       <c r="L18" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="AB18" s="138">
         <f t="shared" si="14"/>
-        <v>-1.2229803842975976E-2</v>
+        <v>-1.1800587742198852E-2</v>
       </c>
       <c r="AC18" s="135">
         <f t="shared" si="25"/>
@@ -5699,39 +5699,39 @@
       </c>
       <c r="D32" s="153">
         <f>SUM(D13:D31)</f>
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="E32" s="153">
         <f>SUM(E13:E31)</f>
-        <v>539</v>
+        <v>562</v>
       </c>
       <c r="F32" s="154">
         <f>IFERROR(SUM(F13:F31)/G10,)</f>
-        <v>1.6586669668906802</v>
+        <v>1.6601457132145065</v>
       </c>
       <c r="G32" s="155">
         <f>IFERROR(SUM(G13:G31)/G10,)</f>
-        <v>6625.032548099417</v>
+        <v>6592.4437837024507</v>
       </c>
       <c r="H32" s="155">
         <f>IFERROR(SUM(H13:H31)/G10,)</f>
-        <v>4786.4157641995453</v>
+        <v>4756.9523004526591</v>
       </c>
       <c r="I32" s="155">
         <f>SUM(I13:I31)</f>
-        <v>2168640.6700000004</v>
+        <v>2247519.41</v>
       </c>
       <c r="J32" s="156">
         <f>IFERROR(I32/C32,)</f>
-        <v>0.72288022333333346</v>
+        <v>0.74917313666666674</v>
       </c>
       <c r="K32" s="156">
         <f>SUM(K13:K31)</f>
-        <v>0.99999999999999978</v>
+        <v>1</v>
       </c>
       <c r="L32" s="155">
         <f>SUM(L13:L31)</f>
-        <v>18552.178142319906</v>
+        <v>18430.690005030927</v>
       </c>
       <c r="M32" s="155">
         <f>SUM(M13:M31)</f>
@@ -5739,16 +5739,16 @@
       </c>
       <c r="N32" s="155">
         <f>SUM(N13:N31)</f>
-        <v>831359.33</v>
+        <v>759577.51307692309</v>
       </c>
       <c r="O32" s="155">
         <f>SUM(O13:O31)</f>
-        <v>160967.45600000001</v>
+        <v>146611.09261538461</v>
       </c>
       <c r="P32" s="157"/>
       <c r="Q32" s="152">
         <f>SUM(Q13:Q31)</f>
-        <v>2620482.6312307692</v>
+        <v>2714530.3596923077</v>
       </c>
       <c r="R32" s="156">
         <f>SUM(R13:R31)</f>
@@ -5756,11 +5756,11 @@
       </c>
       <c r="S32" s="155">
         <f>SUM(S13:S31)</f>
-        <v>31815.633283418945</v>
+        <v>33957.52053826669</v>
       </c>
       <c r="T32" s="158">
         <f>IFERROR(Q32/C32,)</f>
-        <v>0.87349421041025643</v>
+        <v>0.9048434532307692</v>
       </c>
       <c r="U32" s="165"/>
       <c r="V32" s="166">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="Z32" s="164">
         <f>SUM(Z13:Z31)</f>
-        <v>5274</v>
+        <v>5390</v>
       </c>
       <c r="AA32" s="162">
         <f>SUM(AA13:AA31)</f>
@@ -6948,25 +6948,25 @@
         <v>65</v>
       </c>
       <c r="B2" s="19">
-        <v>476526.62</v>
+        <v>484020</v>
       </c>
       <c r="C2" s="18">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D2" s="18">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E2" s="16">
         <f>IFERROR((D2/C2),"")</f>
-        <v>1.5249999999999999</v>
+        <v>1.5121951219512195</v>
       </c>
       <c r="F2" s="17">
         <f>IFERROR((B2/C2),"")</f>
-        <v>5956.5827499999996</v>
+        <v>5902.6829268292686</v>
       </c>
       <c r="G2" s="17">
         <f>IFERROR((B2/D2),"")</f>
-        <v>3905.9559016393441</v>
+        <v>3903.3870967741937</v>
       </c>
       <c r="Q2" s="6" t="s">
         <v>38</v>
@@ -6980,25 +6980,25 @@
         <v>67</v>
       </c>
       <c r="B3" s="19">
-        <v>553432.48</v>
+        <v>558931</v>
       </c>
       <c r="C3" s="18">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D3" s="18">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E3" s="16">
         <f t="shared" ref="E3:E20" si="0">IFERROR((D3/C3),"")</f>
-        <v>1.558139534883721</v>
+        <v>1.5632183908045978</v>
       </c>
       <c r="F3" s="17">
         <f t="shared" ref="F3:F20" si="1">IFERROR((B3/C3),"")</f>
-        <v>6435.2613953488371</v>
+        <v>6424.4942528735628</v>
       </c>
       <c r="G3" s="17">
         <f t="shared" ref="G3:G20" si="2">IFERROR((B3/D3),"")</f>
-        <v>4130.0931343283582</v>
+        <v>4109.786764705882</v>
       </c>
       <c r="Q3" s="6" t="s">
         <v>40</v>
@@ -7038,25 +7038,25 @@
         <v>66</v>
       </c>
       <c r="B5" s="175">
-        <v>482902.48</v>
+        <v>532885</v>
       </c>
       <c r="C5" s="18">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D5" s="18">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E5" s="16">
         <f t="shared" si="0"/>
-        <v>1.631578947368421</v>
+        <v>1.6506024096385543</v>
       </c>
       <c r="F5" s="17">
         <f t="shared" si="1"/>
-        <v>6353.98</v>
+        <v>6420.3012048192768</v>
       </c>
       <c r="G5" s="17">
         <f t="shared" si="2"/>
-        <v>3894.3748387096771</v>
+        <v>3889.6715328467153</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -7064,25 +7064,25 @@
         <v>68</v>
       </c>
       <c r="B6" s="19">
-        <v>269780.68</v>
+        <v>285685</v>
       </c>
       <c r="C6" s="18">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D6" s="18">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E6" s="16">
         <f t="shared" si="0"/>
-        <v>1.2452830188679245</v>
+        <v>1.2413793103448276</v>
       </c>
       <c r="F6" s="17">
         <f t="shared" si="1"/>
-        <v>5090.2015094339622</v>
+        <v>4925.6034482758623</v>
       </c>
       <c r="G6" s="17">
         <f t="shared" si="2"/>
-        <v>4087.5860606060605</v>
+        <v>3967.8472222222222</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">

--- a/EKİM SD KARNE.xlsx
+++ b/EKİM SD KARNE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\UYGULAMA İÇİN GEREKLİ DOSYALAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D959C2-724B-4DA9-BED9-916D7C381E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD84C00E-0B6B-4159-A5D9-D03778DBF2CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SD KARNE" sheetId="1" r:id="rId1"/>
@@ -2690,11 +2690,11 @@
       </c>
       <c r="B9" s="75">
         <f>I32</f>
-        <v>2247519.41</v>
+        <v>2330510.9500000002</v>
       </c>
       <c r="C9" s="76">
         <f>IFERROR(B9/A9,)</f>
-        <v>0.74917313666666674</v>
+        <v>0.7768369833333334</v>
       </c>
       <c r="D9" s="168">
         <f>IFERROR(IF(B9&lt;=A9,A4,IF(AND(B9&gt;A9,B9&lt;B1),A4,IF(AND(B9&gt;=B1,B9&lt;C1),B4,IF(AND(B9&gt;=C1,B9&lt;D1),C4,IF(AND(B9&gt;=D1,B9&lt;E1),D4,IF(AND(B9&gt;=E1,B9&lt;F1),E4,IF(AND(B9&gt;=F1,B9&lt;G1),F4,IF(AND(B9&gt;=G1,B9&lt;H1),G4,IF(AND(B9&gt;=H1,B9&lt;I1),H4,IF(AND(B9&gt;=I1,B9&lt;J1),I4,IF(AND(B9&gt;=J1,B9&lt;K1),J4,IF(B9&gt;=K4,K4,K4)))))))))))),)</f>
@@ -2761,27 +2761,27 @@
       </c>
       <c r="H10" s="83">
         <f ca="1">B11-M10</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I10" s="84">
         <f>C11</f>
-        <v>5390</v>
+        <v>5616</v>
       </c>
       <c r="J10" s="85">
         <f ca="1">I10/H10</f>
-        <v>199.62962962962962</v>
+        <v>200.57142857142858</v>
       </c>
       <c r="K10" s="85">
         <f>IFERROR(I10/G10,)</f>
-        <v>1078</v>
+        <v>1123.2</v>
       </c>
       <c r="L10" s="86">
         <f ca="1">IFERROR(J10/G10,)</f>
-        <v>39.925925925925924</v>
+        <v>40.114285714285714</v>
       </c>
       <c r="M10" s="87">
         <f ca="1">(M11-A11)+B11</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N10" s="2">
         <f>LOOKUP(A9,'PRİM HAVUZU (SV SİSTEM)'!$A:$A,'PRİM HAVUZU (SV SİSTEM)'!$C:$C)*A9</f>
@@ -2804,14 +2804,14 @@
     <row r="11" spans="1:58" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="169">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B11" s="170">
         <f ca="1">(N11-M11)+1</f>
         <v>31</v>
       </c>
       <c r="C11" s="171">
-        <v>5390</v>
+        <v>5616</v>
       </c>
       <c r="F11" s="66"/>
       <c r="K11" s="89"/>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="D13" s="107" cm="1">
         <f t="array" ref="D13:D31">DATA!C2:C20</f>
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E13" s="107" cm="1">
         <f t="array" ref="E13:E31">DATA!D2:D20</f>
@@ -2985,31 +2985,31 @@
       </c>
       <c r="F13" s="108">
         <f>DATA!E2</f>
-        <v>1.5121951219512195</v>
+        <v>1.441860465116279</v>
       </c>
       <c r="G13" s="109">
         <f>DATA!F2</f>
-        <v>5902.6829268292686</v>
+        <v>5623.0116279069771</v>
       </c>
       <c r="H13" s="109">
         <f>DATA!G2</f>
-        <v>3903.3870967741937</v>
+        <v>3899.8306451612902</v>
       </c>
       <c r="I13" s="106" cm="1">
         <f t="array" ref="I13:I31">DATA!B2:B20</f>
-        <v>484020</v>
+        <v>483579</v>
       </c>
       <c r="J13" s="110">
         <f t="shared" ref="J13:J31" si="3">IFERROR(I13/C13,0)</f>
-        <v>1.0148806451612904</v>
+        <v>1.0139559677419356</v>
       </c>
       <c r="K13" s="111">
         <f>IFERROR(I13/$I$32,)</f>
-        <v>0.21535742821460216</v>
+        <v>0.20749913232546707</v>
       </c>
       <c r="L13" s="112">
         <f t="shared" ref="L13:L31" si="4">IFERROR(IF(J13&lt;0.85,"",IF(AND(J13&gt;0.85,J13&lt;1),$M$2*AB13*AJ13,$M$2*AB13*AJ13)),"")</f>
-        <v>9983.7550146007416</v>
+        <v>9619.4522754763275</v>
       </c>
       <c r="M13" s="113">
         <f t="shared" ref="M13:M31" si="5">IFERROR((($E$9+$F$9)*AC13),"")</f>
@@ -3025,30 +3025,30 @@
       </c>
       <c r="P13" s="110">
         <f t="shared" ref="P13:P31" si="7">IFERROR(I13/C13,0)</f>
-        <v>1.0148806451612904</v>
+        <v>1.0139559677419356</v>
       </c>
       <c r="Q13" s="109">
         <f t="shared" ref="Q13:Q31" si="8">IF(V13="",0,IF(W13=V13,I13,(I13/V13)*(W13-V13)+I13))</f>
-        <v>577100.76923076925</v>
+        <v>535391.03571428568</v>
       </c>
       <c r="R13" s="115">
         <f>IFERROR(Q13/$Q$32,)</f>
-        <v>0.21259691097954184</v>
+        <v>0.20502408068210914</v>
       </c>
       <c r="S13" s="106">
         <f>IFERROR(IF(T13&lt;0.85,"",IF(AND(T13&gt;0.85,T13&lt;1),$M$2*AD13*AK13,$M$2*AD13*AK13)),"")</f>
-        <v>11709.837856753164</v>
+        <v>10539.877939705868</v>
       </c>
       <c r="T13" s="110">
         <f t="shared" ref="T13:T31" si="9">IFERROR(Q13/C13,0)</f>
-        <v>1.2100500000000001</v>
+        <v>1.1225941071428571</v>
       </c>
       <c r="U13" s="116">
         <f t="shared" ref="U13:U31" si="10">IFERROR(D13/Z13,0)</f>
-        <v>7.5481661195946917E-2</v>
+        <v>7.6020044770044759E-2</v>
       </c>
       <c r="V13" s="62">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="W13" s="63">
         <v>31</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z13" s="118">
         <f t="shared" ref="Z13:Z31" si="12">(V13/$V$32)*$I$10</f>
-        <v>1086.3565891472867</v>
+        <v>1131.2805755395684</v>
       </c>
       <c r="AA13" s="119">
         <f t="shared" ref="AA13:AA31" si="13">IFERROR(((Y13/$Y$32)*$A$9),"")</f>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AB13" s="120">
         <f t="shared" ref="AB13:AB31" si="14">I13/$I$32</f>
-        <v>0.21535742821460216</v>
+        <v>0.20749913232546707</v>
       </c>
       <c r="AC13" s="121">
         <f>AA13/$C$32</f>
@@ -3075,15 +3075,15 @@
       </c>
       <c r="AD13" s="120">
         <f>Q13/$Q$32</f>
-        <v>0.21259691097954184</v>
+        <v>0.20502408068210914</v>
       </c>
       <c r="AE13" s="120">
         <f t="shared" ref="AE13:AE31" si="15">I13/C13</f>
-        <v>1.0148806451612904</v>
+        <v>1.0139559677419356</v>
       </c>
       <c r="AF13" s="120">
         <f t="shared" ref="AF13:AF31" si="16">Q13/C13</f>
-        <v>1.2100500000000001</v>
+        <v>1.1225941071428571</v>
       </c>
       <c r="AG13" s="120">
         <f>IFERROR(VLOOKUP(A13,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AK13" s="123">
         <f t="shared" ref="AK13:AK31" si="19">IFERROR(LOOKUP(AF13,AL:AL,AM:AM),"")</f>
-        <v>1.2</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="AL13" s="93">
         <v>0.87</v>
@@ -3135,26 +3135,26 @@
       </c>
       <c r="G14" s="128">
         <f>DATA!F3</f>
-        <v>6424.4942528735628</v>
+        <v>6412.5517241379312</v>
       </c>
       <c r="H14" s="128">
         <f>DATA!G3</f>
-        <v>4109.786764705882</v>
+        <v>4102.1470588235297</v>
       </c>
       <c r="I14" s="125">
-        <v>558931</v>
+        <v>557892</v>
       </c>
       <c r="J14" s="129">
         <f t="shared" si="3"/>
-        <v>0.87896407258064524</v>
+        <v>0.8773301612903226</v>
       </c>
       <c r="K14" s="111">
         <f t="shared" ref="K14:K31" si="21">IFERROR(I14/$I$32,)</f>
-        <v>0.24868795237679392</v>
+        <v>0.23938613118294938</v>
       </c>
       <c r="L14" s="112">
         <f t="shared" si="4"/>
-        <v>8446.9349904301835</v>
+        <v>8130.989331760059</v>
       </c>
       <c r="M14" s="113">
         <f t="shared" si="5"/>
@@ -3162,38 +3162,38 @@
       </c>
       <c r="N14" s="130">
         <f t="shared" ref="N14:N31" si="22">IFERROR(IF(C14-I14&lt;0,"",C14-I14),"")</f>
-        <v>76966.435897435877</v>
+        <v>78005.435897435877</v>
       </c>
       <c r="O14" s="130">
         <f t="shared" si="6"/>
-        <v>15393.287179487175</v>
+        <v>26001.811965811958</v>
       </c>
       <c r="P14" s="129">
         <f t="shared" si="7"/>
-        <v>0.87896407258064524</v>
+        <v>0.8773301612903226</v>
       </c>
       <c r="Q14" s="109">
         <f t="shared" si="8"/>
-        <v>666417.73076923075</v>
+        <v>617666.14285714284</v>
       </c>
       <c r="R14" s="115">
         <f t="shared" ref="R14:R31" si="23">IFERROR(Q14/$Q$32,)</f>
-        <v>0.24550019431161171</v>
+        <v>0.23653073111095238</v>
       </c>
       <c r="S14" s="106">
         <f t="shared" ref="S14:S31" si="24">IFERROR(IF(T14&lt;0.85,"",IF(AND(T14&gt;0.85,T14&lt;1),$M$2*AD14*AK14,$M$2*AD14*AK14)),"")</f>
-        <v>11719.197275659097</v>
+        <v>10205.354924513151</v>
       </c>
       <c r="T14" s="129">
         <f t="shared" si="9"/>
-        <v>1.047995625</v>
+        <v>0.97132982142857138</v>
       </c>
       <c r="U14" s="131">
         <f t="shared" si="10"/>
-        <v>8.0084201512772943E-2</v>
+        <v>7.6903998778998769E-2</v>
       </c>
       <c r="V14" s="62">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="W14" s="64">
         <v>31</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="Z14" s="133">
         <f t="shared" si="12"/>
-        <v>1086.3565891472867</v>
+        <v>1131.2805755395684</v>
       </c>
       <c r="AA14" s="17">
         <f t="shared" si="13"/>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="AB14" s="134">
         <f t="shared" si="14"/>
-        <v>0.24868795237679392</v>
+        <v>0.23938613118294938</v>
       </c>
       <c r="AC14" s="135">
         <f t="shared" ref="AC14:AC31" si="25">AA14/$C$32</f>
@@ -3220,15 +3220,15 @@
       </c>
       <c r="AD14" s="134">
         <f t="shared" ref="AD14:AD18" si="26">Q14/$Q$32</f>
-        <v>0.24550019431161171</v>
+        <v>0.23653073111095238</v>
       </c>
       <c r="AE14" s="134">
         <f t="shared" si="15"/>
-        <v>0.87896407258064524</v>
+        <v>0.8773301612903226</v>
       </c>
       <c r="AF14" s="134">
         <f t="shared" si="16"/>
-        <v>1.047995625</v>
+        <v>0.97132982142857138</v>
       </c>
       <c r="AG14" s="134">
         <f>IFERROR(VLOOKUP(A14,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="AK14" s="137">
         <f t="shared" si="19"/>
-        <v>1.04</v>
+        <v>0.94</v>
       </c>
       <c r="AL14" s="93">
         <v>0.88</v>
@@ -3269,33 +3269,33 @@
         <v>615384.61538461538</v>
       </c>
       <c r="D15" s="126">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E15" s="126">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="F15" s="127">
         <f>DATA!E4</f>
-        <v>1.3333333333333333</v>
+        <v>1.3658536585365855</v>
       </c>
       <c r="G15" s="128">
         <f>DATA!F4</f>
-        <v>5500.2728000000006</v>
+        <v>5484.3536585365855</v>
       </c>
       <c r="H15" s="128">
         <f>DATA!G4</f>
-        <v>4125.2046</v>
+        <v>4015.3303571428573</v>
       </c>
       <c r="I15" s="125">
-        <v>412520.46</v>
+        <v>449717</v>
       </c>
       <c r="J15" s="129">
         <f t="shared" si="3"/>
-        <v>0.67034574750000009</v>
+        <v>0.73079012499999996</v>
       </c>
       <c r="K15" s="111">
         <f t="shared" si="21"/>
-        <v>0.1835447819336074</v>
+        <v>0.1929692713951848</v>
       </c>
       <c r="L15" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3307,23 +3307,23 @@
       </c>
       <c r="N15" s="130">
         <f t="shared" si="22"/>
-        <v>202864.15538461535</v>
+        <v>165667.61538461538</v>
       </c>
       <c r="O15" s="130">
         <f t="shared" si="6"/>
-        <v>40572.831076923074</v>
+        <v>55222.538461538461</v>
       </c>
       <c r="P15" s="129">
         <f t="shared" si="7"/>
-        <v>0.67034574750000009</v>
+        <v>0.73079012499999996</v>
       </c>
       <c r="Q15" s="109">
         <f t="shared" si="8"/>
-        <v>495024.55200000003</v>
+        <v>499685.55555555556</v>
       </c>
       <c r="R15" s="115">
         <f t="shared" si="23"/>
-        <v>0.18236102986746891</v>
+        <v>0.19135092824486225</v>
       </c>
       <c r="S15" s="106" t="str">
         <f t="shared" si="24"/>
@@ -3331,14 +3331,14 @@
       </c>
       <c r="T15" s="129">
         <f t="shared" si="9"/>
-        <v>0.80441489700000002</v>
+        <v>0.81198902777777782</v>
       </c>
       <c r="U15" s="131">
         <f t="shared" si="10"/>
-        <v>7.179962894248608E-2</v>
+        <v>7.5168829798459416E-2</v>
       </c>
       <c r="V15" s="62">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="W15" s="64">
         <v>30</v>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="Z15" s="133">
         <f t="shared" si="12"/>
-        <v>1044.5736434108528</v>
+        <v>1090.8776978417268</v>
       </c>
       <c r="AA15" s="17">
         <f t="shared" si="13"/>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="AB15" s="134">
         <f t="shared" si="14"/>
-        <v>0.1835447819336074</v>
+        <v>0.1929692713951848</v>
       </c>
       <c r="AC15" s="135">
         <f t="shared" si="25"/>
@@ -3365,15 +3365,15 @@
       </c>
       <c r="AD15" s="134">
         <f t="shared" si="26"/>
-        <v>0.18236102986746891</v>
+        <v>0.19135092824486225</v>
       </c>
       <c r="AE15" s="134">
         <f t="shared" si="15"/>
-        <v>0.67034574750000009</v>
+        <v>0.73079012499999996</v>
       </c>
       <c r="AF15" s="134">
         <f t="shared" si="16"/>
-        <v>0.80441489700000002</v>
+        <v>0.81198902777777782</v>
       </c>
       <c r="AG15" s="134">
         <f>IFERROR(VLOOKUP(A15,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3414,37 +3414,37 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D16" s="126">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E16" s="126">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F16" s="127">
         <f>DATA!E5</f>
-        <v>1.6506024096385543</v>
+        <v>1.6179775280898876</v>
       </c>
       <c r="G16" s="128">
         <f>DATA!F5</f>
-        <v>6420.3012048192768</v>
+        <v>6268.4494382022476</v>
       </c>
       <c r="H16" s="128">
         <f>DATA!G5</f>
-        <v>3889.6715328467153</v>
+        <v>3874.25</v>
       </c>
       <c r="I16" s="125">
-        <v>532885</v>
+        <v>557892</v>
       </c>
       <c r="J16" s="129">
         <f t="shared" si="3"/>
-        <v>0.8380046370967742</v>
+        <v>0.8773301612903226</v>
       </c>
       <c r="K16" s="111">
         <f t="shared" si="21"/>
-        <v>0.23709917593103233</v>
-      </c>
-      <c r="L16" s="112" t="str">
+        <v>0.23938613118294938</v>
+      </c>
+      <c r="L16" s="112">
         <f t="shared" si="4"/>
-        <v/>
+        <v>8130.989331760059</v>
       </c>
       <c r="M16" s="113">
         <f t="shared" si="5"/>
@@ -3452,38 +3452,38 @@
       </c>
       <c r="N16" s="130">
         <f t="shared" ref="N16:N25" si="28">IFERROR(IF(C16-I16&lt;0,"",C16-I16),"")</f>
-        <v>103012.43589743588</v>
+        <v>78005.435897435877</v>
       </c>
       <c r="O16" s="130">
         <f t="shared" si="6"/>
-        <v>20602.487179487176</v>
+        <v>26001.811965811958</v>
       </c>
       <c r="P16" s="129">
         <f t="shared" si="7"/>
-        <v>0.8380046370967742</v>
+        <v>0.8773301612903226</v>
       </c>
       <c r="Q16" s="109">
         <f t="shared" si="8"/>
-        <v>635362.88461538462</v>
+        <v>617666.14285714284</v>
       </c>
       <c r="R16" s="115">
         <f t="shared" si="23"/>
-        <v>0.23405996633885615</v>
+        <v>0.23653073111095238</v>
       </c>
       <c r="S16" s="106">
         <f t="shared" si="24"/>
-        <v>10528.485405854428</v>
+        <v>10205.354924513151</v>
       </c>
       <c r="T16" s="129">
         <f t="shared" si="9"/>
-        <v>0.99915937500000007</v>
+        <v>0.97132982142857138</v>
       </c>
       <c r="U16" s="131">
         <f t="shared" si="10"/>
-        <v>7.6402169259312119E-2</v>
+        <v>7.867190679690679E-2</v>
       </c>
       <c r="V16" s="62">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="W16" s="64">
         <v>31</v>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="Z16" s="133">
         <f t="shared" si="12"/>
-        <v>1086.3565891472867</v>
+        <v>1131.2805755395684</v>
       </c>
       <c r="AA16" s="17">
         <f t="shared" si="13"/>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="AB16" s="134">
         <f t="shared" si="14"/>
-        <v>0.23709917593103233</v>
+        <v>0.23938613118294938</v>
       </c>
       <c r="AC16" s="135">
         <f t="shared" si="25"/>
@@ -3510,15 +3510,15 @@
       </c>
       <c r="AD16" s="134">
         <f t="shared" si="26"/>
-        <v>0.23405996633885615</v>
+        <v>0.23653073111095238</v>
       </c>
       <c r="AE16" s="134">
         <f t="shared" si="15"/>
-        <v>0.8380046370967742</v>
+        <v>0.8773301612903226</v>
       </c>
       <c r="AF16" s="134">
         <f t="shared" si="16"/>
-        <v>0.99915937500000007</v>
+        <v>0.97132982142857138</v>
       </c>
       <c r="AG16" s="134">
         <f>IFERROR(VLOOKUP(A16,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3532,13 +3532,13 @@
         <f t="shared" si="27"/>
         <v>0.17391304347826086</v>
       </c>
-      <c r="AJ16" s="135" t="str">
+      <c r="AJ16" s="135">
         <f t="shared" si="18"/>
-        <v/>
+        <v>0.74</v>
       </c>
       <c r="AK16" s="137">
         <f t="shared" si="19"/>
-        <v>0.98</v>
+        <v>0.94</v>
       </c>
       <c r="AL16" s="93">
         <v>0.9</v>
@@ -3559,33 +3559,33 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D17" s="126">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E17" s="126">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F17" s="127">
         <f>DATA!E6</f>
-        <v>1.2413793103448276</v>
+        <v>1.2380952380952381</v>
       </c>
       <c r="G17" s="128">
         <f>DATA!F6</f>
-        <v>4925.6034482758623</v>
+        <v>4888.1428571428569</v>
       </c>
       <c r="H17" s="128">
         <f>DATA!G6</f>
-        <v>3967.8472222222222</v>
+        <v>3948.1153846153848</v>
       </c>
       <c r="I17" s="125">
-        <v>285685</v>
+        <v>307953</v>
       </c>
       <c r="J17" s="129">
         <f t="shared" si="3"/>
-        <v>0.44926270161290321</v>
+        <v>0.48428092741935486</v>
       </c>
       <c r="K17" s="111">
         <f t="shared" si="21"/>
-        <v>0.12711124928616299</v>
+        <v>0.13213969237089401</v>
       </c>
       <c r="L17" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3597,23 +3597,23 @@
       </c>
       <c r="N17" s="130">
         <f t="shared" si="28"/>
-        <v>350212.43589743588</v>
+        <v>327944.43589743588</v>
       </c>
       <c r="O17" s="130">
         <f t="shared" si="6"/>
-        <v>70042.487179487172</v>
+        <v>109314.81196581195</v>
       </c>
       <c r="P17" s="129">
         <f t="shared" si="7"/>
-        <v>0.44926270161290321</v>
+        <v>0.48428092741935486</v>
       </c>
       <c r="Q17" s="109">
         <f t="shared" si="8"/>
-        <v>340624.42307692306</v>
+        <v>340947.96428571432</v>
       </c>
       <c r="R17" s="115">
         <f t="shared" si="23"/>
-        <v>0.12548189850252139</v>
+        <v>0.13056352885112374</v>
       </c>
       <c r="S17" s="106" t="str">
         <f t="shared" si="24"/>
@@ -3621,14 +3621,14 @@
       </c>
       <c r="T17" s="129">
         <f t="shared" si="9"/>
-        <v>0.53565937500000005</v>
+        <v>0.53616816964285718</v>
       </c>
       <c r="U17" s="131">
         <f t="shared" si="10"/>
-        <v>5.3389467675181962E-2</v>
+        <v>5.5689102564102561E-2</v>
       </c>
       <c r="V17" s="62">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="W17" s="64">
         <v>31</v>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="Z17" s="133">
         <f t="shared" si="12"/>
-        <v>1086.3565891472867</v>
+        <v>1131.2805755395684</v>
       </c>
       <c r="AA17" s="17">
         <f t="shared" si="13"/>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="AB17" s="134">
         <f t="shared" si="14"/>
-        <v>0.12711124928616299</v>
+        <v>0.13213969237089401</v>
       </c>
       <c r="AC17" s="135">
         <f t="shared" si="25"/>
@@ -3655,15 +3655,15 @@
       </c>
       <c r="AD17" s="134">
         <f t="shared" si="26"/>
-        <v>0.12548189850252139</v>
+        <v>0.13056352885112374</v>
       </c>
       <c r="AE17" s="134">
         <f t="shared" si="15"/>
-        <v>0.44926270161290321</v>
+        <v>0.48428092741935486</v>
       </c>
       <c r="AF17" s="134">
         <f t="shared" si="16"/>
-        <v>0.53565937500000005</v>
+        <v>0.53616816964285718</v>
       </c>
       <c r="AG17" s="134">
         <f>IFERROR(VLOOKUP(A17,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="K18" s="111">
         <f t="shared" si="21"/>
-        <v>-1.1800587742198852E-2</v>
+        <v>-1.1380358457444706E-2</v>
       </c>
       <c r="L18" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="AB18" s="138">
         <f t="shared" si="14"/>
-        <v>-1.1800587742198852E-2</v>
+        <v>-1.1380358457444706E-2</v>
       </c>
       <c r="AC18" s="135">
         <f t="shared" si="25"/>
@@ -5699,39 +5699,39 @@
       </c>
       <c r="D32" s="153">
         <f>SUM(D13:D31)</f>
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="E32" s="153">
         <f>SUM(E13:E31)</f>
-        <v>562</v>
+        <v>587</v>
       </c>
       <c r="F32" s="154">
         <f>IFERROR(SUM(F13:F31)/G10,)</f>
-        <v>1.6601457132145065</v>
+        <v>1.6454010561285173</v>
       </c>
       <c r="G32" s="155">
         <f>IFERROR(SUM(G13:G31)/G10,)</f>
-        <v>6592.4437837024507</v>
+        <v>6493.0747183281755</v>
       </c>
       <c r="H32" s="155">
         <f>IFERROR(SUM(H13:H31)/G10,)</f>
-        <v>4756.9523004526591</v>
+        <v>4725.707546291469</v>
       </c>
       <c r="I32" s="155">
         <f>SUM(I13:I31)</f>
-        <v>2247519.41</v>
+        <v>2330510.9500000002</v>
       </c>
       <c r="J32" s="156">
         <f>IFERROR(I32/C32,)</f>
-        <v>0.74917313666666674</v>
+        <v>0.7768369833333334</v>
       </c>
       <c r="K32" s="156">
         <f>SUM(K13:K31)</f>
-        <v>1</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="L32" s="155">
         <f>SUM(L13:L31)</f>
-        <v>18430.690005030927</v>
+        <v>25881.430938996444</v>
       </c>
       <c r="M32" s="155">
         <f>SUM(M13:M31)</f>
@@ -5739,33 +5739,33 @@
       </c>
       <c r="N32" s="155">
         <f>SUM(N13:N31)</f>
-        <v>759577.51307692309</v>
+        <v>676144.97307692305</v>
       </c>
       <c r="O32" s="155">
         <f>SUM(O13:O31)</f>
-        <v>146611.09261538461</v>
+        <v>216540.97435897432</v>
       </c>
       <c r="P32" s="157"/>
       <c r="Q32" s="152">
         <f>SUM(Q13:Q31)</f>
-        <v>2714530.3596923077</v>
+        <v>2611356.8412698414</v>
       </c>
       <c r="R32" s="156">
         <f>SUM(R13:R31)</f>
-        <v>1</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="S32" s="155">
         <f>SUM(S13:S31)</f>
-        <v>33957.52053826669</v>
+        <v>30950.587788732169</v>
       </c>
       <c r="T32" s="158">
         <f>IFERROR(Q32/C32,)</f>
-        <v>0.9048434532307692</v>
+        <v>0.87045228042328049</v>
       </c>
       <c r="U32" s="165"/>
       <c r="V32" s="166">
         <f>SUM(V13:V31)</f>
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="W32" s="167">
         <f>SUM(W13:W31)</f>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="Z32" s="164">
         <f>SUM(Z13:Z31)</f>
-        <v>5390</v>
+        <v>5616.0000000000009</v>
       </c>
       <c r="AA32" s="162">
         <f>SUM(AA13:AA31)</f>
@@ -6948,25 +6948,25 @@
         <v>65</v>
       </c>
       <c r="B2" s="19">
-        <v>484020</v>
+        <v>483579</v>
       </c>
       <c r="C2" s="18">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D2" s="18">
         <v>124</v>
       </c>
       <c r="E2" s="16">
         <f>IFERROR((D2/C2),"")</f>
-        <v>1.5121951219512195</v>
+        <v>1.441860465116279</v>
       </c>
       <c r="F2" s="17">
         <f>IFERROR((B2/C2),"")</f>
-        <v>5902.6829268292686</v>
+        <v>5623.0116279069771</v>
       </c>
       <c r="G2" s="17">
         <f>IFERROR((B2/D2),"")</f>
-        <v>3903.3870967741937</v>
+        <v>3899.8306451612902</v>
       </c>
       <c r="Q2" s="6" t="s">
         <v>38</v>
@@ -6980,7 +6980,7 @@
         <v>67</v>
       </c>
       <c r="B3" s="19">
-        <v>558931</v>
+        <v>557892</v>
       </c>
       <c r="C3" s="18">
         <v>87</v>
@@ -6994,11 +6994,11 @@
       </c>
       <c r="F3" s="17">
         <f t="shared" ref="F3:F20" si="1">IFERROR((B3/C3),"")</f>
-        <v>6424.4942528735628</v>
+        <v>6412.5517241379312</v>
       </c>
       <c r="G3" s="17">
         <f t="shared" ref="G3:G20" si="2">IFERROR((B3/D3),"")</f>
-        <v>4109.786764705882</v>
+        <v>4102.1470588235297</v>
       </c>
       <c r="Q3" s="6" t="s">
         <v>40</v>
@@ -7012,25 +7012,25 @@
         <v>64</v>
       </c>
       <c r="B4" s="174">
-        <v>412520.46</v>
+        <v>449717</v>
       </c>
       <c r="C4" s="18">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D4" s="18">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="E4" s="16">
         <f t="shared" si="0"/>
-        <v>1.3333333333333333</v>
+        <v>1.3658536585365855</v>
       </c>
       <c r="F4" s="17">
         <f t="shared" si="1"/>
-        <v>5500.2728000000006</v>
+        <v>5484.3536585365855</v>
       </c>
       <c r="G4" s="17">
         <f t="shared" si="2"/>
-        <v>4125.2046</v>
+        <v>4015.3303571428573</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -7038,25 +7038,25 @@
         <v>66</v>
       </c>
       <c r="B5" s="175">
-        <v>532885</v>
+        <v>557892</v>
       </c>
       <c r="C5" s="18">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D5" s="18">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E5" s="16">
         <f t="shared" si="0"/>
-        <v>1.6506024096385543</v>
+        <v>1.6179775280898876</v>
       </c>
       <c r="F5" s="17">
         <f t="shared" si="1"/>
-        <v>6420.3012048192768</v>
+        <v>6268.4494382022476</v>
       </c>
       <c r="G5" s="17">
         <f t="shared" si="2"/>
-        <v>3889.6715328467153</v>
+        <v>3874.25</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -7064,25 +7064,25 @@
         <v>68</v>
       </c>
       <c r="B6" s="19">
-        <v>285685</v>
+        <v>307953</v>
       </c>
       <c r="C6" s="18">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D6" s="18">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E6" s="16">
         <f t="shared" si="0"/>
-        <v>1.2413793103448276</v>
+        <v>1.2380952380952381</v>
       </c>
       <c r="F6" s="17">
         <f t="shared" si="1"/>
-        <v>4925.6034482758623</v>
+        <v>4888.1428571428569</v>
       </c>
       <c r="G6" s="17">
         <f t="shared" si="2"/>
-        <v>3967.8472222222222</v>
+        <v>3948.1153846153848</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">

--- a/EKİM SD KARNE.xlsx
+++ b/EKİM SD KARNE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\UYGULAMA İÇİN GEREKLİ DOSYALAR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD84C00E-0B6B-4159-A5D9-D03778DBF2CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86BEB446-6B3F-4635-B262-95FC015112A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2690,11 +2690,11 @@
       </c>
       <c r="B9" s="75">
         <f>I32</f>
-        <v>2330510.9500000002</v>
+        <v>2514813.9500000002</v>
       </c>
       <c r="C9" s="76">
         <f>IFERROR(B9/A9,)</f>
-        <v>0.7768369833333334</v>
+        <v>0.83827131666666677</v>
       </c>
       <c r="D9" s="168">
         <f>IFERROR(IF(B9&lt;=A9,A4,IF(AND(B9&gt;A9,B9&lt;B1),A4,IF(AND(B9&gt;=B1,B9&lt;C1),B4,IF(AND(B9&gt;=C1,B9&lt;D1),C4,IF(AND(B9&gt;=D1,B9&lt;E1),D4,IF(AND(B9&gt;=E1,B9&lt;F1),E4,IF(AND(B9&gt;=F1,B9&lt;G1),F4,IF(AND(B9&gt;=G1,B9&lt;H1),G4,IF(AND(B9&gt;=H1,B9&lt;I1),H4,IF(AND(B9&gt;=I1,B9&lt;J1),I4,IF(AND(B9&gt;=J1,B9&lt;K1),J4,IF(B9&gt;=K4,K4,K4)))))))))))),)</f>
@@ -2761,27 +2761,27 @@
       </c>
       <c r="H10" s="83">
         <f ca="1">B11-M10</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I10" s="84">
         <f>C11</f>
-        <v>5616</v>
+        <v>6076</v>
       </c>
       <c r="J10" s="85">
         <f ca="1">I10/H10</f>
-        <v>200.57142857142858</v>
+        <v>202.53333333333333</v>
       </c>
       <c r="K10" s="85">
         <f>IFERROR(I10/G10,)</f>
-        <v>1123.2</v>
+        <v>1215.2</v>
       </c>
       <c r="L10" s="86">
         <f ca="1">IFERROR(J10/G10,)</f>
-        <v>40.114285714285714</v>
+        <v>40.506666666666668</v>
       </c>
       <c r="M10" s="87">
         <f ca="1">(M11-A11)+B11</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N10" s="2">
         <f>LOOKUP(A9,'PRİM HAVUZU (SV SİSTEM)'!$A:$A,'PRİM HAVUZU (SV SİSTEM)'!$C:$C)*A9</f>
@@ -2804,14 +2804,14 @@
     <row r="11" spans="1:58" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="169">
         <f ca="1">TODAY()</f>
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="B11" s="170">
         <f ca="1">(N11-M11)+1</f>
         <v>31</v>
       </c>
       <c r="C11" s="171">
-        <v>5616</v>
+        <v>6076</v>
       </c>
       <c r="F11" s="66"/>
       <c r="K11" s="89"/>
@@ -2977,39 +2977,39 @@
       </c>
       <c r="D13" s="107" cm="1">
         <f t="array" ref="D13:D31">DATA!C2:C20</f>
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E13" s="107" cm="1">
         <f t="array" ref="E13:E31">DATA!D2:D20</f>
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="F13" s="108">
         <f>DATA!E2</f>
-        <v>1.441860465116279</v>
+        <v>1.4886363636363635</v>
       </c>
       <c r="G13" s="109">
         <f>DATA!F2</f>
-        <v>5623.0116279069771</v>
+        <v>5682.125</v>
       </c>
       <c r="H13" s="109">
         <f>DATA!G2</f>
-        <v>3899.8306451612902</v>
+        <v>3817</v>
       </c>
       <c r="I13" s="106" cm="1">
         <f t="array" ref="I13:I31">DATA!B2:B20</f>
-        <v>483579</v>
+        <v>500027</v>
       </c>
       <c r="J13" s="110">
         <f t="shared" ref="J13:J31" si="3">IFERROR(I13/C13,0)</f>
-        <v>1.0139559677419356</v>
+        <v>1.0484437096774195</v>
       </c>
       <c r="K13" s="111">
         <f>IFERROR(I13/$I$32,)</f>
-        <v>0.20749913232546707</v>
+        <v>0.19883260151312585</v>
       </c>
       <c r="L13" s="112">
         <f t="shared" ref="L13:L31" si="4">IFERROR(IF(J13&lt;0.85,"",IF(AND(J13&gt;0.85,J13&lt;1),$M$2*AB13*AJ13,$M$2*AB13*AJ13)),"")</f>
-        <v>9619.4522754763275</v>
+        <v>9491.4730658305762</v>
       </c>
       <c r="M13" s="113">
         <f t="shared" ref="M13:M31" si="5">IFERROR((($E$9+$F$9)*AC13),"")</f>
@@ -3025,30 +3025,30 @@
       </c>
       <c r="P13" s="110">
         <f t="shared" ref="P13:P31" si="7">IFERROR(I13/C13,0)</f>
-        <v>1.0139559677419356</v>
+        <v>1.0484437096774195</v>
       </c>
       <c r="Q13" s="109">
         <f t="shared" ref="Q13:Q31" si="8">IF(V13="",0,IF(W13=V13,I13,(I13/V13)*(W13-V13)+I13))</f>
-        <v>535391.03571428568</v>
+        <v>516694.56666666665</v>
       </c>
       <c r="R13" s="115">
         <f>IFERROR(Q13/$Q$32,)</f>
-        <v>0.20502408068210914</v>
+        <v>0.19671220760563643</v>
       </c>
       <c r="S13" s="106">
         <f>IFERROR(IF(T13&lt;0.85,"",IF(AND(T13&gt;0.85,T13&lt;1),$M$2*AD13*AK13,$M$2*AD13*AK13)),"")</f>
-        <v>10539.877939705868</v>
+        <v>9751.4175554266094</v>
       </c>
       <c r="T13" s="110">
         <f t="shared" ref="T13:T31" si="9">IFERROR(Q13/C13,0)</f>
-        <v>1.1225941071428571</v>
+        <v>1.0833918333333334</v>
       </c>
       <c r="U13" s="116">
         <f t="shared" ref="U13:U31" si="10">IFERROR(D13/Z13,0)</f>
-        <v>7.6020044770044759E-2</v>
+        <v>7.1933289444810186E-2</v>
       </c>
       <c r="V13" s="62">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="W13" s="63">
         <v>31</v>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="Z13" s="118">
         <f t="shared" ref="Z13:Z31" si="12">(V13/$V$32)*$I$10</f>
-        <v>1131.2805755395684</v>
+        <v>1223.3557046979865</v>
       </c>
       <c r="AA13" s="119">
         <f t="shared" ref="AA13:AA31" si="13">IFERROR(((Y13/$Y$32)*$A$9),"")</f>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AB13" s="120">
         <f t="shared" ref="AB13:AB31" si="14">I13/$I$32</f>
-        <v>0.20749913232546707</v>
+        <v>0.19883260151312585</v>
       </c>
       <c r="AC13" s="121">
         <f>AA13/$C$32</f>
@@ -3075,15 +3075,15 @@
       </c>
       <c r="AD13" s="120">
         <f>Q13/$Q$32</f>
-        <v>0.20502408068210914</v>
+        <v>0.19671220760563643</v>
       </c>
       <c r="AE13" s="120">
         <f t="shared" ref="AE13:AE31" si="15">I13/C13</f>
-        <v>1.0139559677419356</v>
+        <v>1.0484437096774195</v>
       </c>
       <c r="AF13" s="120">
         <f t="shared" ref="AF13:AF31" si="16">Q13/C13</f>
-        <v>1.1225941071428571</v>
+        <v>1.0833918333333334</v>
       </c>
       <c r="AG13" s="120">
         <f>IFERROR(VLOOKUP(A13,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3099,11 +3099,11 @@
       </c>
       <c r="AJ13" s="121">
         <f t="shared" ref="AJ13:AJ31" si="18">IFERROR(LOOKUP(AE13,AL:AL,AM:AM),"")</f>
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AK13" s="123">
         <f t="shared" ref="AK13:AK31" si="19">IFERROR(LOOKUP(AF13,AL:AL,AM:AM),"")</f>
-        <v>1.1200000000000001</v>
+        <v>1.08</v>
       </c>
       <c r="AL13" s="93">
         <v>0.87</v>
@@ -3124,37 +3124,37 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D14" s="126">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E14" s="126">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="F14" s="127">
         <f>DATA!E3</f>
-        <v>1.5632183908045978</v>
+        <v>1.576086956521739</v>
       </c>
       <c r="G14" s="128">
         <f>DATA!F3</f>
-        <v>6412.5517241379312</v>
+        <v>6460.673913043478</v>
       </c>
       <c r="H14" s="128">
         <f>DATA!G3</f>
-        <v>4102.1470588235297</v>
+        <v>4099.186206896552</v>
       </c>
       <c r="I14" s="125">
-        <v>557892</v>
+        <v>594382</v>
       </c>
       <c r="J14" s="129">
         <f t="shared" si="3"/>
-        <v>0.8773301612903226</v>
+        <v>0.93471362903225808</v>
       </c>
       <c r="K14" s="111">
         <f t="shared" ref="K14:K31" si="21">IFERROR(I14/$I$32,)</f>
-        <v>0.23938613118294938</v>
+        <v>0.23635227568226269</v>
       </c>
       <c r="L14" s="112">
         <f t="shared" si="4"/>
-        <v>8130.989331760059</v>
+        <v>9329.7697302816359</v>
       </c>
       <c r="M14" s="113">
         <f t="shared" si="5"/>
@@ -3162,38 +3162,38 @@
       </c>
       <c r="N14" s="130">
         <f t="shared" ref="N14:N31" si="22">IFERROR(IF(C14-I14&lt;0,"",C14-I14),"")</f>
-        <v>78005.435897435877</v>
+        <v>41515.435897435877</v>
       </c>
       <c r="O14" s="130">
         <f t="shared" si="6"/>
-        <v>26001.811965811958</v>
+        <v>41515.435897435877</v>
       </c>
       <c r="P14" s="129">
         <f t="shared" si="7"/>
-        <v>0.8773301612903226</v>
+        <v>0.93471362903225808</v>
       </c>
       <c r="Q14" s="109">
         <f t="shared" si="8"/>
-        <v>617666.14285714284</v>
+        <v>614194.73333333328</v>
       </c>
       <c r="R14" s="115">
         <f t="shared" ref="R14:R31" si="23">IFERROR(Q14/$Q$32,)</f>
-        <v>0.23653073111095238</v>
+        <v>0.23383176384685903</v>
       </c>
       <c r="S14" s="106">
         <f t="shared" ref="S14:S31" si="24">IFERROR(IF(T14&lt;0.85,"",IF(AND(T14&gt;0.85,T14&lt;1),$M$2*AD14*AK14,$M$2*AD14*AK14)),"")</f>
-        <v>10205.354924513151</v>
+        <v>9874.2477237251642</v>
       </c>
       <c r="T14" s="129">
         <f t="shared" si="9"/>
-        <v>0.97132982142857138</v>
+        <v>0.96587075</v>
       </c>
       <c r="U14" s="131">
         <f t="shared" si="10"/>
-        <v>7.6903998778998769E-2</v>
+        <v>7.5202984419574279E-2</v>
       </c>
       <c r="V14" s="62">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="W14" s="64">
         <v>31</v>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="Z14" s="133">
         <f t="shared" si="12"/>
-        <v>1131.2805755395684</v>
+        <v>1223.3557046979865</v>
       </c>
       <c r="AA14" s="17">
         <f t="shared" si="13"/>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="AB14" s="134">
         <f t="shared" si="14"/>
-        <v>0.23938613118294938</v>
+        <v>0.23635227568226269</v>
       </c>
       <c r="AC14" s="135">
         <f t="shared" ref="AC14:AC31" si="25">AA14/$C$32</f>
@@ -3220,15 +3220,15 @@
       </c>
       <c r="AD14" s="134">
         <f t="shared" ref="AD14:AD18" si="26">Q14/$Q$32</f>
-        <v>0.23653073111095238</v>
+        <v>0.23383176384685903</v>
       </c>
       <c r="AE14" s="134">
         <f t="shared" si="15"/>
-        <v>0.8773301612903226</v>
+        <v>0.93471362903225808</v>
       </c>
       <c r="AF14" s="134">
         <f t="shared" si="16"/>
-        <v>0.97132982142857138</v>
+        <v>0.96587075</v>
       </c>
       <c r="AG14" s="134">
         <f>IFERROR(VLOOKUP(A14,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3244,11 +3244,11 @@
       </c>
       <c r="AJ14" s="135">
         <f t="shared" si="18"/>
-        <v>0.74</v>
+        <v>0.86</v>
       </c>
       <c r="AK14" s="137">
         <f t="shared" si="19"/>
-        <v>0.94</v>
+        <v>0.92</v>
       </c>
       <c r="AL14" s="93">
         <v>0.88</v>
@@ -3269,37 +3269,37 @@
         <v>615384.61538461538</v>
       </c>
       <c r="D15" s="126">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="E15" s="126">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="F15" s="127">
         <f>DATA!E4</f>
-        <v>1.3658536585365855</v>
+        <v>1.4347826086956521</v>
       </c>
       <c r="G15" s="128">
         <f>DATA!F4</f>
-        <v>5484.3536585365855</v>
+        <v>5721.858695652174</v>
       </c>
       <c r="H15" s="128">
         <f>DATA!G4</f>
-        <v>4015.3303571428573</v>
+        <v>3987.962121212121</v>
       </c>
       <c r="I15" s="125">
-        <v>449717</v>
+        <v>526411</v>
       </c>
       <c r="J15" s="129">
         <f t="shared" si="3"/>
-        <v>0.73079012499999996</v>
+        <v>0.85541787499999999</v>
       </c>
       <c r="K15" s="111">
         <f t="shared" si="21"/>
-        <v>0.1929692713951848</v>
-      </c>
-      <c r="L15" s="112" t="str">
+        <v>0.20932403369243277</v>
+      </c>
+      <c r="L15" s="112">
         <f t="shared" si="4"/>
-        <v/>
+        <v>6725.5812025378646</v>
       </c>
       <c r="M15" s="113">
         <f t="shared" si="5"/>
@@ -3307,38 +3307,38 @@
       </c>
       <c r="N15" s="130">
         <f t="shared" si="22"/>
-        <v>165667.61538461538</v>
+        <v>88973.615384615376</v>
       </c>
       <c r="O15" s="130">
         <f t="shared" si="6"/>
-        <v>55222.538461538461</v>
+        <v>88973.615384615376</v>
       </c>
       <c r="P15" s="129">
         <f t="shared" si="7"/>
-        <v>0.73079012499999996</v>
+        <v>0.85541787499999999</v>
       </c>
       <c r="Q15" s="109">
         <f t="shared" si="8"/>
-        <v>499685.55555555556</v>
+        <v>544563.10344827583</v>
       </c>
       <c r="R15" s="115">
         <f t="shared" si="23"/>
-        <v>0.19135092824486225</v>
-      </c>
-      <c r="S15" s="106" t="str">
+        <v>0.20732211478622781</v>
+      </c>
+      <c r="S15" s="106">
         <f t="shared" si="24"/>
-        <v/>
+        <v>7232.2246522027708</v>
       </c>
       <c r="T15" s="129">
         <f t="shared" si="9"/>
-        <v>0.81198902777777782</v>
+        <v>0.88491504310344826</v>
       </c>
       <c r="U15" s="131">
         <f t="shared" si="10"/>
-        <v>7.5168829798459416E-2</v>
+        <v>7.7796190778869956E-2</v>
       </c>
       <c r="V15" s="62">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="W15" s="64">
         <v>30</v>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="Z15" s="133">
         <f t="shared" si="12"/>
-        <v>1090.8776978417268</v>
+        <v>1182.5771812080536</v>
       </c>
       <c r="AA15" s="17">
         <f t="shared" si="13"/>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="AB15" s="134">
         <f t="shared" si="14"/>
-        <v>0.1929692713951848</v>
+        <v>0.20932403369243277</v>
       </c>
       <c r="AC15" s="135">
         <f t="shared" si="25"/>
@@ -3365,15 +3365,15 @@
       </c>
       <c r="AD15" s="134">
         <f t="shared" si="26"/>
-        <v>0.19135092824486225</v>
+        <v>0.20732211478622781</v>
       </c>
       <c r="AE15" s="134">
         <f t="shared" si="15"/>
-        <v>0.73079012499999996</v>
+        <v>0.85541787499999999</v>
       </c>
       <c r="AF15" s="134">
         <f t="shared" si="16"/>
-        <v>0.81198902777777782</v>
+        <v>0.88491504310344826</v>
       </c>
       <c r="AG15" s="134">
         <f>IFERROR(VLOOKUP(A15,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3387,13 +3387,13 @@
         <f t="shared" si="27"/>
         <v>0.17391304347826086</v>
       </c>
-      <c r="AJ15" s="135" t="str">
+      <c r="AJ15" s="135">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK15" s="137" t="str">
+        <v>0.7</v>
+      </c>
+      <c r="AK15" s="137">
         <f t="shared" si="19"/>
-        <v/>
+        <v>0.76</v>
       </c>
       <c r="AL15" s="93">
         <v>0.89</v>
@@ -3414,37 +3414,37 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D16" s="126">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E16" s="126">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="F16" s="127">
         <f>DATA!E5</f>
-        <v>1.6179775280898876</v>
+        <v>1.6666666666666667</v>
       </c>
       <c r="G16" s="128">
         <f>DATA!F5</f>
-        <v>6268.4494382022476</v>
+        <v>6441</v>
       </c>
       <c r="H16" s="128">
         <f>DATA!G5</f>
-        <v>3874.25</v>
+        <v>3864.6</v>
       </c>
       <c r="I16" s="125">
-        <v>557892</v>
+        <v>618336</v>
       </c>
       <c r="J16" s="129">
         <f t="shared" si="3"/>
-        <v>0.8773301612903226</v>
+        <v>0.97238322580645165</v>
       </c>
       <c r="K16" s="111">
         <f t="shared" si="21"/>
-        <v>0.23938613118294938</v>
+        <v>0.24587743359702613</v>
       </c>
       <c r="L16" s="112">
         <f t="shared" si="4"/>
-        <v>8130.989331760059</v>
+        <v>10608.627749977288</v>
       </c>
       <c r="M16" s="113">
         <f t="shared" si="5"/>
@@ -3452,38 +3452,38 @@
       </c>
       <c r="N16" s="130">
         <f t="shared" ref="N16:N25" si="28">IFERROR(IF(C16-I16&lt;0,"",C16-I16),"")</f>
-        <v>78005.435897435877</v>
+        <v>17561.435897435877</v>
       </c>
       <c r="O16" s="130">
         <f t="shared" si="6"/>
-        <v>26001.811965811958</v>
+        <v>17561.435897435877</v>
       </c>
       <c r="P16" s="129">
         <f t="shared" si="7"/>
-        <v>0.8773301612903226</v>
+        <v>0.97238322580645165</v>
       </c>
       <c r="Q16" s="109">
         <f t="shared" si="8"/>
-        <v>617666.14285714284</v>
+        <v>638947.19999999995</v>
       </c>
       <c r="R16" s="115">
         <f t="shared" si="23"/>
-        <v>0.23653073111095238</v>
+        <v>0.24325534341553315</v>
       </c>
       <c r="S16" s="106">
         <f t="shared" si="24"/>
-        <v>10205.354924513151</v>
+        <v>11165.420262772972</v>
       </c>
       <c r="T16" s="129">
         <f t="shared" si="9"/>
-        <v>0.97132982142857138</v>
+        <v>1.004796</v>
       </c>
       <c r="U16" s="131">
         <f t="shared" si="10"/>
-        <v>7.867190679690679E-2</v>
+        <v>7.8472679394338385E-2</v>
       </c>
       <c r="V16" s="62">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="W16" s="64">
         <v>31</v>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="Z16" s="133">
         <f t="shared" si="12"/>
-        <v>1131.2805755395684</v>
+        <v>1223.3557046979865</v>
       </c>
       <c r="AA16" s="17">
         <f t="shared" si="13"/>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="AB16" s="134">
         <f t="shared" si="14"/>
-        <v>0.23938613118294938</v>
+        <v>0.24587743359702613</v>
       </c>
       <c r="AC16" s="135">
         <f t="shared" si="25"/>
@@ -3510,15 +3510,15 @@
       </c>
       <c r="AD16" s="134">
         <f t="shared" si="26"/>
-        <v>0.23653073111095238</v>
+        <v>0.24325534341553315</v>
       </c>
       <c r="AE16" s="134">
         <f t="shared" si="15"/>
-        <v>0.8773301612903226</v>
+        <v>0.97238322580645165</v>
       </c>
       <c r="AF16" s="134">
         <f t="shared" si="16"/>
-        <v>0.97132982142857138</v>
+        <v>1.004796</v>
       </c>
       <c r="AG16" s="134">
         <f>IFERROR(VLOOKUP(A16,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3534,11 +3534,11 @@
       </c>
       <c r="AJ16" s="135">
         <f t="shared" si="18"/>
-        <v>0.74</v>
+        <v>0.94</v>
       </c>
       <c r="AK16" s="137">
         <f t="shared" si="19"/>
-        <v>0.94</v>
+        <v>1</v>
       </c>
       <c r="AL16" s="93">
         <v>0.9</v>
@@ -3559,33 +3559,33 @@
         <v>635897.43589743588</v>
       </c>
       <c r="D17" s="126">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E17" s="126">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F17" s="127">
         <f>DATA!E6</f>
-        <v>1.2380952380952381</v>
+        <v>1.1846153846153846</v>
       </c>
       <c r="G17" s="128">
         <f>DATA!F6</f>
-        <v>4888.1428571428569</v>
+        <v>4648.9230769230771</v>
       </c>
       <c r="H17" s="128">
         <f>DATA!G6</f>
-        <v>3948.1153846153848</v>
+        <v>3924.4155844155844</v>
       </c>
       <c r="I17" s="125">
-        <v>307953</v>
+        <v>302180</v>
       </c>
       <c r="J17" s="129">
         <f t="shared" si="3"/>
-        <v>0.48428092741935486</v>
+        <v>0.4752024193548387</v>
       </c>
       <c r="K17" s="111">
         <f t="shared" si="21"/>
-        <v>0.13213969237089401</v>
+        <v>0.12015998241142252</v>
       </c>
       <c r="L17" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3597,23 +3597,23 @@
       </c>
       <c r="N17" s="130">
         <f t="shared" si="28"/>
-        <v>327944.43589743588</v>
+        <v>333717.43589743588</v>
       </c>
       <c r="O17" s="130">
         <f t="shared" si="6"/>
-        <v>109314.81196581195</v>
+        <v>333717.43589743588</v>
       </c>
       <c r="P17" s="129">
         <f t="shared" si="7"/>
-        <v>0.48428092741935486</v>
+        <v>0.4752024193548387</v>
       </c>
       <c r="Q17" s="109">
         <f t="shared" si="8"/>
-        <v>340947.96428571432</v>
+        <v>312252.66666666669</v>
       </c>
       <c r="R17" s="115">
         <f t="shared" si="23"/>
-        <v>0.13056352885112374</v>
+        <v>0.11887857034574377</v>
       </c>
       <c r="S17" s="106" t="str">
         <f t="shared" si="24"/>
@@ -3621,14 +3621,14 @@
       </c>
       <c r="T17" s="129">
         <f t="shared" si="9"/>
-        <v>0.53616816964285718</v>
+        <v>0.49104250000000005</v>
       </c>
       <c r="U17" s="131">
         <f t="shared" si="10"/>
-        <v>5.5689102564102561E-2</v>
+        <v>5.3132543339916613E-2</v>
       </c>
       <c r="V17" s="62">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="W17" s="64">
         <v>31</v>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="Z17" s="133">
         <f t="shared" si="12"/>
-        <v>1131.2805755395684</v>
+        <v>1223.3557046979865</v>
       </c>
       <c r="AA17" s="17">
         <f t="shared" si="13"/>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="AB17" s="134">
         <f t="shared" si="14"/>
-        <v>0.13213969237089401</v>
+        <v>0.12015998241142252</v>
       </c>
       <c r="AC17" s="135">
         <f t="shared" si="25"/>
@@ -3655,15 +3655,15 @@
       </c>
       <c r="AD17" s="134">
         <f t="shared" si="26"/>
-        <v>0.13056352885112374</v>
+        <v>0.11887857034574377</v>
       </c>
       <c r="AE17" s="134">
         <f t="shared" si="15"/>
-        <v>0.48428092741935486</v>
+        <v>0.4752024193548387</v>
       </c>
       <c r="AF17" s="134">
         <f t="shared" si="16"/>
-        <v>0.53616816964285718</v>
+        <v>0.49104250000000005</v>
       </c>
       <c r="AG17" s="134">
         <f>IFERROR(VLOOKUP(A17,DATA!$Q$2:$R$3,2,0),"")</f>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="K18" s="111">
         <f t="shared" si="21"/>
-        <v>-1.1380358457444706E-2</v>
+        <v>-1.0546326896269999E-2</v>
       </c>
       <c r="L18" s="112" t="str">
         <f t="shared" si="4"/>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="AB18" s="138">
         <f t="shared" si="14"/>
-        <v>-1.1380358457444706E-2</v>
+        <v>-1.0546326896269999E-2</v>
       </c>
       <c r="AC18" s="135">
         <f t="shared" si="25"/>
@@ -5699,39 +5699,39 @@
       </c>
       <c r="D32" s="153">
         <f>SUM(D13:D31)</f>
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="E32" s="153">
         <f>SUM(E13:E31)</f>
-        <v>587</v>
+        <v>638</v>
       </c>
       <c r="F32" s="154">
         <f>IFERROR(SUM(F13:F31)/G10,)</f>
-        <v>1.6454010561285173</v>
+        <v>1.6701575960271611</v>
       </c>
       <c r="G32" s="155">
         <f>IFERROR(SUM(G13:G31)/G10,)</f>
-        <v>6493.0747183281755</v>
+        <v>6548.688994266603</v>
       </c>
       <c r="H32" s="155">
         <f>IFERROR(SUM(H13:H31)/G10,)</f>
-        <v>4725.707546291469</v>
+        <v>4696.4056396477081</v>
       </c>
       <c r="I32" s="155">
         <f>SUM(I13:I31)</f>
-        <v>2330510.9500000002</v>
+        <v>2514813.9500000002</v>
       </c>
       <c r="J32" s="156">
         <f>IFERROR(I32/C32,)</f>
-        <v>0.7768369833333334</v>
+        <v>0.83827131666666677</v>
       </c>
       <c r="K32" s="156">
         <f>SUM(K13:K31)</f>
-        <v>0.99999999999999989</v>
+        <v>1</v>
       </c>
       <c r="L32" s="155">
         <f>SUM(L13:L31)</f>
-        <v>25881.430938996444</v>
+        <v>36155.451748627369</v>
       </c>
       <c r="M32" s="155">
         <f>SUM(M13:M31)</f>
@@ -5739,33 +5739,33 @@
       </c>
       <c r="N32" s="155">
         <f>SUM(N13:N31)</f>
-        <v>676144.97307692305</v>
+        <v>508289.97307692299</v>
       </c>
       <c r="O32" s="155">
         <f>SUM(O13:O31)</f>
-        <v>216540.97435897432</v>
+        <v>481767.92307692301</v>
       </c>
       <c r="P32" s="157"/>
       <c r="Q32" s="152">
         <f>SUM(Q13:Q31)</f>
-        <v>2611356.8412698414</v>
+        <v>2626652.270114942</v>
       </c>
       <c r="R32" s="156">
         <f>SUM(R13:R31)</f>
-        <v>0.99999999999999989</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="S32" s="155">
         <f>SUM(S13:S31)</f>
-        <v>30950.587788732169</v>
+        <v>38023.310194127516</v>
       </c>
       <c r="T32" s="158">
         <f>IFERROR(Q32/C32,)</f>
-        <v>0.87045228042328049</v>
+        <v>0.87555075670498062</v>
       </c>
       <c r="U32" s="165"/>
       <c r="V32" s="166">
         <f>SUM(V13:V31)</f>
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="W32" s="167">
         <f>SUM(W13:W31)</f>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="Z32" s="164">
         <f>SUM(Z13:Z31)</f>
-        <v>5616.0000000000009</v>
+        <v>6076</v>
       </c>
       <c r="AA32" s="162">
         <f>SUM(AA13:AA31)</f>
@@ -6948,25 +6948,25 @@
         <v>65</v>
       </c>
       <c r="B2" s="19">
-        <v>483579</v>
+        <v>500027</v>
       </c>
       <c r="C2" s="18">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D2" s="18">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E2" s="16">
         <f>IFERROR((D2/C2),"")</f>
-        <v>1.441860465116279</v>
+        <v>1.4886363636363635</v>
       </c>
       <c r="F2" s="17">
         <f>IFERROR((B2/C2),"")</f>
-        <v>5623.0116279069771</v>
+        <v>5682.125</v>
       </c>
       <c r="G2" s="17">
         <f>IFERROR((B2/D2),"")</f>
-        <v>3899.8306451612902</v>
+        <v>3817</v>
       </c>
       <c r="Q2" s="6" t="s">
         <v>38</v>
@@ -6980,25 +6980,25 @@
         <v>67</v>
       </c>
       <c r="B3" s="19">
-        <v>557892</v>
+        <v>594382</v>
       </c>
       <c r="C3" s="18">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D3" s="18">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="E3" s="16">
         <f t="shared" ref="E3:E20" si="0">IFERROR((D3/C3),"")</f>
-        <v>1.5632183908045978</v>
+        <v>1.576086956521739</v>
       </c>
       <c r="F3" s="17">
         <f t="shared" ref="F3:F20" si="1">IFERROR((B3/C3),"")</f>
-        <v>6412.5517241379312</v>
+        <v>6460.673913043478</v>
       </c>
       <c r="G3" s="17">
         <f t="shared" ref="G3:G20" si="2">IFERROR((B3/D3),"")</f>
-        <v>4102.1470588235297</v>
+        <v>4099.186206896552</v>
       </c>
       <c r="Q3" s="6" t="s">
         <v>40</v>
@@ -7012,25 +7012,25 @@
         <v>64</v>
       </c>
       <c r="B4" s="174">
-        <v>449717</v>
+        <v>526411</v>
       </c>
       <c r="C4" s="18">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="D4" s="18">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="E4" s="16">
         <f t="shared" si="0"/>
-        <v>1.3658536585365855</v>
+        <v>1.4347826086956521</v>
       </c>
       <c r="F4" s="17">
         <f t="shared" si="1"/>
-        <v>5484.3536585365855</v>
+        <v>5721.858695652174</v>
       </c>
       <c r="G4" s="17">
         <f t="shared" si="2"/>
-        <v>4015.3303571428573</v>
+        <v>3987.962121212121</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -7038,25 +7038,25 @@
         <v>66</v>
       </c>
       <c r="B5" s="175">
-        <v>557892</v>
+        <v>618336</v>
       </c>
       <c r="C5" s="18">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D5" s="18">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="E5" s="16">
         <f t="shared" si="0"/>
-        <v>1.6179775280898876</v>
+        <v>1.6666666666666667</v>
       </c>
       <c r="F5" s="17">
         <f t="shared" si="1"/>
-        <v>6268.4494382022476</v>
+        <v>6441</v>
       </c>
       <c r="G5" s="17">
         <f t="shared" si="2"/>
-        <v>3874.25</v>
+        <v>3864.6</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -7064,25 +7064,25 @@
         <v>68</v>
       </c>
       <c r="B6" s="19">
-        <v>307953</v>
+        <v>302180</v>
       </c>
       <c r="C6" s="18">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D6" s="18">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E6" s="16">
         <f t="shared" si="0"/>
-        <v>1.2380952380952381</v>
+        <v>1.1846153846153846</v>
       </c>
       <c r="F6" s="17">
         <f t="shared" si="1"/>
-        <v>4888.1428571428569</v>
+        <v>4648.9230769230771</v>
       </c>
       <c r="G6" s="17">
         <f t="shared" si="2"/>
-        <v>3948.1153846153848</v>
+        <v>3924.4155844155844</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
